--- a/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
@@ -34002,7 +34002,7 @@
         <v>1</v>
       </c>
       <c r="O533" s="5" t="n">
-        <v>34.77</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="534">
@@ -34063,7 +34063,7 @@
         <v>1</v>
       </c>
       <c r="O534" s="5" t="n">
-        <v>11.55</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="535">
@@ -34124,7 +34124,7 @@
         <v>1</v>
       </c>
       <c r="O535" s="5" t="n">
-        <v>11.45</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="536">
@@ -34179,13 +34179,13 @@
       </c>
       <c r="L536" s="5" t="n"/>
       <c r="M536" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N536" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O536" s="5" t="n">
-        <v>10.94</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="537">
@@ -34240,13 +34240,13 @@
       </c>
       <c r="L537" s="5" t="n"/>
       <c r="M537" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N537" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O537" s="5" t="n">
-        <v>12.74</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="538">
@@ -34301,13 +34301,13 @@
       </c>
       <c r="L538" s="5" t="n"/>
       <c r="M538" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N538" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O538" s="5" t="n">
-        <v>8.68</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="539">
@@ -34368,7 +34368,7 @@
         <v>1</v>
       </c>
       <c r="O539" s="5" t="n">
-        <v>9.130000000000001</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="540">
@@ -34429,7 +34429,7 @@
         <v>1</v>
       </c>
       <c r="O540" s="5" t="n">
-        <v>11.57</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="541">
@@ -34490,7 +34490,7 @@
         <v>1</v>
       </c>
       <c r="O541" s="5" t="n">
-        <v>9.210000000000001</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Raw" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$541</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$637</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -551,27 +551,27 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Raw!E2:E541,"en")</f>
+        <f>COUNTIF(Raw!E2:E637,"en")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"en",Raw!I2:I541,TRUE)/COUNTIF(Raw!E2:E541,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"en",Raw!I2:I637,TRUE)/COUNTIF(Raw!E2:E637,"en"),"")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"en",Raw!K2:K541,"success")/COUNTIF(Raw!E2:E541,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"en",Raw!K2:K637,"success")/COUNTIF(Raw!E2:E637,"en"),"")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"en",Raw!J2:J541,TRUE)/COUNTIF(Raw!E2:E541,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"en",Raw!J2:J637,TRUE)/COUNTIF(Raw!E2:E637,"en"),"")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!E2:E541,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!E2:E637,"en"),"")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!E2:E541,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!E2:E637,"en"),"")</f>
         <v/>
       </c>
     </row>
@@ -582,27 +582,27 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Raw!E2:E541,"fr")</f>
+        <f>COUNTIF(Raw!E2:E637,"fr")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"fr",Raw!I2:I541,TRUE)/COUNTIF(Raw!E2:E541,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"fr",Raw!I2:I637,TRUE)/COUNTIF(Raw!E2:E637,"fr"),"")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"fr",Raw!K2:K541,"success")/COUNTIF(Raw!E2:E541,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"fr",Raw!K2:K637,"success")/COUNTIF(Raw!E2:E637,"fr"),"")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"fr",Raw!J2:J541,TRUE)/COUNTIF(Raw!E2:E541,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"fr",Raw!J2:J637,TRUE)/COUNTIF(Raw!E2:E637,"fr"),"")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!E2:E541,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!E2:E637,"fr"),"")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!E2:E541,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!E2:E637,"fr"),"")</f>
         <v/>
       </c>
     </row>
@@ -613,27 +613,27 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Raw!E2:E541,"ar")</f>
+        <f>COUNTIF(Raw!E2:E637,"ar")</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"ar",Raw!I2:I541,TRUE)/COUNTIF(Raw!E2:E541,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"ar",Raw!I2:I637,TRUE)/COUNTIF(Raw!E2:E637,"ar"),"")</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"ar",Raw!K2:K541,"success")/COUNTIF(Raw!E2:E541,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"ar",Raw!K2:K637,"success")/COUNTIF(Raw!E2:E637,"ar"),"")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E541,"ar",Raw!J2:J541,TRUE)/COUNTIF(Raw!E2:E541,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E637,"ar",Raw!J2:J637,TRUE)/COUNTIF(Raw!E2:E637,"ar"),"")</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!E2:E541,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!E2:E637,"ar"),"")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!E2:E541,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!E2:E637,"ar"),"")</f>
         <v/>
       </c>
     </row>
@@ -688,27 +688,27 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Raw!F2:F541,"zero-shot")</f>
+        <f>COUNTIF(Raw!F2:F637,"zero-shot")</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"zero-shot",Raw!I2:I541,TRUE)/COUNTIF(Raw!F2:F541,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"zero-shot",Raw!I2:I637,TRUE)/COUNTIF(Raw!F2:F637,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"zero-shot",Raw!K2:K541,"success")/COUNTIF(Raw!F2:F541,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"zero-shot",Raw!K2:K637,"success")/COUNTIF(Raw!F2:F637,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"zero-shot",Raw!J2:J541,TRUE)/COUNTIF(Raw!F2:F541,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"zero-shot",Raw!J2:J637,TRUE)/COUNTIF(Raw!F2:F637,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!F2:F541,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!F2:F637,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!F2:F541,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!F2:F637,"zero-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -719,27 +719,27 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Raw!F2:F541,"few-shot")</f>
+        <f>COUNTIF(Raw!F2:F637,"few-shot")</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"few-shot",Raw!I2:I541,TRUE)/COUNTIF(Raw!F2:F541,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"few-shot",Raw!I2:I637,TRUE)/COUNTIF(Raw!F2:F637,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"few-shot",Raw!K2:K541,"success")/COUNTIF(Raw!F2:F541,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"few-shot",Raw!K2:K637,"success")/COUNTIF(Raw!F2:F637,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"few-shot",Raw!J2:J541,TRUE)/COUNTIF(Raw!F2:F541,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"few-shot",Raw!J2:J637,TRUE)/COUNTIF(Raw!F2:F637,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!F2:F541,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!F2:F637,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!F2:F541,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!F2:F637,"few-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -750,27 +750,27 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF(Raw!F2:F541,"cot")</f>
+        <f>COUNTIF(Raw!F2:F637,"cot")</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"cot",Raw!I2:I541,TRUE)/COUNTIF(Raw!F2:F541,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"cot",Raw!I2:I637,TRUE)/COUNTIF(Raw!F2:F637,"cot"),"")</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"cot",Raw!K2:K541,"success")/COUNTIF(Raw!F2:F541,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"cot",Raw!K2:K637,"success")/COUNTIF(Raw!F2:F637,"cot"),"")</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F541,"cot",Raw!J2:J541,TRUE)/COUNTIF(Raw!F2:F541,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F637,"cot",Raw!J2:J637,TRUE)/COUNTIF(Raw!F2:F637,"cot"),"")</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!F2:F541,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!F2:F637,"cot"),"")</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!F2:F541,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!F2:F637,"cot"),"")</f>
         <v/>
       </c>
     </row>
@@ -823,27 +823,27 @@
         <v>1</v>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Raw!B2:B541,"1")</f>
+        <f>COUNTIF(Raw!B2:B637,"1")</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"1",Raw!I2:I541,TRUE)/COUNTIF(Raw!B2:B541,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"1",Raw!I2:I637,TRUE)/COUNTIF(Raw!B2:B637,"1"),"")</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"1",Raw!K2:K541,"success")/COUNTIF(Raw!B2:B541,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"1",Raw!K2:K637,"success")/COUNTIF(Raw!B2:B637,"1"),"")</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"1",Raw!J2:J541,TRUE)/COUNTIF(Raw!B2:B541,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"1",Raw!J2:J637,TRUE)/COUNTIF(Raw!B2:B637,"1"),"")</f>
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!B2:B541,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!B2:B637,"1"),"")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!B2:B541,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!B2:B637,"1"),"")</f>
         <v/>
       </c>
     </row>
@@ -852,27 +852,27 @@
         <v>2</v>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Raw!B2:B541,"2")</f>
+        <f>COUNTIF(Raw!B2:B637,"2")</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"2",Raw!I2:I541,TRUE)/COUNTIF(Raw!B2:B541,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"2",Raw!I2:I637,TRUE)/COUNTIF(Raw!B2:B637,"2"),"")</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"2",Raw!K2:K541,"success")/COUNTIF(Raw!B2:B541,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"2",Raw!K2:K637,"success")/COUNTIF(Raw!B2:B637,"2"),"")</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"2",Raw!J2:J541,TRUE)/COUNTIF(Raw!B2:B541,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"2",Raw!J2:J637,TRUE)/COUNTIF(Raw!B2:B637,"2"),"")</f>
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!B2:B541,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!B2:B637,"2"),"")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!B2:B541,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!B2:B637,"2"),"")</f>
         <v/>
       </c>
     </row>
@@ -881,27 +881,27 @@
         <v>3</v>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Raw!B2:B541,"3")</f>
+        <f>COUNTIF(Raw!B2:B637,"3")</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"3",Raw!I2:I541,TRUE)/COUNTIF(Raw!B2:B541,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"3",Raw!I2:I637,TRUE)/COUNTIF(Raw!B2:B637,"3"),"")</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"3",Raw!K2:K541,"success")/COUNTIF(Raw!B2:B541,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"3",Raw!K2:K637,"success")/COUNTIF(Raw!B2:B637,"3"),"")</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B541,"3",Raw!J2:J541,TRUE)/COUNTIF(Raw!B2:B541,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B637,"3",Raw!J2:J637,TRUE)/COUNTIF(Raw!B2:B637,"3"),"")</f>
         <v/>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!B2:B541,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!B2:B637,"3"),"")</f>
         <v/>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!B2:B541,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!B2:B637,"3"),"")</f>
         <v/>
       </c>
     </row>
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF(Raw!C2:C541,"single_kg1")</f>
+        <f>COUNTIF(Raw!C2:C637,"single_kg1")</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg1",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg1",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg1",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"single_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -987,27 +987,27 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF(Raw!C2:C541,"single_kg2")</f>
+        <f>COUNTIF(Raw!C2:C637,"single_kg2")</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg2",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg2",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg2",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"single_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF(Raw!C2:C541,"single_kg3")</f>
+        <f>COUNTIF(Raw!C2:C637,"single_kg3")</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg3",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg3",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"single_kg3",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"single_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"single_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"single_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1049,27 +1049,27 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Raw!C2:C541,"cross_kg")</f>
+        <f>COUNTIF(Raw!C2:C637,"cross_kg")</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"cross_kg",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"cross_kg",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"cross_kg",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"cross_kg",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"cross_kg",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"cross_kg",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"cross_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1080,27 +1080,27 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Raw!C2:C541,"open_kg")</f>
+        <f>COUNTIF(Raw!C2:C637,"open_kg")</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"open_kg",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"open_kg",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"open_kg",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"open_kg",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"open_kg",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"open_kg",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="G28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"open_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1111,399 +1111,740 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Raw!C2:C541,"count_kg1")</f>
+        <f>COUNTIF(Raw!C2:C637,"count_kg1")</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"count_kg1",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"count_kg1",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"count_kg1",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="F29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="G29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"count_kg1"),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>count_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF(Raw!C2:C541,"count_kg3")</f>
+        <f>COUNTIF(Raw!C2:C637,"count_kg2")</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"count_kg3",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"count_kg3",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"count_kg3",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"count_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="G30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"count_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"count_kg2"),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg1</t>
+          <t>count_kg3</t>
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF(Raw!C2:C541,"filter_numeric_kg1")</f>
+        <f>COUNTIF(Raw!C2:C637,"count_kg3")</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_numeric_kg1",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_numeric_kg1",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_numeric_kg1",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="F31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="G31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"count_kg3"),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_numeric_kg1</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF(Raw!C2:C541,"filter_numeric_kg2")</f>
+        <f>COUNTIF(Raw!C2:C637,"filter_numeric_kg1")</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_numeric_kg2",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_numeric_kg2",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_numeric_kg2",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="F32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF(Raw!C2:C541,"filter_string_kg2")</f>
+        <f>COUNTIF(Raw!C2:C637,"filter_numeric_kg2")</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_string_kg2",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_string_kg2",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_string_kg2",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="F33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF(Raw!C2:C541,"filter_string_kg3")</f>
+        <f>COUNTIF(Raw!C2:C637,"filter_numeric_kg3")</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_string_kg3",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_string_kg3",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"filter_string_kg3",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="F34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"filter_string_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"filter_string_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="B35" s="5">
-        <f>COUNTIF(Raw!C2:C541,"ranking_kg2")</f>
+        <f>COUNTIF(Raw!C2:C637,"filter_string_kg2")</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"ranking_kg2",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"ranking_kg2",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"ranking_kg2",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="F35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_string_kg2"),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>compare_two_airports</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="B36" s="5">
-        <f>COUNTIF(Raw!C2:C541,"compare_two_airports")</f>
+        <f>COUNTIF(Raw!C2:C637,"filter_string_kg3")</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"compare_two_airports",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"compare_two_airports",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"compare_two_airports",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="F36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_string_kg3"),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="B37" s="5">
-        <f>COUNTIF(Raw!C2:C541,"out_of_scope")</f>
+        <f>COUNTIF(Raw!C2:C637,"ranking_kg1")</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"out_of_scope",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"out_of_scope",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"out_of_scope",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="F37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ranking_kg1"),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="B38" s="5">
-        <f>COUNTIF(Raw!C2:C541,"ask_query")</f>
+        <f>COUNTIF(Raw!C2:C637,"ranking_kg2")</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"ask_query",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"ask_query",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"ask_query",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="F38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="G38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ranking_kg2"),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>typo_fuzzy</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="B39" s="5">
-        <f>COUNTIF(Raw!C2:C541,"typo_fuzzy")</f>
+        <f>COUNTIF(Raw!C2:C637,"ranking_kg3")</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"typo_fuzzy",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"typo_fuzzy",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"typo_fuzzy",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="F39" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="G39" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ranking_kg3"),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>multilingual_edge</t>
+          <t>compare_two_airports</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <f>COUNTIF(Raw!C2:C541,"multilingual_edge")</f>
+        <f>COUNTIF(Raw!C2:C637,"compare_two_airports")</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"multilingual_edge",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_airports",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="D40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"multilingual_edge",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_airports",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="E40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"multilingual_edge",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_airports",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="F40" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="G40" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"compare_two_airports"),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="B41" s="5">
+        <f>COUNTIF(Raw!C2:C637,"compare_two_flights")</f>
+        <v/>
+      </c>
+      <c r="C41" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_flights",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_flights"),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_flights",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"compare_two_flights"),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_flights",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_flights"),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"compare_two_flights"),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"compare_two_flights"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="B42" s="5">
+        <f>COUNTIF(Raw!C2:C637,"compare_two_departments")</f>
+        <v/>
+      </c>
+      <c r="C42" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_departments",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_departments"),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_departments",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"compare_two_departments"),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_departments",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_departments"),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"compare_two_departments"),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"compare_two_departments"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1</t>
+        </is>
+      </c>
+      <c r="B43" s="5">
+        <f>COUNTIF(Raw!C2:C637,"group_aggregate_kg1")</f>
+        <v/>
+      </c>
+      <c r="C43" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg2</t>
+        </is>
+      </c>
+      <c r="B44" s="5">
+        <f>COUNTIF(Raw!C2:C637,"group_aggregate_kg2")</f>
+        <v/>
+      </c>
+      <c r="C44" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="B45" s="5">
+        <f>COUNTIF(Raw!C2:C637,"group_aggregate_kg3")</f>
+        <v/>
+      </c>
+      <c r="C45" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="B46" s="5">
+        <f>COUNTIF(Raw!C2:C637,"out_of_scope")</f>
+        <v/>
+      </c>
+      <c r="C46" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"out_of_scope",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"out_of_scope"),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"out_of_scope",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"out_of_scope"),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"out_of_scope",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"out_of_scope"),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"out_of_scope"),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"out_of_scope"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="B47" s="5">
+        <f>COUNTIF(Raw!C2:C637,"ask_query")</f>
+        <v/>
+      </c>
+      <c r="C47" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ask_query",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ask_query"),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ask_query",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ask_query"),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ask_query",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ask_query"),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ask_query"),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ask_query"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>typo_fuzzy</t>
+        </is>
+      </c>
+      <c r="B48" s="5">
+        <f>COUNTIF(Raw!C2:C637,"typo_fuzzy")</f>
+        <v/>
+      </c>
+      <c r="C48" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"typo_fuzzy",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"typo_fuzzy",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"typo_fuzzy",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>multilingual_edge</t>
+        </is>
+      </c>
+      <c r="B49" s="5">
+        <f>COUNTIF(Raw!C2:C637,"multilingual_edge")</f>
+        <v/>
+      </c>
+      <c r="C49" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multilingual_edge",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"multilingual_edge"),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multilingual_edge",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"multilingual_edge"),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multilingual_edge",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"multilingual_edge"),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"multilingual_edge"),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"multilingual_edge"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>property_ambiguity</t>
         </is>
       </c>
-      <c r="B41" s="5">
-        <f>COUNTIF(Raw!C2:C541,"property_ambiguity")</f>
+      <c r="B50" s="5">
+        <f>COUNTIF(Raw!C2:C637,"property_ambiguity")</f>
         <v/>
       </c>
-      <c r="C41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"property_ambiguity",Raw!I2:I541,TRUE)/COUNTIF(Raw!C2:C541,"property_ambiguity"),"")</f>
+      <c r="C50" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"property_ambiguity",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"property_ambiguity"),"")</f>
         <v/>
       </c>
-      <c r="D41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"property_ambiguity",Raw!K2:K541,"success")/COUNTIF(Raw!C2:C541,"property_ambiguity"),"")</f>
+      <c r="D50" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"property_ambiguity",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"property_ambiguity"),"")</f>
         <v/>
       </c>
-      <c r="E41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C541,"property_ambiguity",Raw!J2:J541,TRUE)/COUNTIF(Raw!C2:C541,"property_ambiguity"),"")</f>
+      <c r="E50" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"property_ambiguity",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"property_ambiguity"),"")</f>
         <v/>
       </c>
-      <c r="F41" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M541,Raw!C2:C541,"property_ambiguity"),"")</f>
+      <c r="F50" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"property_ambiguity"),"")</f>
         <v/>
       </c>
-      <c r="G41" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N541,Raw!C2:C541,"property_ambiguity"),"")</f>
+      <c r="G50" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"property_ambiguity"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>ghost_property</t>
+        </is>
+      </c>
+      <c r="B51" s="5">
+        <f>COUNTIF(Raw!C2:C637,"ghost_property")</f>
+        <v/>
+      </c>
+      <c r="C51" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ghost_property",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ghost_property"),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ghost_property",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ghost_property"),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ghost_property",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ghost_property"),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ghost_property"),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ghost_property"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>multi_value_ambiguity</t>
+        </is>
+      </c>
+      <c r="B52" s="5">
+        <f>COUNTIF(Raw!C2:C637,"multi_value_ambiguity")</f>
+        <v/>
+      </c>
+      <c r="C52" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multi_value_ambiguity",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multi_value_ambiguity",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="6">
+        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multi_value_ambiguity",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="6">
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1518,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O541"/>
+  <dimension ref="A1:O637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33398,20 +33739,20 @@
     <row r="524">
       <c r="A524" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B524" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C524" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E524" s="5" t="inlineStr">
@@ -33426,12 +33767,12 @@
       </c>
       <c r="G524" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H524" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I524" s="5" t="b">
@@ -33453,46 +33794,46 @@
         <v>1</v>
       </c>
       <c r="O524" s="5" t="n">
-        <v>25.94</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C525" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E525" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F525" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G525" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H525" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I525" s="5" t="b">
@@ -33514,46 +33855,46 @@
         <v>1</v>
       </c>
       <c r="O525" s="5" t="n">
-        <v>15.82</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_001</t>
         </is>
       </c>
       <c r="B526" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C526" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E526" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F526" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G526" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H526" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I526" s="5" t="b">
@@ -33575,31 +33916,31 @@
         <v>1</v>
       </c>
       <c r="O526" s="5" t="n">
-        <v>15.64</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C527" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E527" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F527" s="5" t="inlineStr">
@@ -33609,12 +33950,12 @@
       </c>
       <c r="G527" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H527" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I527" s="5" t="b">
@@ -33636,26 +33977,26 @@
         <v>1</v>
       </c>
       <c r="O527" s="5" t="n">
-        <v>20.2</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B528" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C528" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E528" s="5" t="inlineStr">
@@ -33665,17 +34006,17 @@
       </c>
       <c r="F528" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G528" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H528" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I528" s="5" t="b">
@@ -33697,46 +34038,46 @@
         <v>1</v>
       </c>
       <c r="O528" s="5" t="n">
-        <v>17.53</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_002</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C529" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E529" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F529" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G529" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H529" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I529" s="5" t="b">
@@ -33758,31 +34099,31 @@
         <v>1</v>
       </c>
       <c r="O529" s="5" t="n">
-        <v>17.52</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B530" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C530" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E530" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F530" s="5" t="inlineStr">
@@ -33792,114 +34133,114 @@
       </c>
       <c r="G530" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H530" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I530" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J530" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K530" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L530" s="5" t="n"/>
       <c r="M530" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N530" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O530" s="5" t="n">
-        <v>12.89</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C531" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E531" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F531" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I531" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J531" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L531" s="5" t="n"/>
       <c r="M531" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N531" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O531" s="5" t="n">
-        <v>5.49</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>filter_string_kg2_003</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C532" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>filter_string_kg2</t>
         </is>
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E532" s="5" t="inlineStr">
@@ -33909,58 +34250,58 @@
       </c>
       <c r="F532" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G532" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H532" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I532" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J532" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K532" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L532" s="5" t="n"/>
       <c r="M532" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N532" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O532" s="5" t="n">
-        <v>6.3</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>filter_numeric_kg3_001</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C533" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E533" s="5" t="inlineStr">
@@ -33975,53 +34316,57 @@
       </c>
       <c r="G533" s="5" t="inlineStr">
         <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H533" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H533" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I533" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J533" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K533" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L533" s="5" t="n"/>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L533" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'memberOf', 'value': '550', 'operator': '&gt;', 'direction': 'incoming', 'limit': 10}</t>
+        </is>
+      </c>
       <c r="M533" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N533" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O533" s="5" t="n">
-        <v>33.34</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>filter_numeric_kg3_001</t>
         </is>
       </c>
       <c r="B534" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C534" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E534" s="5" t="inlineStr">
@@ -34036,53 +34381,57 @@
       </c>
       <c r="G534" s="5" t="inlineStr">
         <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H534" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H534" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I534" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J534" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K534" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L534" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L534" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'size', 'operator': '&gt;', 'threshold': 550}</t>
+        </is>
+      </c>
       <c r="M534" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N534" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O534" s="5" t="n">
-        <v>13.65</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_001</t>
+          <t>filter_numeric_kg3_001</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C535" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E535" s="5" t="inlineStr">
@@ -34097,53 +34446,57 @@
       </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H535" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H535" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I535" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J535" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L535" s="5" t="n"/>
+          <t>execution_failure</t>
+        </is>
+      </c>
+      <c r="L535" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'memberOf', 'value': 'Department', 'operator': '&gt;=', 'threshold': 550, 'limit': 10}</t>
+        </is>
+      </c>
       <c r="M535" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N535" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O535" s="5" t="n">
-        <v>13.49</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B536" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C536" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E536" s="5" t="inlineStr">
@@ -34158,12 +34511,12 @@
       </c>
       <c r="G536" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H536" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I536" s="5" t="b">
@@ -34185,46 +34538,46 @@
         <v>1</v>
       </c>
       <c r="O536" s="5" t="n">
-        <v>13.48</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C537" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E537" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F537" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G537" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H537" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I537" s="5" t="b">
@@ -34246,46 +34599,46 @@
         <v>1</v>
       </c>
       <c r="O537" s="5" t="n">
-        <v>16.2</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B538" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C538" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E538" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F538" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G538" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H538" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I538" s="5" t="b">
@@ -34307,31 +34660,31 @@
         <v>1</v>
       </c>
       <c r="O538" s="5" t="n">
-        <v>10.18</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C539" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E539" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F539" s="5" t="inlineStr">
@@ -34341,12 +34694,12 @@
       </c>
       <c r="G539" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H539" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I539" s="5" t="b">
@@ -34368,26 +34721,26 @@
         <v>1</v>
       </c>
       <c r="O539" s="5" t="n">
-        <v>10.9</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B540" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C540" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E540" s="5" t="inlineStr">
@@ -34397,17 +34750,17 @@
       </c>
       <c r="F540" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G540" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H540" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I540" s="5" t="b">
@@ -34429,46 +34782,46 @@
         <v>1</v>
       </c>
       <c r="O540" s="5" t="n">
-        <v>13.55</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2_003</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C541" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E541" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F541" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G541" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H541" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I541" s="5" t="b">
@@ -34490,11 +34843,5865 @@
         <v>1</v>
       </c>
       <c r="O541" s="5" t="n">
-        <v>9.859999999999999</v>
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="5" t="inlineStr">
+        <is>
+          <t>open_kg_007</t>
+        </is>
+      </c>
+      <c r="B542" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C542" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="D542" s="5" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="E542" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F542" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G542" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H542" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I542" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J542" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K542" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L542" s="5" t="n"/>
+      <c r="M542" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N542" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" s="5" t="n">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="5" t="inlineStr">
+        <is>
+          <t>open_kg_007</t>
+        </is>
+      </c>
+      <c r="B543" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="E543" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G543" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H543" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I543" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J543" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K543" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L543" s="5" t="n"/>
+      <c r="M543" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N543" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" s="5" t="n">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="5" t="inlineStr">
+        <is>
+          <t>open_kg_007</t>
+        </is>
+      </c>
+      <c r="B544" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C544" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="D544" s="5" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="E544" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F544" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G544" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="H544" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I544" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J544" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K544" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L544" s="5" t="n"/>
+      <c r="M544" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N544" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" s="5" t="n">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_001</t>
+        </is>
+      </c>
+      <c r="B545" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E545" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F545" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G545" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H545" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I545" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J545" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K545" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L545" s="5" t="n"/>
+      <c r="M545" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N545" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O545" s="5" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_001</t>
+        </is>
+      </c>
+      <c r="B546" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C546" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D546" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E546" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F546" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G546" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H546" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I546" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J546" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K546" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L546" s="5" t="n"/>
+      <c r="M546" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N546" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O546" s="5" t="n">
+        <v>41.08</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_001</t>
+        </is>
+      </c>
+      <c r="B547" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E547" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G547" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H547" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I547" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J547" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K547" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L547" s="5" t="n"/>
+      <c r="M547" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N547" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O547" s="5" t="n">
+        <v>37.13</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B548" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C548" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E548" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F548" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G548" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H548" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I548" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J548" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K548" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L548" s="5" t="n"/>
+      <c r="M548" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N548" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O548" s="5" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B549" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C549" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E549" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F549" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G549" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H549" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I549" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J549" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K549" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L549" s="5" t="n"/>
+      <c r="M549" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N549" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O549" s="5" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B550" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C550" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E550" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F550" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G550" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H550" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I550" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J550" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K550" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L550" s="5" t="n"/>
+      <c r="M550" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N550" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O550" s="5" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B551" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C551" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E551" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F551" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G551" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H551" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I551" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J551" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K551" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L551" s="5" t="n"/>
+      <c r="M551" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N551" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O551" s="5" t="n">
+        <v>14.77</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B552" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C552" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D552" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E552" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F552" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G552" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H552" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I552" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J552" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K552" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L552" s="5" t="n"/>
+      <c r="M552" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N552" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O552" s="5" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B553" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C553" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E553" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F553" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G553" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H553" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I553" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J553" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K553" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L553" s="5" t="n"/>
+      <c r="M553" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N553" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O553" s="5" t="n">
+        <v>13.21</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B554" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C554" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D554" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E554" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F554" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G554" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H554" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I554" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J554" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K554" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L554" s="5" t="n"/>
+      <c r="M554" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N554" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O554" s="5" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B555" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E555" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F555" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G555" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H555" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I555" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J555" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K555" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L555" s="5" t="n"/>
+      <c r="M555" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N555" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O555" s="5" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_009</t>
+        </is>
+      </c>
+      <c r="B556" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C556" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E556" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F556" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G556" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H556" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I556" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J556" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K556" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L556" s="5" t="n"/>
+      <c r="M556" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N556" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O556" s="5" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_001</t>
+        </is>
+      </c>
+      <c r="B557" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E557" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F557" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G557" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H557" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I557" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J557" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K557" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L557" s="5" t="n"/>
+      <c r="M557" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N557" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O557" s="5" t="n">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_001</t>
+        </is>
+      </c>
+      <c r="B558" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C558" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E558" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F558" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G558" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H558" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I558" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J558" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K558" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L558" s="5" t="n"/>
+      <c r="M558" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N558" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O558" s="5" t="n">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_001</t>
+        </is>
+      </c>
+      <c r="B559" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C559" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E559" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F559" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G559" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H559" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I559" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J559" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K559" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L559" s="5" t="n"/>
+      <c r="M559" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N559" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O559" s="5" t="n">
+        <v>68.23999999999999</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_001</t>
+        </is>
+      </c>
+      <c r="B560" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C560" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D560" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E560" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F560" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G560" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H560" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I560" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J560" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K560" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L560" s="5" t="n"/>
+      <c r="M560" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N560" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O560" s="5" t="n">
+        <v>15.89</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_001</t>
+        </is>
+      </c>
+      <c r="B561" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C561" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E561" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G561" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H561" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I561" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J561" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K561" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L561" s="5" t="n"/>
+      <c r="M561" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N561" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O561" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_001</t>
+        </is>
+      </c>
+      <c r="B562" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C562" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D562" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E562" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F562" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G562" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H562" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I562" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J562" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K562" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L562" s="5" t="n"/>
+      <c r="M562" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N562" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O562" s="5" t="n">
+        <v>15.93</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_001</t>
+        </is>
+      </c>
+      <c r="B563" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E563" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F563" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G563" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H563" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I563" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J563" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K563" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L563" s="5" t="n"/>
+      <c r="M563" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N563" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O563" s="5" t="n">
+        <v>55.99</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_001</t>
+        </is>
+      </c>
+      <c r="B564" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C564" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E564" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F564" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G564" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H564" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I564" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J564" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K564" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L564" s="5" t="n"/>
+      <c r="M564" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N564" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O564" s="5" t="n">
+        <v>81.94</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_001</t>
+        </is>
+      </c>
+      <c r="B565" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E565" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G565" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H565" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I565" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J565" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K565" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L565" s="5" t="n"/>
+      <c r="M565" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N565" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O565" s="5" t="n">
+        <v>65.08</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3_002</t>
+        </is>
+      </c>
+      <c r="B566" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C566" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="D566" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E566" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F566" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G566" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H566" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I566" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J566" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K566" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L566" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'size', 'value': '&lt;420', 'direction': 'incoming', 'mode': 'list'}</t>
+        </is>
+      </c>
+      <c r="M566" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N566" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O566" s="5" t="n">
+        <v>17.58</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3_002</t>
+        </is>
+      </c>
+      <c r="B567" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C567" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="D567" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E567" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F567" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G567" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H567" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I567" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J567" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K567" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L567" s="5" t="n"/>
+      <c r="M567" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N567" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O567" s="5" t="n">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3_002</t>
+        </is>
+      </c>
+      <c r="B568" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C568" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="D568" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E568" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F568" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G568" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H568" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I568" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J568" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K568" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L568" s="5" t="n"/>
+      <c r="M568" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N568" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O568" s="5" t="n">
+        <v>10.79</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3_003</t>
+        </is>
+      </c>
+      <c r="B569" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C569" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="D569" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E569" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F569" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G569" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H569" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I569" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J569" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K569" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L569" s="5" t="n"/>
+      <c r="M569" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N569" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O569" s="5" t="n">
+        <v>21.11</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3_003</t>
+        </is>
+      </c>
+      <c r="B570" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C570" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="D570" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E570" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F570" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G570" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H570" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I570" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J570" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K570" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L570" s="5" t="n"/>
+      <c r="M570" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N570" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O570" s="5" t="n">
+        <v>14.57</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3_003</t>
+        </is>
+      </c>
+      <c r="B571" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="D571" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E571" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F571" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G571" s="5" t="inlineStr">
+        <is>
+          <t>filter_numeric_kg3</t>
+        </is>
+      </c>
+      <c r="H571" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I571" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J571" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K571" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L571" s="5" t="n"/>
+      <c r="M571" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N571" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O571" s="5" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B572" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C572" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D572" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E572" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F572" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G572" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H572" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I572" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J572" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K572" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L572" s="5" t="n"/>
+      <c r="M572" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N572" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O572" s="5" t="n">
+        <v>17.11</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B573" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C573" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D573" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E573" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F573" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G573" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H573" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I573" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J573" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K573" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L573" s="5" t="n"/>
+      <c r="M573" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N573" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O573" s="5" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B574" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C574" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D574" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E574" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F574" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G574" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H574" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I574" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J574" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K574" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L574" s="5" t="n"/>
+      <c r="M574" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N574" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O574" s="5" t="n">
+        <v>13.03</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B575" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C575" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D575" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E575" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G575" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H575" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I575" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J575" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K575" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L575" s="5" t="n"/>
+      <c r="M575" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N575" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O575" s="5" t="n">
+        <v>12.46</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B576" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C576" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D576" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E576" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F576" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G576" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H576" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I576" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J576" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K576" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L576" s="5" t="n"/>
+      <c r="M576" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N576" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O576" s="5" t="n">
+        <v>12.24</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B577" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C577" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D577" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E577" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F577" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G577" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H577" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I577" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J577" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K577" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L577" s="5" t="n"/>
+      <c r="M577" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N577" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O577" s="5" t="n">
+        <v>13.66</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B578" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C578" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D578" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E578" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F578" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G578" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H578" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I578" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J578" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K578" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L578" s="5" t="n"/>
+      <c r="M578" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N578" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O578" s="5" t="n">
+        <v>12.81</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B579" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C579" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D579" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E579" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F579" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G579" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H579" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I579" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J579" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K579" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L579" s="5" t="n"/>
+      <c r="M579" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N579" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O579" s="5" t="n">
+        <v>13.71</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_010</t>
+        </is>
+      </c>
+      <c r="B580" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C580" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D580" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E580" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F580" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G580" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H580" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I580" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J580" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K580" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L580" s="5" t="n"/>
+      <c r="M580" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N580" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O580" s="5" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B581" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C581" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E581" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F581" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G581" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H581" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I581" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J581" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K581" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L581" s="5" t="n"/>
+      <c r="M581" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N581" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O581" s="5" t="n">
+        <v>17.15</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B582" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C582" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D582" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E582" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F582" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G582" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H582" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I582" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J582" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K582" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L582" s="5" t="n"/>
+      <c r="M582" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N582" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O582" s="5" t="n">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B583" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C583" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D583" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E583" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F583" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G583" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H583" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I583" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J583" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K583" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L583" s="5" t="n"/>
+      <c r="M583" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N583" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O583" s="5" t="n">
+        <v>12.41</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B584" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C584" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D584" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E584" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F584" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G584" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H584" s="5" t="inlineStr">
+        <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="I584" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J584" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K584" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L584" s="5" t="n"/>
+      <c r="M584" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N584" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O584" s="5" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B585" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C585" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D585" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E585" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F585" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G585" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H585" s="5" t="inlineStr">
+        <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="I585" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J585" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K585" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L585" s="5" t="n"/>
+      <c r="M585" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N585" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O585" s="5" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B586" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C586" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D586" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E586" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F586" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G586" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H586" s="5" t="inlineStr">
+        <is>
+          <t>ask_query</t>
+        </is>
+      </c>
+      <c r="I586" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J586" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K586" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L586" s="5" t="n"/>
+      <c r="M586" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N586" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O586" s="5" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B587" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C587" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D587" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E587" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F587" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G587" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H587" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I587" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J587" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K587" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L587" s="5" t="n"/>
+      <c r="M587" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N587" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O587" s="5" t="n">
+        <v>13.81</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B588" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C588" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D588" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E588" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F588" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G588" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H588" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I588" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J588" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K588" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L588" s="5" t="n"/>
+      <c r="M588" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N588" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O588" s="5" t="n">
+        <v>14.08</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_011</t>
+        </is>
+      </c>
+      <c r="B589" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C589" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D589" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E589" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F589" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G589" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H589" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I589" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J589" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K589" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L589" s="5" t="n"/>
+      <c r="M589" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N589" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O589" s="5" t="n">
+        <v>14.18</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B590" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C590" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D590" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E590" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F590" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G590" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H590" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I590" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J590" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K590" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L590" s="5" t="n"/>
+      <c r="M590" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N590" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O590" s="5" t="n">
+        <v>15.67</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B591" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C591" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D591" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E591" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F591" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G591" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H591" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I591" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J591" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K591" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L591" s="5" t="n"/>
+      <c r="M591" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N591" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O591" s="5" t="n">
+        <v>12.41</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B592" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C592" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D592" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E592" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F592" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G592" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H592" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I592" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J592" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K592" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L592" s="5" t="n"/>
+      <c r="M592" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N592" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O592" s="5" t="n">
+        <v>13.05</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B593" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D593" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E593" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F593" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G593" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H593" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I593" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J593" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K593" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L593" s="5" t="n"/>
+      <c r="M593" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N593" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O593" s="5" t="n">
+        <v>18.37</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B594" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C594" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D594" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E594" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F594" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G594" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H594" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I594" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J594" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K594" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L594" s="5" t="n"/>
+      <c r="M594" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N594" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O594" s="5" t="n">
+        <v>13.97</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B595" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D595" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E595" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F595" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G595" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H595" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I595" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J595" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K595" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L595" s="5" t="n"/>
+      <c r="M595" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N595" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O595" s="5" t="n">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B596" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C596" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D596" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E596" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F596" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G596" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H596" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I596" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J596" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K596" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L596" s="5" t="n"/>
+      <c r="M596" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N596" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O596" s="5" t="n">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B597" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C597" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D597" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E597" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F597" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G597" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H597" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I597" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J597" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K597" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L597" s="5" t="n"/>
+      <c r="M597" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N597" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O597" s="5" t="n">
+        <v>13.79</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_012</t>
+        </is>
+      </c>
+      <c r="B598" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C598" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D598" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E598" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F598" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G598" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H598" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I598" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J598" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K598" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L598" s="5" t="n"/>
+      <c r="M598" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N598" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O598" s="5" t="n">
+        <v>13.97</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C599" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D599" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E599" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F599" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G599" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H599" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I599" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J599" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K599" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L599" s="5" t="n"/>
+      <c r="M599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N599" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O599" s="5" t="n">
+        <v>15.89</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C600" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D600" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E600" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F600" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G600" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H600" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I600" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J600" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K600" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L600" s="5" t="n"/>
+      <c r="M600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N600" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O600" s="5" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B601" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C601" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D601" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E601" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F601" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G601" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H601" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I601" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J601" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K601" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L601" s="5" t="n"/>
+      <c r="M601" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N601" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O601" s="5" t="n">
+        <v>12.59</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B602" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C602" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D602" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E602" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F602" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G602" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H602" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I602" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J602" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K602" s="5" t="inlineStr">
+        <is>
+          <t>no_results</t>
+        </is>
+      </c>
+      <c r="L602" s="5" t="n"/>
+      <c r="M602" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N602" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O602" s="5" t="n">
+        <v>16.74</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B603" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C603" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D603" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E603" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F603" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G603" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H603" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I603" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J603" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K603" s="5" t="inlineStr">
+        <is>
+          <t>no_results</t>
+        </is>
+      </c>
+      <c r="L603" s="5" t="n"/>
+      <c r="M603" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N603" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O603" s="5" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B604" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C604" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D604" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E604" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F604" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G604" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H604" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I604" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J604" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K604" s="5" t="inlineStr">
+        <is>
+          <t>no_results</t>
+        </is>
+      </c>
+      <c r="L604" s="5" t="n"/>
+      <c r="M604" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N604" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O604" s="5" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B605" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C605" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D605" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E605" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F605" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G605" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H605" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I605" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J605" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K605" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L605" s="5" t="n"/>
+      <c r="M605" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N605" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O605" s="5" t="n">
+        <v>17.85</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B606" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C606" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D606" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E606" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F606" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G606" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H606" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I606" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J606" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K606" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L606" s="5" t="n"/>
+      <c r="M606" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N606" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O606" s="5" t="n">
+        <v>13.07</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3_013</t>
+        </is>
+      </c>
+      <c r="B607" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C607" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="D607" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E607" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F607" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G607" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="H607" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I607" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J607" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K607" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L607" s="5" t="n"/>
+      <c r="M607" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N607" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O607" s="5" t="n">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1_001</t>
+        </is>
+      </c>
+      <c r="B608" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C608" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1</t>
+        </is>
+      </c>
+      <c r="D608" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E608" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F608" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G608" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H608" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I608" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J608" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K608" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L608" s="5" t="n"/>
+      <c r="M608" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N608" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="O608" s="5" t="n">
+        <v>16.73</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1_001</t>
+        </is>
+      </c>
+      <c r="B609" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C609" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1</t>
+        </is>
+      </c>
+      <c r="D609" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E609" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F609" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G609" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H609" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I609" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J609" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K609" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L609" s="5" t="n"/>
+      <c r="M609" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N609" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="O609" s="5" t="n">
+        <v>14.66</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1_001</t>
+        </is>
+      </c>
+      <c r="B610" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C610" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg1</t>
+        </is>
+      </c>
+      <c r="D610" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E610" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F610" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G610" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H610" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I610" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J610" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K610" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L610" s="5" t="n"/>
+      <c r="M610" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N610" s="5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="O610" s="5" t="n">
+        <v>11.73</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B611" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C611" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D611" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E611" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F611" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G611" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H611" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I611" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J611" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K611" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L611" s="5" t="n"/>
+      <c r="M611" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N611" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O611" s="5" t="n">
+        <v>13.44</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B612" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C612" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D612" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E612" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F612" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G612" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H612" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I612" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J612" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K612" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L612" s="5" t="n"/>
+      <c r="M612" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N612" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O612" s="5" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B613" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C613" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D613" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E613" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F613" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G613" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H613" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I613" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J613" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K613" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L613" s="5" t="n"/>
+      <c r="M613" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N613" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O613" s="5" t="n">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B614" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C614" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D614" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E614" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F614" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G614" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H614" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I614" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J614" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K614" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L614" s="5" t="n"/>
+      <c r="M614" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N614" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O614" s="5" t="n">
+        <v>13.87</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B615" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C615" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D615" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E615" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F615" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G615" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H615" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I615" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J615" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K615" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L615" s="5" t="n"/>
+      <c r="M615" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N615" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O615" s="5" t="n">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B616" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C616" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D616" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E616" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F616" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G616" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I616" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J616" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K616" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L616" s="5" t="n"/>
+      <c r="M616" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N616" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O616" s="5" t="n">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B617" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D617" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E617" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F617" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G617" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H617" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I617" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J617" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K617" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L617" s="5" t="n"/>
+      <c r="M617" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N617" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O617" s="5" t="n">
+        <v>13.66</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B618" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C618" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D618" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E618" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F618" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G618" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H618" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I618" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J618" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K618" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L618" s="5" t="n"/>
+      <c r="M618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N618" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O618" s="5" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B619" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D619" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E619" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F619" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G619" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H619" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I619" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J619" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K619" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L619" s="5" t="n"/>
+      <c r="M619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N619" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O619" s="5" t="n">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_002</t>
+        </is>
+      </c>
+      <c r="B620" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C620" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D620" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E620" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F620" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G620" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H620" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I620" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J620" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K620" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L620" s="5" t="n"/>
+      <c r="M620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N620" s="5" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="O620" s="5" t="n">
+        <v>38.68</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_002</t>
+        </is>
+      </c>
+      <c r="B621" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C621" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D621" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E621" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F621" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G621" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H621" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I621" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J621" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K621" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L621" s="5" t="n"/>
+      <c r="M621" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N621" s="5" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="O621" s="5" t="n">
+        <v>12.81</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_002</t>
+        </is>
+      </c>
+      <c r="B622" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C622" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D622" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E622" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F622" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G622" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H622" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I622" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J622" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K622" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L622" s="5" t="n"/>
+      <c r="M622" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N622" s="5" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="O622" s="5" t="n">
+        <v>12.27</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_002</t>
+        </is>
+      </c>
+      <c r="B623" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C623" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D623" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E623" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F623" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G623" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H623" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I623" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J623" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K623" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L623" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'department', 'property': 'memberOf', 'function': 'COUNT'}</t>
+        </is>
+      </c>
+      <c r="M623" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N623" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O623" s="5" t="n">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_002</t>
+        </is>
+      </c>
+      <c r="B624" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C624" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D624" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E624" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G624" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H624" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I624" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J624" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K624" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L624" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'department', 'property': 'memberOf', 'function': 'COUNT'}</t>
+        </is>
+      </c>
+      <c r="M624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O624" s="5" t="n">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_002</t>
+        </is>
+      </c>
+      <c r="B625" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C625" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D625" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E625" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F625" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G625" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H625" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I625" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J625" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K625" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L625" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'memberOf', 'function': 'COUNT'}</t>
+        </is>
+      </c>
+      <c r="M625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O625" s="5" t="n">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_002</t>
+        </is>
+      </c>
+      <c r="B626" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C626" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D626" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E626" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F626" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G626" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H626" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I626" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J626" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K626" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L626" s="5" t="n"/>
+      <c r="M626" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N626" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O626" s="5" t="n">
+        <v>28.86</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_002</t>
+        </is>
+      </c>
+      <c r="B627" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C627" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D627" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E627" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F627" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G627" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H627" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I627" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J627" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K627" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L627" s="5" t="n"/>
+      <c r="M627" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N627" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O627" s="5" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_002</t>
+        </is>
+      </c>
+      <c r="B628" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C628" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D628" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E628" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F628" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G628" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H628" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I628" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J628" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K628" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L628" s="5" t="n"/>
+      <c r="M628" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N628" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O628" s="5" t="n">
+        <v>13.68</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_003</t>
+        </is>
+      </c>
+      <c r="B629" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C629" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D629" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E629" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F629" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G629" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H629" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I629" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J629" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K629" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L629" s="5" t="n"/>
+      <c r="M629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O629" s="5" t="n">
+        <v>31.71</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_003</t>
+        </is>
+      </c>
+      <c r="B630" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C630" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D630" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E630" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F630" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G630" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I630" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J630" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K630" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L630" s="5" t="n"/>
+      <c r="M630" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N630" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O630" s="5" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_003</t>
+        </is>
+      </c>
+      <c r="B631" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C631" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D631" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E631" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F631" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G631" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H631" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I631" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J631" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K631" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L631" s="5" t="n"/>
+      <c r="M631" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N631" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O631" s="5" t="n">
+        <v>17.69</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_002</t>
+        </is>
+      </c>
+      <c r="B632" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C632" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D632" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E632" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F632" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G632" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H632" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I632" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J632" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K632" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L632" s="5" t="n"/>
+      <c r="M632" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N632" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O632" s="5" t="n">
+        <v>66.22</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_002</t>
+        </is>
+      </c>
+      <c r="B633" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C633" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D633" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E633" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F633" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G633" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H633" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I633" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J633" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K633" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L633" s="5" t="n"/>
+      <c r="M633" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N633" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O633" s="5" t="n">
+        <v>58.65</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_002</t>
+        </is>
+      </c>
+      <c r="B634" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C634" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D634" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E634" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F634" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G634" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H634" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I634" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J634" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K634" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L634" s="5" t="n"/>
+      <c r="M634" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N634" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O634" s="5" t="n">
+        <v>55.44</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments_002</t>
+        </is>
+      </c>
+      <c r="B635" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C635" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="D635" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E635" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F635" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G635" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="H635" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I635" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J635" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K635" s="5" t="inlineStr">
+        <is>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L635" s="5" t="n"/>
+      <c r="M635" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N635" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O635" s="5" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments_002</t>
+        </is>
+      </c>
+      <c r="B636" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C636" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="D636" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E636" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F636" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G636" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="H636" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I636" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J636" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K636" s="5" t="inlineStr">
+        <is>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L636" s="5" t="n"/>
+      <c r="M636" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N636" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O636" s="5" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments_002</t>
+        </is>
+      </c>
+      <c r="B637" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C637" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="D637" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E637" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F637" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G637" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="H637" s="5" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="I637" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J637" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K637" s="5" t="inlineStr">
+        <is>
+          <t>routing_miss</t>
+        </is>
+      </c>
+      <c r="L637" s="5" t="n"/>
+      <c r="M637" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N637" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O637" s="5" t="n">
+        <v>7.93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O541"/>
+  <autoFilter ref="A1:O637"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Raw" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$637</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$610</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,27 +551,27 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Raw!E2:E637,"en")</f>
+        <f>COUNTIF(Raw!E2:E610,"en")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"en",Raw!I2:I637,TRUE)/COUNTIF(Raw!E2:E637,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"en",Raw!I2:I610,TRUE)/COUNTIF(Raw!E2:E610,"en"),"")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"en",Raw!K2:K637,"success")/COUNTIF(Raw!E2:E637,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"en",Raw!K2:K610,"success")/COUNTIF(Raw!E2:E610,"en"),"")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"en",Raw!J2:J637,TRUE)/COUNTIF(Raw!E2:E637,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"en",Raw!J2:J610,TRUE)/COUNTIF(Raw!E2:E610,"en"),"")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!E2:E637,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!E2:E610,"en"),"")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!E2:E637,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!E2:E610,"en"),"")</f>
         <v/>
       </c>
     </row>
@@ -582,27 +582,27 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Raw!E2:E637,"fr")</f>
+        <f>COUNTIF(Raw!E2:E610,"fr")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"fr",Raw!I2:I637,TRUE)/COUNTIF(Raw!E2:E637,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"fr",Raw!I2:I610,TRUE)/COUNTIF(Raw!E2:E610,"fr"),"")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"fr",Raw!K2:K637,"success")/COUNTIF(Raw!E2:E637,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"fr",Raw!K2:K610,"success")/COUNTIF(Raw!E2:E610,"fr"),"")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"fr",Raw!J2:J637,TRUE)/COUNTIF(Raw!E2:E637,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"fr",Raw!J2:J610,TRUE)/COUNTIF(Raw!E2:E610,"fr"),"")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!E2:E637,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!E2:E610,"fr"),"")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!E2:E637,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!E2:E610,"fr"),"")</f>
         <v/>
       </c>
     </row>
@@ -613,27 +613,27 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Raw!E2:E637,"ar")</f>
+        <f>COUNTIF(Raw!E2:E610,"ar")</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"ar",Raw!I2:I637,TRUE)/COUNTIF(Raw!E2:E637,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"ar",Raw!I2:I610,TRUE)/COUNTIF(Raw!E2:E610,"ar"),"")</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"ar",Raw!K2:K637,"success")/COUNTIF(Raw!E2:E637,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"ar",Raw!K2:K610,"success")/COUNTIF(Raw!E2:E610,"ar"),"")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E637,"ar",Raw!J2:J637,TRUE)/COUNTIF(Raw!E2:E637,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E610,"ar",Raw!J2:J610,TRUE)/COUNTIF(Raw!E2:E610,"ar"),"")</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!E2:E637,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!E2:E610,"ar"),"")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!E2:E637,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!E2:E610,"ar"),"")</f>
         <v/>
       </c>
     </row>
@@ -688,27 +688,27 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Raw!F2:F637,"zero-shot")</f>
+        <f>COUNTIF(Raw!F2:F610,"zero-shot")</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"zero-shot",Raw!I2:I637,TRUE)/COUNTIF(Raw!F2:F637,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"zero-shot",Raw!I2:I610,TRUE)/COUNTIF(Raw!F2:F610,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"zero-shot",Raw!K2:K637,"success")/COUNTIF(Raw!F2:F637,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"zero-shot",Raw!K2:K610,"success")/COUNTIF(Raw!F2:F610,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"zero-shot",Raw!J2:J637,TRUE)/COUNTIF(Raw!F2:F637,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"zero-shot",Raw!J2:J610,TRUE)/COUNTIF(Raw!F2:F610,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!F2:F637,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!F2:F610,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!F2:F637,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!F2:F610,"zero-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -719,27 +719,27 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Raw!F2:F637,"few-shot")</f>
+        <f>COUNTIF(Raw!F2:F610,"few-shot")</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"few-shot",Raw!I2:I637,TRUE)/COUNTIF(Raw!F2:F637,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"few-shot",Raw!I2:I610,TRUE)/COUNTIF(Raw!F2:F610,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"few-shot",Raw!K2:K637,"success")/COUNTIF(Raw!F2:F637,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"few-shot",Raw!K2:K610,"success")/COUNTIF(Raw!F2:F610,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"few-shot",Raw!J2:J637,TRUE)/COUNTIF(Raw!F2:F637,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"few-shot",Raw!J2:J610,TRUE)/COUNTIF(Raw!F2:F610,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!F2:F637,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!F2:F610,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!F2:F637,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!F2:F610,"few-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -750,27 +750,27 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF(Raw!F2:F637,"cot")</f>
+        <f>COUNTIF(Raw!F2:F610,"cot")</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"cot",Raw!I2:I637,TRUE)/COUNTIF(Raw!F2:F637,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"cot",Raw!I2:I610,TRUE)/COUNTIF(Raw!F2:F610,"cot"),"")</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"cot",Raw!K2:K637,"success")/COUNTIF(Raw!F2:F637,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"cot",Raw!K2:K610,"success")/COUNTIF(Raw!F2:F610,"cot"),"")</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F637,"cot",Raw!J2:J637,TRUE)/COUNTIF(Raw!F2:F637,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F610,"cot",Raw!J2:J610,TRUE)/COUNTIF(Raw!F2:F610,"cot"),"")</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!F2:F637,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!F2:F610,"cot"),"")</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!F2:F637,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!F2:F610,"cot"),"")</f>
         <v/>
       </c>
     </row>
@@ -823,27 +823,27 @@
         <v>1</v>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Raw!B2:B637,"1")</f>
+        <f>COUNTIF(Raw!B2:B610,"1")</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"1",Raw!I2:I637,TRUE)/COUNTIF(Raw!B2:B637,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"1",Raw!I2:I610,TRUE)/COUNTIF(Raw!B2:B610,"1"),"")</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"1",Raw!K2:K637,"success")/COUNTIF(Raw!B2:B637,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"1",Raw!K2:K610,"success")/COUNTIF(Raw!B2:B610,"1"),"")</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"1",Raw!J2:J637,TRUE)/COUNTIF(Raw!B2:B637,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"1",Raw!J2:J610,TRUE)/COUNTIF(Raw!B2:B610,"1"),"")</f>
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!B2:B637,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!B2:B610,"1"),"")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!B2:B637,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!B2:B610,"1"),"")</f>
         <v/>
       </c>
     </row>
@@ -852,27 +852,27 @@
         <v>2</v>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Raw!B2:B637,"2")</f>
+        <f>COUNTIF(Raw!B2:B610,"2")</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"2",Raw!I2:I637,TRUE)/COUNTIF(Raw!B2:B637,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"2",Raw!I2:I610,TRUE)/COUNTIF(Raw!B2:B610,"2"),"")</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"2",Raw!K2:K637,"success")/COUNTIF(Raw!B2:B637,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"2",Raw!K2:K610,"success")/COUNTIF(Raw!B2:B610,"2"),"")</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"2",Raw!J2:J637,TRUE)/COUNTIF(Raw!B2:B637,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"2",Raw!J2:J610,TRUE)/COUNTIF(Raw!B2:B610,"2"),"")</f>
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!B2:B637,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!B2:B610,"2"),"")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!B2:B637,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!B2:B610,"2"),"")</f>
         <v/>
       </c>
     </row>
@@ -881,27 +881,27 @@
         <v>3</v>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Raw!B2:B637,"3")</f>
+        <f>COUNTIF(Raw!B2:B610,"3")</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"3",Raw!I2:I637,TRUE)/COUNTIF(Raw!B2:B637,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"3",Raw!I2:I610,TRUE)/COUNTIF(Raw!B2:B610,"3"),"")</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"3",Raw!K2:K637,"success")/COUNTIF(Raw!B2:B637,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"3",Raw!K2:K610,"success")/COUNTIF(Raw!B2:B610,"3"),"")</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B637,"3",Raw!J2:J637,TRUE)/COUNTIF(Raw!B2:B637,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B610,"3",Raw!J2:J610,TRUE)/COUNTIF(Raw!B2:B610,"3"),"")</f>
         <v/>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!B2:B637,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!B2:B610,"3"),"")</f>
         <v/>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!B2:B637,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!B2:B610,"3"),"")</f>
         <v/>
       </c>
     </row>
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF(Raw!C2:C637,"single_kg1")</f>
+        <f>COUNTIF(Raw!C2:C610,"single_kg1")</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"single_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -987,27 +987,27 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF(Raw!C2:C637,"single_kg2")</f>
+        <f>COUNTIF(Raw!C2:C610,"single_kg2")</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"single_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF(Raw!C2:C637,"single_kg3")</f>
+        <f>COUNTIF(Raw!C2:C610,"single_kg3")</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"single_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"single_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"single_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"single_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1049,27 +1049,27 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Raw!C2:C637,"cross_kg")</f>
+        <f>COUNTIF(Raw!C2:C610,"cross_kg")</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"cross_kg",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"cross_kg",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"cross_kg",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"cross_kg",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"cross_kg",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"cross_kg",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"cross_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1080,27 +1080,27 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Raw!C2:C637,"open_kg")</f>
+        <f>COUNTIF(Raw!C2:C610,"open_kg")</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"open_kg",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"open_kg",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"open_kg",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"open_kg",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"open_kg",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"open_kg",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="G28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"open_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1111,27 +1111,27 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Raw!C2:C637,"count_kg1")</f>
+        <f>COUNTIF(Raw!C2:C610,"count_kg1")</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="F29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="G29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"count_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1142,27 +1142,27 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF(Raw!C2:C637,"count_kg2")</f>
+        <f>COUNTIF(Raw!C2:C610,"count_kg2")</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"count_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"count_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="G30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"count_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"count_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF(Raw!C2:C637,"count_kg3")</f>
+        <f>COUNTIF(Raw!C2:C610,"count_kg3")</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"count_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="F31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"count_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="G31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"count_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"count_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1204,27 +1204,27 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF(Raw!C2:C637,"filter_numeric_kg1")</f>
+        <f>COUNTIF(Raw!C2:C610,"filter_numeric_kg1")</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="F32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF(Raw!C2:C637,"filter_numeric_kg2")</f>
+        <f>COUNTIF(Raw!C2:C610,"filter_numeric_kg2")</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="F33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1266,27 +1266,27 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF(Raw!C2:C637,"filter_numeric_kg3")</f>
+        <f>COUNTIF(Raw!C2:C610,"filter_numeric_kg3")</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_numeric_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="F34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1297,27 +1297,27 @@
         </is>
       </c>
       <c r="B35" s="5">
-        <f>COUNTIF(Raw!C2:C637,"filter_string_kg2")</f>
+        <f>COUNTIF(Raw!C2:C610,"filter_string_kg2")</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="F35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_string_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="B36" s="5">
-        <f>COUNTIF(Raw!C2:C637,"filter_string_kg3")</f>
+        <f>COUNTIF(Raw!C2:C610,"filter_string_kg3")</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"filter_string_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="F36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"filter_string_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"filter_string_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_string_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1359,27 +1359,27 @@
         </is>
       </c>
       <c r="B37" s="5">
-        <f>COUNTIF(Raw!C2:C637,"ranking_kg1")</f>
+        <f>COUNTIF(Raw!C2:C610,"ranking_kg1")</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ranking_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="F37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ranking_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ranking_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ranking_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1390,27 +1390,27 @@
         </is>
       </c>
       <c r="B38" s="5">
-        <f>COUNTIF(Raw!C2:C637,"ranking_kg2")</f>
+        <f>COUNTIF(Raw!C2:C610,"ranking_kg2")</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="F38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="G38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ranking_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1421,27 +1421,27 @@
         </is>
       </c>
       <c r="B39" s="5">
-        <f>COUNTIF(Raw!C2:C637,"ranking_kg3")</f>
+        <f>COUNTIF(Raw!C2:C610,"ranking_kg3")</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ranking_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ranking_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ranking_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="F39" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ranking_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="G39" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ranking_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ranking_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1452,27 +1452,27 @@
         </is>
       </c>
       <c r="B40" s="5">
-        <f>COUNTIF(Raw!C2:C637,"compare_two_airports")</f>
+        <f>COUNTIF(Raw!C2:C610,"compare_two_airports")</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_airports",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_airports",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="D40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_airports",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_airports",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="E40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_airports",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_airports",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="F40" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="G40" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"compare_two_airports"),"")</f>
         <v/>
       </c>
     </row>
@@ -1483,27 +1483,27 @@
         </is>
       </c>
       <c r="B41" s="5">
-        <f>COUNTIF(Raw!C2:C637,"compare_two_flights")</f>
+        <f>COUNTIF(Raw!C2:C610,"compare_two_flights")</f>
         <v/>
       </c>
       <c r="C41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_flights",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_flights"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_flights",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="D41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_flights",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"compare_two_flights"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_flights",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="E41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_flights",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_flights"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_flights",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="F41" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"compare_two_flights"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="G41" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"compare_two_flights"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"compare_two_flights"),"")</f>
         <v/>
       </c>
     </row>
@@ -1514,27 +1514,27 @@
         </is>
       </c>
       <c r="B42" s="5">
-        <f>COUNTIF(Raw!C2:C637,"compare_two_departments")</f>
+        <f>COUNTIF(Raw!C2:C610,"compare_two_departments")</f>
         <v/>
       </c>
       <c r="C42" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_departments",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_departments"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_departments",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="D42" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_departments",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"compare_two_departments"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_departments",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="E42" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"compare_two_departments",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"compare_two_departments"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_departments",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="F42" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"compare_two_departments"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="G42" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"compare_two_departments"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"compare_two_departments"),"")</f>
         <v/>
       </c>
     </row>
@@ -1545,27 +1545,27 @@
         </is>
       </c>
       <c r="B43" s="5">
-        <f>COUNTIF(Raw!C2:C637,"group_aggregate_kg1")</f>
+        <f>COUNTIF(Raw!C2:C610,"group_aggregate_kg1")</f>
         <v/>
       </c>
       <c r="C43" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg1",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="D43" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg1",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="E43" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg1",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="F43" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="G43" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1576,27 +1576,27 @@
         </is>
       </c>
       <c r="B44" s="5">
-        <f>COUNTIF(Raw!C2:C637,"group_aggregate_kg2")</f>
+        <f>COUNTIF(Raw!C2:C610,"group_aggregate_kg2")</f>
         <v/>
       </c>
       <c r="C44" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg2",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="D44" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg2",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="E44" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg2",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="F44" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="G44" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1607,27 +1607,27 @@
         </is>
       </c>
       <c r="B45" s="5">
-        <f>COUNTIF(Raw!C2:C637,"group_aggregate_kg3")</f>
+        <f>COUNTIF(Raw!C2:C610,"group_aggregate_kg3")</f>
         <v/>
       </c>
       <c r="C45" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg3",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="D45" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg3",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="E45" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"group_aggregate_kg3",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="F45" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="G45" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1638,27 +1638,27 @@
         </is>
       </c>
       <c r="B46" s="5">
-        <f>COUNTIF(Raw!C2:C637,"out_of_scope")</f>
+        <f>COUNTIF(Raw!C2:C610,"out_of_scope")</f>
         <v/>
       </c>
       <c r="C46" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"out_of_scope",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"out_of_scope",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="D46" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"out_of_scope",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"out_of_scope",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="E46" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"out_of_scope",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"out_of_scope",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="F46" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="G46" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"out_of_scope"),"")</f>
         <v/>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
         </is>
       </c>
       <c r="B47" s="5">
-        <f>COUNTIF(Raw!C2:C637,"ask_query")</f>
+        <f>COUNTIF(Raw!C2:C610,"ask_query")</f>
         <v/>
       </c>
       <c r="C47" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ask_query",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ask_query",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="D47" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ask_query",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ask_query",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="E47" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ask_query",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ask_query",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="F47" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="G47" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ask_query"),"")</f>
         <v/>
       </c>
     </row>
@@ -1700,27 +1700,27 @@
         </is>
       </c>
       <c r="B48" s="5">
-        <f>COUNTIF(Raw!C2:C637,"typo_fuzzy")</f>
+        <f>COUNTIF(Raw!C2:C610,"typo_fuzzy")</f>
         <v/>
       </c>
       <c r="C48" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"typo_fuzzy",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"typo_fuzzy",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="D48" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"typo_fuzzy",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"typo_fuzzy",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="E48" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"typo_fuzzy",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"typo_fuzzy",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="F48" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="G48" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"typo_fuzzy"),"")</f>
         <v/>
       </c>
     </row>
@@ -1731,27 +1731,27 @@
         </is>
       </c>
       <c r="B49" s="5">
-        <f>COUNTIF(Raw!C2:C637,"multilingual_edge")</f>
+        <f>COUNTIF(Raw!C2:C610,"multilingual_edge")</f>
         <v/>
       </c>
       <c r="C49" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multilingual_edge",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multilingual_edge",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="D49" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multilingual_edge",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multilingual_edge",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="E49" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multilingual_edge",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multilingual_edge",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="F49" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="G49" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"multilingual_edge"),"")</f>
         <v/>
       </c>
     </row>
@@ -1762,27 +1762,27 @@
         </is>
       </c>
       <c r="B50" s="5">
-        <f>COUNTIF(Raw!C2:C637,"property_ambiguity")</f>
+        <f>COUNTIF(Raw!C2:C610,"property_ambiguity")</f>
         <v/>
       </c>
       <c r="C50" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"property_ambiguity",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"property_ambiguity",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="D50" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"property_ambiguity",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"property_ambiguity",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="E50" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"property_ambiguity",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"property_ambiguity",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="F50" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="G50" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"property_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1793,27 +1793,27 @@
         </is>
       </c>
       <c r="B51" s="5">
-        <f>COUNTIF(Raw!C2:C637,"ghost_property")</f>
+        <f>COUNTIF(Raw!C2:C610,"ghost_property")</f>
         <v/>
       </c>
       <c r="C51" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ghost_property",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"ghost_property"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ghost_property",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="D51" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ghost_property",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"ghost_property"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ghost_property",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="E51" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"ghost_property",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"ghost_property"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ghost_property",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="F51" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"ghost_property"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="G51" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"ghost_property"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ghost_property"),"")</f>
         <v/>
       </c>
     </row>
@@ -1824,27 +1824,27 @@
         </is>
       </c>
       <c r="B52" s="5">
-        <f>COUNTIF(Raw!C2:C637,"multi_value_ambiguity")</f>
+        <f>COUNTIF(Raw!C2:C610,"multi_value_ambiguity")</f>
         <v/>
       </c>
       <c r="C52" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multi_value_ambiguity",Raw!I2:I637,TRUE)/COUNTIF(Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multi_value_ambiguity",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="D52" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multi_value_ambiguity",Raw!K2:K637,"success")/COUNTIF(Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multi_value_ambiguity",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="E52" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C637,"multi_value_ambiguity",Raw!J2:J637,TRUE)/COUNTIF(Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multi_value_ambiguity",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="F52" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M637,Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="G52" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N637,Raw!C2:C637,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O637"/>
+  <dimension ref="A1:O610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36482,7 +36482,7 @@
     <row r="569">
       <c r="A569" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3_003</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
@@ -36490,7 +36490,7 @@
       </c>
       <c r="C569" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D569" s="5" t="inlineStr">
@@ -36510,40 +36510,40 @@
       </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H569" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I569" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J569" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K569" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L569" s="5" t="n"/>
       <c r="M569" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N569" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O569" s="5" t="n">
-        <v>21.11</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3_003</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B570" s="5" t="n">
@@ -36551,7 +36551,7 @@
       </c>
       <c r="C570" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D570" s="5" t="inlineStr">
@@ -36561,50 +36561,50 @@
       </c>
       <c r="E570" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F570" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G570" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H570" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I570" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J570" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K570" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L570" s="5" t="n"/>
       <c r="M570" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N570" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O570" s="5" t="n">
-        <v>14.57</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3_003</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -36612,7 +36612,7 @@
       </c>
       <c r="C571" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D571" s="5" t="inlineStr">
@@ -36622,44 +36622,44 @@
       </c>
       <c r="E571" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F571" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G571" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H571" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I571" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J571" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K571" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L571" s="5" t="n"/>
       <c r="M571" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N571" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O571" s="5" t="n">
-        <v>11.55</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="572">
@@ -36683,7 +36683,7 @@
       </c>
       <c r="E572" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F572" s="5" t="inlineStr">
@@ -36720,7 +36720,7 @@
         <v>1</v>
       </c>
       <c r="O572" s="5" t="n">
-        <v>17.11</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="573">
@@ -36744,7 +36744,7 @@
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F573" s="5" t="inlineStr">
@@ -36781,7 +36781,7 @@
         <v>1</v>
       </c>
       <c r="O573" s="5" t="n">
-        <v>12.6</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="574">
@@ -36805,7 +36805,7 @@
       </c>
       <c r="E574" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F574" s="5" t="inlineStr">
@@ -36842,7 +36842,7 @@
         <v>1</v>
       </c>
       <c r="O574" s="5" t="n">
-        <v>13.03</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="575">
@@ -36866,7 +36866,7 @@
       </c>
       <c r="E575" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F575" s="5" t="inlineStr">
@@ -36903,7 +36903,7 @@
         <v>1</v>
       </c>
       <c r="O575" s="5" t="n">
-        <v>12.46</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="576">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="E576" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F576" s="5" t="inlineStr">
@@ -36964,7 +36964,7 @@
         <v>1</v>
       </c>
       <c r="O576" s="5" t="n">
-        <v>12.24</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="577">
@@ -36988,7 +36988,7 @@
       </c>
       <c r="E577" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F577" s="5" t="inlineStr">
@@ -37025,13 +37025,13 @@
         <v>1</v>
       </c>
       <c r="O577" s="5" t="n">
-        <v>13.66</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="E578" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F578" s="5" t="inlineStr">
@@ -37086,13 +37086,13 @@
         <v>1</v>
       </c>
       <c r="O578" s="5" t="n">
-        <v>12.81</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
@@ -37110,7 +37110,7 @@
       </c>
       <c r="E579" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F579" s="5" t="inlineStr">
@@ -37147,13 +37147,13 @@
         <v>1</v>
       </c>
       <c r="O579" s="5" t="n">
-        <v>13.71</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
@@ -37171,7 +37171,7 @@
       </c>
       <c r="E580" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F580" s="5" t="inlineStr">
@@ -37208,13 +37208,13 @@
         <v>1</v>
       </c>
       <c r="O580" s="5" t="n">
-        <v>14.4</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -37232,7 +37232,7 @@
       </c>
       <c r="E581" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F581" s="5" t="inlineStr">
@@ -37269,13 +37269,13 @@
         <v>1</v>
       </c>
       <c r="O581" s="5" t="n">
-        <v>17.15</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
@@ -37293,7 +37293,7 @@
       </c>
       <c r="E582" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F582" s="5" t="inlineStr">
@@ -37330,13 +37330,13 @@
         <v>1</v>
       </c>
       <c r="O582" s="5" t="n">
-        <v>12.11</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -37354,7 +37354,7 @@
       </c>
       <c r="E583" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F583" s="5" t="inlineStr">
@@ -37391,13 +37391,13 @@
         <v>1</v>
       </c>
       <c r="O583" s="5" t="n">
-        <v>12.41</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="E584" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F584" s="5" t="inlineStr">
@@ -37430,11 +37430,11 @@
       </c>
       <c r="H584" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I584" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J584" s="5" t="b">
         <v>1</v>
@@ -37446,19 +37446,19 @@
       </c>
       <c r="L584" s="5" t="n"/>
       <c r="M584" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N584" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O584" s="5" t="n">
-        <v>5.52</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -37476,7 +37476,7 @@
       </c>
       <c r="E585" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F585" s="5" t="inlineStr">
@@ -37491,11 +37491,11 @@
       </c>
       <c r="H585" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I585" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J585" s="5" t="b">
         <v>1</v>
@@ -37507,19 +37507,19 @@
       </c>
       <c r="L585" s="5" t="n"/>
       <c r="M585" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N585" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O585" s="5" t="n">
-        <v>4.96</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
@@ -37537,7 +37537,7 @@
       </c>
       <c r="E586" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F586" s="5" t="inlineStr">
@@ -37552,11 +37552,11 @@
       </c>
       <c r="H586" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I586" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J586" s="5" t="b">
         <v>1</v>
@@ -37568,19 +37568,19 @@
       </c>
       <c r="L586" s="5" t="n"/>
       <c r="M586" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N586" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O586" s="5" t="n">
-        <v>5.45</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -37598,7 +37598,7 @@
       </c>
       <c r="E587" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F587" s="5" t="inlineStr">
@@ -37635,13 +37635,13 @@
         <v>1</v>
       </c>
       <c r="O587" s="5" t="n">
-        <v>13.81</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
@@ -37659,7 +37659,7 @@
       </c>
       <c r="E588" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F588" s="5" t="inlineStr">
@@ -37696,13 +37696,13 @@
         <v>1</v>
       </c>
       <c r="O588" s="5" t="n">
-        <v>14.08</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -37720,7 +37720,7 @@
       </c>
       <c r="E589" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F589" s="5" t="inlineStr">
@@ -37757,13 +37757,13 @@
         <v>1</v>
       </c>
       <c r="O589" s="5" t="n">
-        <v>14.18</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
@@ -37781,7 +37781,7 @@
       </c>
       <c r="E590" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F590" s="5" t="inlineStr">
@@ -37807,24 +37807,24 @@
       </c>
       <c r="K590" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L590" s="5" t="n"/>
       <c r="M590" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N590" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O590" s="5" t="n">
-        <v>15.67</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -37842,7 +37842,7 @@
       </c>
       <c r="E591" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F591" s="5" t="inlineStr">
@@ -37868,24 +37868,24 @@
       </c>
       <c r="K591" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L591" s="5" t="n"/>
       <c r="M591" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N591" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O591" s="5" t="n">
-        <v>12.41</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="E592" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F592" s="5" t="inlineStr">
@@ -37929,24 +37929,24 @@
       </c>
       <c r="K592" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L592" s="5" t="n"/>
       <c r="M592" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N592" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O592" s="5" t="n">
-        <v>13.05</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
@@ -37964,7 +37964,7 @@
       </c>
       <c r="E593" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F593" s="5" t="inlineStr">
@@ -38001,13 +38001,13 @@
         <v>1</v>
       </c>
       <c r="O593" s="5" t="n">
-        <v>18.37</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B594" s="5" t="n">
@@ -38025,7 +38025,7 @@
       </c>
       <c r="E594" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F594" s="5" t="inlineStr">
@@ -38062,13 +38062,13 @@
         <v>1</v>
       </c>
       <c r="O594" s="5" t="n">
-        <v>13.97</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B595" s="5" t="n">
@@ -38086,7 +38086,7 @@
       </c>
       <c r="E595" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F595" s="5" t="inlineStr">
@@ -38123,31 +38123,31 @@
         <v>1</v>
       </c>
       <c r="O595" s="5" t="n">
-        <v>14.19</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E596" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F596" s="5" t="inlineStr">
@@ -38157,12 +38157,12 @@
       </c>
       <c r="G596" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H596" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I596" s="5" t="b">
@@ -38178,52 +38178,52 @@
       </c>
       <c r="L596" s="5" t="n"/>
       <c r="M596" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N596" s="5" t="n">
-        <v>1</v>
+        <v>0.0213</v>
       </c>
       <c r="O596" s="5" t="n">
-        <v>17.02</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B597" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C597" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F597" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G597" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H597" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I597" s="5" t="b">
@@ -38239,32 +38239,32 @@
       </c>
       <c r="L597" s="5" t="n"/>
       <c r="M597" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N597" s="5" t="n">
-        <v>1</v>
+        <v>0.0213</v>
       </c>
       <c r="O597" s="5" t="n">
-        <v>13.79</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B598" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C598" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D598" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E598" s="5" t="inlineStr">
@@ -38274,17 +38274,17 @@
       </c>
       <c r="F598" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G598" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H598" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I598" s="5" t="b">
@@ -38300,27 +38300,27 @@
       </c>
       <c r="L598" s="5" t="n"/>
       <c r="M598" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N598" s="5" t="n">
-        <v>1</v>
+        <v>0.0213</v>
       </c>
       <c r="O598" s="5" t="n">
-        <v>13.97</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C599" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D599" s="5" t="inlineStr">
@@ -38340,12 +38340,12 @@
       </c>
       <c r="G599" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H599" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I599" s="5" t="b">
@@ -38361,27 +38361,27 @@
       </c>
       <c r="L599" s="5" t="n"/>
       <c r="M599" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N599" s="5" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="O599" s="5" t="n">
-        <v>15.89</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
@@ -38401,12 +38401,12 @@
       </c>
       <c r="G600" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H600" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I600" s="5" t="b">
@@ -38422,27 +38422,27 @@
       </c>
       <c r="L600" s="5" t="n"/>
       <c r="M600" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N600" s="5" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="O600" s="5" t="n">
-        <v>11.9</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C601" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D601" s="5" t="inlineStr">
@@ -38462,12 +38462,12 @@
       </c>
       <c r="G601" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H601" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I601" s="5" t="b">
@@ -38483,27 +38483,27 @@
       </c>
       <c r="L601" s="5" t="n"/>
       <c r="M601" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N601" s="5" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="O601" s="5" t="n">
-        <v>12.59</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D602" s="5" t="inlineStr">
@@ -38523,12 +38523,12 @@
       </c>
       <c r="G602" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H602" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I602" s="5" t="b">
@@ -38539,7 +38539,7 @@
       </c>
       <c r="K602" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L602" s="5" t="n"/>
@@ -38547,24 +38547,24 @@
         <v>0</v>
       </c>
       <c r="N602" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O602" s="5" t="n">
-        <v>16.74</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C603" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D603" s="5" t="inlineStr">
@@ -38584,12 +38584,12 @@
       </c>
       <c r="G603" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H603" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I603" s="5" t="b">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="K603" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L603" s="5" t="n"/>
@@ -38608,24 +38608,24 @@
         <v>0</v>
       </c>
       <c r="N603" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O603" s="5" t="n">
-        <v>12.99</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
@@ -38645,12 +38645,12 @@
       </c>
       <c r="G604" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H604" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I604" s="5" t="b">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="K604" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L604" s="5" t="n"/>
@@ -38669,24 +38669,24 @@
         <v>0</v>
       </c>
       <c r="N604" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O604" s="5" t="n">
-        <v>12.8</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B605" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C605" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D605" s="5" t="inlineStr">
@@ -38706,12 +38706,12 @@
       </c>
       <c r="G605" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H605" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I605" s="5" t="b">
@@ -38727,27 +38727,27 @@
       </c>
       <c r="L605" s="5" t="n"/>
       <c r="M605" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N605" s="5" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="O605" s="5" t="n">
-        <v>17.85</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
@@ -38767,12 +38767,12 @@
       </c>
       <c r="G606" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H606" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I606" s="5" t="b">
@@ -38788,27 +38788,27 @@
       </c>
       <c r="L606" s="5" t="n"/>
       <c r="M606" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N606" s="5" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="O606" s="5" t="n">
-        <v>13.07</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C607" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D607" s="5" t="inlineStr">
@@ -38828,12 +38828,12 @@
       </c>
       <c r="G607" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H607" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I607" s="5" t="b">
@@ -38849,19 +38849,19 @@
       </c>
       <c r="L607" s="5" t="n"/>
       <c r="M607" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N607" s="5" t="n">
-        <v>1</v>
+        <v>0.0769</v>
       </c>
       <c r="O607" s="5" t="n">
-        <v>13.32</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>ranking_kg1_002</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
@@ -38869,7 +38869,7 @@
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
@@ -38889,16 +38889,16 @@
       </c>
       <c r="G608" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="H608" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I608" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J608" s="5" t="b">
         <v>1</v>
@@ -38913,16 +38913,16 @@
         <v>0</v>
       </c>
       <c r="N608" s="5" t="n">
-        <v>0.0213</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="O608" s="5" t="n">
-        <v>16.73</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>ranking_kg1_002</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
@@ -38930,7 +38930,7 @@
       </c>
       <c r="C609" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D609" s="5" t="inlineStr">
@@ -38950,16 +38950,16 @@
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H609" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H609" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I609" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J609" s="5" t="b">
         <v>1</v>
@@ -38974,16 +38974,16 @@
         <v>0</v>
       </c>
       <c r="N609" s="5" t="n">
-        <v>0.0213</v>
+        <v>0.1099</v>
       </c>
       <c r="O609" s="5" t="n">
-        <v>14.66</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>ranking_kg1_002</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
@@ -39011,16 +39011,16 @@
       </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H610" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H610" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I610" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J610" s="5" t="b">
         <v>1</v>
@@ -39035,1673 +39035,14 @@
         <v>0</v>
       </c>
       <c r="N610" s="5" t="n">
-        <v>0.0213</v>
+        <v>0.1099</v>
       </c>
       <c r="O610" s="5" t="n">
-        <v>11.73</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B611" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C611" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D611" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E611" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F611" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G611" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H611" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I611" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J611" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K611" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L611" s="5" t="n"/>
-      <c r="M611" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N611" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O611" s="5" t="n">
-        <v>13.44</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B612" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C612" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D612" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E612" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F612" s="5" t="inlineStr">
-        <is>
-          <t>few-shot</t>
-        </is>
-      </c>
-      <c r="G612" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H612" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I612" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J612" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K612" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L612" s="5" t="n"/>
-      <c r="M612" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N612" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O612" s="5" t="n">
-        <v>9.630000000000001</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B613" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C613" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D613" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E613" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F613" s="5" t="inlineStr">
-        <is>
-          <t>cot</t>
-        </is>
-      </c>
-      <c r="G613" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H613" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I613" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J613" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K613" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L613" s="5" t="n"/>
-      <c r="M613" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N613" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O613" s="5" t="n">
-        <v>9.76</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B614" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C614" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D614" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E614" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F614" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G614" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H614" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I614" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J614" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K614" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L614" s="5" t="n"/>
-      <c r="M614" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N614" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O614" s="5" t="n">
-        <v>13.87</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B615" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C615" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D615" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E615" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F615" s="5" t="inlineStr">
-        <is>
-          <t>few-shot</t>
-        </is>
-      </c>
-      <c r="G615" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H615" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I615" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J615" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K615" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L615" s="5" t="n"/>
-      <c r="M615" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N615" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O615" s="5" t="n">
-        <v>10.04</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B616" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C616" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D616" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E616" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F616" s="5" t="inlineStr">
-        <is>
-          <t>cot</t>
-        </is>
-      </c>
-      <c r="G616" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H616" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I616" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J616" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K616" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L616" s="5" t="n"/>
-      <c r="M616" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N616" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O616" s="5" t="n">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B617" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C617" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D617" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E617" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F617" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G617" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H617" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I617" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J617" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K617" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L617" s="5" t="n"/>
-      <c r="M617" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N617" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O617" s="5" t="n">
-        <v>13.66</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B618" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C618" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D618" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E618" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F618" s="5" t="inlineStr">
-        <is>
-          <t>few-shot</t>
-        </is>
-      </c>
-      <c r="G618" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H618" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I618" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J618" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K618" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L618" s="5" t="n"/>
-      <c r="M618" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N618" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O618" s="5" t="n">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3_001</t>
-        </is>
-      </c>
-      <c r="B619" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C619" s="5" t="inlineStr">
-        <is>
-          <t>group_aggregate_kg3</t>
-        </is>
-      </c>
-      <c r="D619" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E619" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F619" s="5" t="inlineStr">
-        <is>
-          <t>cot</t>
-        </is>
-      </c>
-      <c r="G619" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="H619" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I619" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J619" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K619" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L619" s="5" t="n"/>
-      <c r="M619" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N619" s="5" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="O619" s="5" t="n">
-        <v>9.91</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1_002</t>
-        </is>
-      </c>
-      <c r="B620" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C620" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1</t>
-        </is>
-      </c>
-      <c r="D620" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="E620" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F620" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G620" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1</t>
-        </is>
-      </c>
-      <c r="H620" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="I620" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J620" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K620" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L620" s="5" t="n"/>
-      <c r="M620" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N620" s="5" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="O620" s="5" t="n">
-        <v>38.68</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1_002</t>
-        </is>
-      </c>
-      <c r="B621" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C621" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1</t>
-        </is>
-      </c>
-      <c r="D621" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="E621" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F621" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G621" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1</t>
-        </is>
-      </c>
-      <c r="H621" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I621" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J621" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K621" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L621" s="5" t="n"/>
-      <c r="M621" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N621" s="5" t="n">
-        <v>0.1099</v>
-      </c>
-      <c r="O621" s="5" t="n">
-        <v>12.81</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1_002</t>
-        </is>
-      </c>
-      <c r="B622" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C622" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1</t>
-        </is>
-      </c>
-      <c r="D622" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="E622" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F622" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G622" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg1</t>
-        </is>
-      </c>
-      <c r="H622" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I622" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J622" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K622" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L622" s="5" t="n"/>
-      <c r="M622" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N622" s="5" t="n">
-        <v>0.1099</v>
-      </c>
-      <c r="O622" s="5" t="n">
         <v>12.27</v>
       </c>
     </row>
-    <row r="623">
-      <c r="A623" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3_002</t>
-        </is>
-      </c>
-      <c r="B623" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C623" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3</t>
-        </is>
-      </c>
-      <c r="D623" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E623" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F623" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G623" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3</t>
-        </is>
-      </c>
-      <c r="H623" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I623" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J623" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K623" s="5" t="inlineStr">
-        <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L623" s="5" t="inlineStr">
-        <is>
-          <t>params={'group_by': 'department', 'property': 'memberOf', 'function': 'COUNT'}</t>
-        </is>
-      </c>
-      <c r="M623" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N623" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O623" s="5" t="n">
-        <v>11.58</v>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3_002</t>
-        </is>
-      </c>
-      <c r="B624" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C624" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3</t>
-        </is>
-      </c>
-      <c r="D624" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E624" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F624" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G624" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3</t>
-        </is>
-      </c>
-      <c r="H624" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I624" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J624" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K624" s="5" t="inlineStr">
-        <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L624" s="5" t="inlineStr">
-        <is>
-          <t>params={'group_by': 'department', 'property': 'memberOf', 'function': 'COUNT'}</t>
-        </is>
-      </c>
-      <c r="M624" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N624" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O624" s="5" t="n">
-        <v>7.62</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3_002</t>
-        </is>
-      </c>
-      <c r="B625" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C625" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3</t>
-        </is>
-      </c>
-      <c r="D625" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E625" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F625" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G625" s="5" t="inlineStr">
-        <is>
-          <t>ranking_kg3</t>
-        </is>
-      </c>
-      <c r="H625" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I625" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J625" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K625" s="5" t="inlineStr">
-        <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L625" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'memberOf', 'function': 'COUNT'}</t>
-        </is>
-      </c>
-      <c r="M625" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N625" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O625" s="5" t="n">
-        <v>7.74</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2_002</t>
-        </is>
-      </c>
-      <c r="B626" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C626" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="D626" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
-      </c>
-      <c r="E626" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F626" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G626" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="H626" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="I626" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J626" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K626" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L626" s="5" t="n"/>
-      <c r="M626" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N626" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O626" s="5" t="n">
-        <v>28.86</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2_002</t>
-        </is>
-      </c>
-      <c r="B627" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C627" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="D627" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
-      </c>
-      <c r="E627" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F627" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G627" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="H627" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="I627" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J627" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K627" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L627" s="5" t="n"/>
-      <c r="M627" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N627" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O627" s="5" t="n">
-        <v>32.25</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2_002</t>
-        </is>
-      </c>
-      <c r="B628" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C628" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="D628" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
-      </c>
-      <c r="E628" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F628" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G628" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="H628" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I628" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J628" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K628" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L628" s="5" t="n"/>
-      <c r="M628" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N628" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O628" s="5" t="n">
-        <v>13.68</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2_003</t>
-        </is>
-      </c>
-      <c r="B629" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C629" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="D629" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
-      </c>
-      <c r="E629" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F629" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G629" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="H629" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I629" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J629" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K629" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L629" s="5" t="n"/>
-      <c r="M629" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N629" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O629" s="5" t="n">
-        <v>31.71</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2_003</t>
-        </is>
-      </c>
-      <c r="B630" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C630" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="D630" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
-      </c>
-      <c r="E630" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F630" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G630" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="H630" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I630" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J630" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K630" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L630" s="5" t="n"/>
-      <c r="M630" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N630" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O630" s="5" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2_003</t>
-        </is>
-      </c>
-      <c r="B631" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C631" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="D631" s="5" t="inlineStr">
-        <is>
-          <t>airports</t>
-        </is>
-      </c>
-      <c r="E631" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F631" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G631" s="5" t="inlineStr">
-        <is>
-          <t>count_kg2</t>
-        </is>
-      </c>
-      <c r="H631" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="I631" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J631" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K631" s="5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L631" s="5" t="n"/>
-      <c r="M631" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N631" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O631" s="5" t="n">
-        <v>17.69</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights_002</t>
-        </is>
-      </c>
-      <c r="B632" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C632" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights</t>
-        </is>
-      </c>
-      <c r="D632" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="E632" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F632" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G632" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights</t>
-        </is>
-      </c>
-      <c r="H632" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="I632" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J632" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K632" s="5" t="inlineStr">
-        <is>
-          <t>generation_failure</t>
-        </is>
-      </c>
-      <c r="L632" s="5" t="n"/>
-      <c r="M632" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N632" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O632" s="5" t="n">
-        <v>66.22</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights_002</t>
-        </is>
-      </c>
-      <c r="B633" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C633" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights</t>
-        </is>
-      </c>
-      <c r="D633" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="E633" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F633" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G633" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights</t>
-        </is>
-      </c>
-      <c r="H633" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="I633" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J633" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K633" s="5" t="inlineStr">
-        <is>
-          <t>generation_failure</t>
-        </is>
-      </c>
-      <c r="L633" s="5" t="n"/>
-      <c r="M633" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N633" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O633" s="5" t="n">
-        <v>58.65</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights_002</t>
-        </is>
-      </c>
-      <c r="B634" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C634" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights</t>
-        </is>
-      </c>
-      <c r="D634" s="5" t="inlineStr">
-        <is>
-          <t>flights</t>
-        </is>
-      </c>
-      <c r="E634" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F634" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G634" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_flights</t>
-        </is>
-      </c>
-      <c r="H634" s="5" t="inlineStr">
-        <is>
-          <t>open_kg</t>
-        </is>
-      </c>
-      <c r="I634" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J634" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K634" s="5" t="inlineStr">
-        <is>
-          <t>generation_failure</t>
-        </is>
-      </c>
-      <c r="L634" s="5" t="n"/>
-      <c r="M634" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N634" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O634" s="5" t="n">
-        <v>55.44</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments_002</t>
-        </is>
-      </c>
-      <c r="B635" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C635" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments</t>
-        </is>
-      </c>
-      <c r="D635" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E635" s="5" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="F635" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G635" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments</t>
-        </is>
-      </c>
-      <c r="H635" s="5" t="inlineStr">
-        <is>
-          <t>single_kg3</t>
-        </is>
-      </c>
-      <c r="I635" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J635" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K635" s="5" t="inlineStr">
-        <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L635" s="5" t="n"/>
-      <c r="M635" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N635" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O635" s="5" t="n">
-        <v>5.14</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments_002</t>
-        </is>
-      </c>
-      <c r="B636" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C636" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments</t>
-        </is>
-      </c>
-      <c r="D636" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E636" s="5" t="inlineStr">
-        <is>
-          <t>fr</t>
-        </is>
-      </c>
-      <c r="F636" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G636" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments</t>
-        </is>
-      </c>
-      <c r="H636" s="5" t="inlineStr">
-        <is>
-          <t>single_kg3</t>
-        </is>
-      </c>
-      <c r="I636" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J636" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K636" s="5" t="inlineStr">
-        <is>
-          <t>mapping_failure</t>
-        </is>
-      </c>
-      <c r="L636" s="5" t="n"/>
-      <c r="M636" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N636" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O636" s="5" t="n">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments_002</t>
-        </is>
-      </c>
-      <c r="B637" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C637" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments</t>
-        </is>
-      </c>
-      <c r="D637" s="5" t="inlineStr">
-        <is>
-          <t>university</t>
-        </is>
-      </c>
-      <c r="E637" s="5" t="inlineStr">
-        <is>
-          <t>ar</t>
-        </is>
-      </c>
-      <c r="F637" s="5" t="inlineStr">
-        <is>
-          <t>zero-shot</t>
-        </is>
-      </c>
-      <c r="G637" s="5" t="inlineStr">
-        <is>
-          <t>compare_two_departments</t>
-        </is>
-      </c>
-      <c r="H637" s="5" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="I637" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J637" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K637" s="5" t="inlineStr">
-        <is>
-          <t>routing_miss</t>
-        </is>
-      </c>
-      <c r="L637" s="5" t="n"/>
-      <c r="M637" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N637" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O637" s="5" t="n">
-        <v>7.93</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O637"/>
+  <autoFilter ref="A1:O610"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Raw" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$610</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw'!$A$1:$O$634</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -551,27 +551,27 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Raw!E2:E610,"en")</f>
+        <f>COUNTIF(Raw!E2:E634,"en")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"en",Raw!I2:I610,TRUE)/COUNTIF(Raw!E2:E610,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"en",Raw!I2:I634,TRUE)/COUNTIF(Raw!E2:E634,"en"),"")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"en",Raw!K2:K610,"success")/COUNTIF(Raw!E2:E610,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"en",Raw!K2:K634,"success")/COUNTIF(Raw!E2:E634,"en"),"")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"en",Raw!J2:J610,TRUE)/COUNTIF(Raw!E2:E610,"en"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"en",Raw!J2:J634,TRUE)/COUNTIF(Raw!E2:E634,"en"),"")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!E2:E610,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!E2:E634,"en"),"")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!E2:E610,"en"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!E2:E634,"en"),"")</f>
         <v/>
       </c>
     </row>
@@ -582,27 +582,27 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Raw!E2:E610,"fr")</f>
+        <f>COUNTIF(Raw!E2:E634,"fr")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"fr",Raw!I2:I610,TRUE)/COUNTIF(Raw!E2:E610,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"fr",Raw!I2:I634,TRUE)/COUNTIF(Raw!E2:E634,"fr"),"")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"fr",Raw!K2:K610,"success")/COUNTIF(Raw!E2:E610,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"fr",Raw!K2:K634,"success")/COUNTIF(Raw!E2:E634,"fr"),"")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"fr",Raw!J2:J610,TRUE)/COUNTIF(Raw!E2:E610,"fr"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"fr",Raw!J2:J634,TRUE)/COUNTIF(Raw!E2:E634,"fr"),"")</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!E2:E610,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!E2:E634,"fr"),"")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!E2:E610,"fr"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!E2:E634,"fr"),"")</f>
         <v/>
       </c>
     </row>
@@ -613,27 +613,27 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Raw!E2:E610,"ar")</f>
+        <f>COUNTIF(Raw!E2:E634,"ar")</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"ar",Raw!I2:I610,TRUE)/COUNTIF(Raw!E2:E610,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"ar",Raw!I2:I634,TRUE)/COUNTIF(Raw!E2:E634,"ar"),"")</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"ar",Raw!K2:K610,"success")/COUNTIF(Raw!E2:E610,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"ar",Raw!K2:K634,"success")/COUNTIF(Raw!E2:E634,"ar"),"")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(COUNTIFS(Raw!E2:E610,"ar",Raw!J2:J610,TRUE)/COUNTIF(Raw!E2:E610,"ar"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!E2:E634,"ar",Raw!J2:J634,TRUE)/COUNTIF(Raw!E2:E634,"ar"),"")</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!E2:E610,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!E2:E634,"ar"),"")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!E2:E610,"ar"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!E2:E634,"ar"),"")</f>
         <v/>
       </c>
     </row>
@@ -688,27 +688,27 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF(Raw!F2:F610,"zero-shot")</f>
+        <f>COUNTIF(Raw!F2:F634,"zero-shot")</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"zero-shot",Raw!I2:I610,TRUE)/COUNTIF(Raw!F2:F610,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"zero-shot",Raw!I2:I634,TRUE)/COUNTIF(Raw!F2:F634,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"zero-shot",Raw!K2:K610,"success")/COUNTIF(Raw!F2:F610,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"zero-shot",Raw!K2:K634,"success")/COUNTIF(Raw!F2:F634,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"zero-shot",Raw!J2:J610,TRUE)/COUNTIF(Raw!F2:F610,"zero-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"zero-shot",Raw!J2:J634,TRUE)/COUNTIF(Raw!F2:F634,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!F2:F610,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!F2:F634,"zero-shot"),"")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!F2:F610,"zero-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!F2:F634,"zero-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -719,27 +719,27 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF(Raw!F2:F610,"few-shot")</f>
+        <f>COUNTIF(Raw!F2:F634,"few-shot")</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"few-shot",Raw!I2:I610,TRUE)/COUNTIF(Raw!F2:F610,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"few-shot",Raw!I2:I634,TRUE)/COUNTIF(Raw!F2:F634,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"few-shot",Raw!K2:K610,"success")/COUNTIF(Raw!F2:F610,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"few-shot",Raw!K2:K634,"success")/COUNTIF(Raw!F2:F634,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"few-shot",Raw!J2:J610,TRUE)/COUNTIF(Raw!F2:F610,"few-shot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"few-shot",Raw!J2:J634,TRUE)/COUNTIF(Raw!F2:F634,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!F2:F610,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!F2:F634,"few-shot"),"")</f>
         <v/>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!F2:F610,"few-shot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!F2:F634,"few-shot"),"")</f>
         <v/>
       </c>
     </row>
@@ -750,27 +750,27 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF(Raw!F2:F610,"cot")</f>
+        <f>COUNTIF(Raw!F2:F634,"cot")</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"cot",Raw!I2:I610,TRUE)/COUNTIF(Raw!F2:F610,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"cot",Raw!I2:I634,TRUE)/COUNTIF(Raw!F2:F634,"cot"),"")</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"cot",Raw!K2:K610,"success")/COUNTIF(Raw!F2:F610,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"cot",Raw!K2:K634,"success")/COUNTIF(Raw!F2:F634,"cot"),"")</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IFERROR(COUNTIFS(Raw!F2:F610,"cot",Raw!J2:J610,TRUE)/COUNTIF(Raw!F2:F610,"cot"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!F2:F634,"cot",Raw!J2:J634,TRUE)/COUNTIF(Raw!F2:F634,"cot"),"")</f>
         <v/>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!F2:F610,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!F2:F634,"cot"),"")</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!F2:F610,"cot"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!F2:F634,"cot"),"")</f>
         <v/>
       </c>
     </row>
@@ -823,27 +823,27 @@
         <v>1</v>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF(Raw!B2:B610,"1")</f>
+        <f>COUNTIF(Raw!B2:B634,"1")</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"1",Raw!I2:I610,TRUE)/COUNTIF(Raw!B2:B610,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"1",Raw!I2:I634,TRUE)/COUNTIF(Raw!B2:B634,"1"),"")</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"1",Raw!K2:K610,"success")/COUNTIF(Raw!B2:B610,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"1",Raw!K2:K634,"success")/COUNTIF(Raw!B2:B634,"1"),"")</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"1",Raw!J2:J610,TRUE)/COUNTIF(Raw!B2:B610,"1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"1",Raw!J2:J634,TRUE)/COUNTIF(Raw!B2:B634,"1"),"")</f>
         <v/>
       </c>
       <c r="F18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!B2:B610,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!B2:B634,"1"),"")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!B2:B610,"1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!B2:B634,"1"),"")</f>
         <v/>
       </c>
     </row>
@@ -852,27 +852,27 @@
         <v>2</v>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF(Raw!B2:B610,"2")</f>
+        <f>COUNTIF(Raw!B2:B634,"2")</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"2",Raw!I2:I610,TRUE)/COUNTIF(Raw!B2:B610,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"2",Raw!I2:I634,TRUE)/COUNTIF(Raw!B2:B634,"2"),"")</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"2",Raw!K2:K610,"success")/COUNTIF(Raw!B2:B610,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"2",Raw!K2:K634,"success")/COUNTIF(Raw!B2:B634,"2"),"")</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"2",Raw!J2:J610,TRUE)/COUNTIF(Raw!B2:B610,"2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"2",Raw!J2:J634,TRUE)/COUNTIF(Raw!B2:B634,"2"),"")</f>
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!B2:B610,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!B2:B634,"2"),"")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!B2:B610,"2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!B2:B634,"2"),"")</f>
         <v/>
       </c>
     </row>
@@ -881,27 +881,27 @@
         <v>3</v>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF(Raw!B2:B610,"3")</f>
+        <f>COUNTIF(Raw!B2:B634,"3")</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"3",Raw!I2:I610,TRUE)/COUNTIF(Raw!B2:B610,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"3",Raw!I2:I634,TRUE)/COUNTIF(Raw!B2:B634,"3"),"")</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"3",Raw!K2:K610,"success")/COUNTIF(Raw!B2:B610,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"3",Raw!K2:K634,"success")/COUNTIF(Raw!B2:B634,"3"),"")</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IFERROR(COUNTIFS(Raw!B2:B610,"3",Raw!J2:J610,TRUE)/COUNTIF(Raw!B2:B610,"3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!B2:B634,"3",Raw!J2:J634,TRUE)/COUNTIF(Raw!B2:B634,"3"),"")</f>
         <v/>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!B2:B610,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!B2:B634,"3"),"")</f>
         <v/>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!B2:B610,"3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!B2:B634,"3"),"")</f>
         <v/>
       </c>
     </row>
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF(Raw!C2:C610,"single_kg1")</f>
+        <f>COUNTIF(Raw!C2:C634,"single_kg1")</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg1",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg1",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg1",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="F24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"single_kg1"),"")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"single_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"single_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -987,27 +987,27 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF(Raw!C2:C610,"single_kg2")</f>
+        <f>COUNTIF(Raw!C2:C634,"single_kg2")</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg2",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg2",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg2",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="F25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"single_kg2"),"")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"single_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"single_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF(Raw!C2:C610,"single_kg3")</f>
+        <f>COUNTIF(Raw!C2:C634,"single_kg3")</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg3",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg3",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"single_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"single_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"single_kg3",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="F26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"single_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"single_kg3"),"")</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"single_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"single_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1049,27 +1049,27 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF(Raw!C2:C610,"cross_kg")</f>
+        <f>COUNTIF(Raw!C2:C634,"cross_kg")</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"cross_kg",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"cross_kg",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"cross_kg",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"cross_kg",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"cross_kg",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"cross_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"cross_kg",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="F27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"cross_kg"),"")</f>
         <v/>
       </c>
       <c r="G27" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"cross_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"cross_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1080,27 +1080,27 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF(Raw!C2:C610,"open_kg")</f>
+        <f>COUNTIF(Raw!C2:C634,"open_kg")</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"open_kg",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"open_kg",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"open_kg",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"open_kg",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"open_kg",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"open_kg"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"open_kg",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="F28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"open_kg"),"")</f>
         <v/>
       </c>
       <c r="G28" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"open_kg"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"open_kg"),"")</f>
         <v/>
       </c>
     </row>
@@ -1111,27 +1111,27 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF(Raw!C2:C610,"count_kg1")</f>
+        <f>COUNTIF(Raw!C2:C634,"count_kg1")</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg1",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg1",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg1",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="F29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"count_kg1"),"")</f>
         <v/>
       </c>
       <c r="G29" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"count_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"count_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1142,27 +1142,27 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF(Raw!C2:C610,"count_kg2")</f>
+        <f>COUNTIF(Raw!C2:C634,"count_kg2")</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg2",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"count_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg2",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg2",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="F30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"count_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"count_kg2"),"")</f>
         <v/>
       </c>
       <c r="G30" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"count_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"count_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF(Raw!C2:C610,"count_kg3")</f>
+        <f>COUNTIF(Raw!C2:C634,"count_kg3")</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg3",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg3",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"count_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"count_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"count_kg3",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="F31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"count_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"count_kg3"),"")</f>
         <v/>
       </c>
       <c r="G31" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"count_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"count_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1204,27 +1204,27 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF(Raw!C2:C610,"filter_numeric_kg1")</f>
+        <f>COUNTIF(Raw!C2:C634,"filter_numeric_kg1")</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg1",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg1",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg1",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="F32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_numeric_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"filter_numeric_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1235,27 +1235,27 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF(Raw!C2:C610,"filter_numeric_kg2")</f>
+        <f>COUNTIF(Raw!C2:C634,"filter_numeric_kg2")</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg2",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg2",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg2",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="F33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_numeric_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"filter_numeric_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1266,27 +1266,27 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF(Raw!C2:C610,"filter_numeric_kg3")</f>
+        <f>COUNTIF(Raw!C2:C634,"filter_numeric_kg3")</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg3",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg3",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_numeric_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_numeric_kg3",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="F34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_numeric_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"filter_numeric_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1297,27 +1297,27 @@
         </is>
       </c>
       <c r="B35" s="5">
-        <f>COUNTIF(Raw!C2:C610,"filter_string_kg2")</f>
+        <f>COUNTIF(Raw!C2:C634,"filter_string_kg2")</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_string_kg2",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_string_kg2",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_string_kg2",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="F35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"filter_string_kg2"),"")</f>
         <v/>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_string_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"filter_string_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1328,27 +1328,27 @@
         </is>
       </c>
       <c r="B36" s="5">
-        <f>COUNTIF(Raw!C2:C610,"filter_string_kg3")</f>
+        <f>COUNTIF(Raw!C2:C634,"filter_string_kg3")</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_string_kg3",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_string_kg3",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"filter_string_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"filter_string_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"filter_string_kg3",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="F36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"filter_string_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"filter_string_kg3"),"")</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"filter_string_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"filter_string_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1359,27 +1359,27 @@
         </is>
       </c>
       <c r="B37" s="5">
-        <f>COUNTIF(Raw!C2:C610,"ranking_kg1")</f>
+        <f>COUNTIF(Raw!C2:C634,"ranking_kg1")</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg1",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ranking_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg1",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg1",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="F37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ranking_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"ranking_kg1"),"")</f>
         <v/>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ranking_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"ranking_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1390,27 +1390,27 @@
         </is>
       </c>
       <c r="B38" s="5">
-        <f>COUNTIF(Raw!C2:C610,"ranking_kg2")</f>
+        <f>COUNTIF(Raw!C2:C634,"ranking_kg2")</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg2",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg2",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg2",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="F38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"ranking_kg2"),"")</f>
         <v/>
       </c>
       <c r="G38" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ranking_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"ranking_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1421,27 +1421,27 @@
         </is>
       </c>
       <c r="B39" s="5">
-        <f>COUNTIF(Raw!C2:C610,"ranking_kg3")</f>
+        <f>COUNTIF(Raw!C2:C634,"ranking_kg3")</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg3",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ranking_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg3",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ranking_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ranking_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ranking_kg3",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="F39" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ranking_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"ranking_kg3"),"")</f>
         <v/>
       </c>
       <c r="G39" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ranking_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"ranking_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1452,27 +1452,27 @@
         </is>
       </c>
       <c r="B40" s="5">
-        <f>COUNTIF(Raw!C2:C610,"compare_two_airports")</f>
+        <f>COUNTIF(Raw!C2:C634,"compare_two_airports")</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_airports",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_airports",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="D40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_airports",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_airports",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="E40" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_airports",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_airports"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_airports",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="F40" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"compare_two_airports"),"")</f>
         <v/>
       </c>
       <c r="G40" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"compare_two_airports"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"compare_two_airports"),"")</f>
         <v/>
       </c>
     </row>
@@ -1483,27 +1483,27 @@
         </is>
       </c>
       <c r="B41" s="5">
-        <f>COUNTIF(Raw!C2:C610,"compare_two_flights")</f>
+        <f>COUNTIF(Raw!C2:C634,"compare_two_flights")</f>
         <v/>
       </c>
       <c r="C41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_flights",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_flights"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_flights",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="D41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_flights",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"compare_two_flights"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_flights",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="E41" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_flights",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_flights"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_flights",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="F41" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"compare_two_flights"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"compare_two_flights"),"")</f>
         <v/>
       </c>
       <c r="G41" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"compare_two_flights"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"compare_two_flights"),"")</f>
         <v/>
       </c>
     </row>
@@ -1514,27 +1514,27 @@
         </is>
       </c>
       <c r="B42" s="5">
-        <f>COUNTIF(Raw!C2:C610,"compare_two_departments")</f>
+        <f>COUNTIF(Raw!C2:C634,"compare_two_departments")</f>
         <v/>
       </c>
       <c r="C42" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_departments",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_departments"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_departments",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="D42" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_departments",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"compare_two_departments"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_departments",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="E42" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"compare_two_departments",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"compare_two_departments"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"compare_two_departments",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="F42" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"compare_two_departments"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"compare_two_departments"),"")</f>
         <v/>
       </c>
       <c r="G42" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"compare_two_departments"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"compare_two_departments"),"")</f>
         <v/>
       </c>
     </row>
@@ -1545,27 +1545,27 @@
         </is>
       </c>
       <c r="B43" s="5">
-        <f>COUNTIF(Raw!C2:C610,"group_aggregate_kg1")</f>
+        <f>COUNTIF(Raw!C2:C634,"group_aggregate_kg1")</f>
         <v/>
       </c>
       <c r="C43" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg1",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg1",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="D43" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg1",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg1",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="E43" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg1",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg1",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="F43" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
       <c r="G43" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"group_aggregate_kg1"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"group_aggregate_kg1"),"")</f>
         <v/>
       </c>
     </row>
@@ -1576,27 +1576,27 @@
         </is>
       </c>
       <c r="B44" s="5">
-        <f>COUNTIF(Raw!C2:C610,"group_aggregate_kg2")</f>
+        <f>COUNTIF(Raw!C2:C634,"group_aggregate_kg2")</f>
         <v/>
       </c>
       <c r="C44" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg2",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg2",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="D44" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg2",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg2",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="E44" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg2",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg2",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="F44" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
       <c r="G44" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"group_aggregate_kg2"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"group_aggregate_kg2"),"")</f>
         <v/>
       </c>
     </row>
@@ -1607,27 +1607,27 @@
         </is>
       </c>
       <c r="B45" s="5">
-        <f>COUNTIF(Raw!C2:C610,"group_aggregate_kg3")</f>
+        <f>COUNTIF(Raw!C2:C634,"group_aggregate_kg3")</f>
         <v/>
       </c>
       <c r="C45" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg3",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg3",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="D45" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg3",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg3",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="E45" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"group_aggregate_kg3",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"group_aggregate_kg3",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="F45" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
       <c r="G45" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"group_aggregate_kg3"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"group_aggregate_kg3"),"")</f>
         <v/>
       </c>
     </row>
@@ -1638,27 +1638,27 @@
         </is>
       </c>
       <c r="B46" s="5">
-        <f>COUNTIF(Raw!C2:C610,"out_of_scope")</f>
+        <f>COUNTIF(Raw!C2:C634,"out_of_scope")</f>
         <v/>
       </c>
       <c r="C46" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"out_of_scope",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"out_of_scope",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="D46" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"out_of_scope",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"out_of_scope",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="E46" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"out_of_scope",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"out_of_scope"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"out_of_scope",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="F46" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"out_of_scope"),"")</f>
         <v/>
       </c>
       <c r="G46" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"out_of_scope"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"out_of_scope"),"")</f>
         <v/>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
         </is>
       </c>
       <c r="B47" s="5">
-        <f>COUNTIF(Raw!C2:C610,"ask_query")</f>
+        <f>COUNTIF(Raw!C2:C634,"ask_query")</f>
         <v/>
       </c>
       <c r="C47" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ask_query",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ask_query",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="D47" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ask_query",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ask_query",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="E47" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ask_query",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ask_query"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ask_query",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="F47" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"ask_query"),"")</f>
         <v/>
       </c>
       <c r="G47" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ask_query"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"ask_query"),"")</f>
         <v/>
       </c>
     </row>
@@ -1700,27 +1700,27 @@
         </is>
       </c>
       <c r="B48" s="5">
-        <f>COUNTIF(Raw!C2:C610,"typo_fuzzy")</f>
+        <f>COUNTIF(Raw!C2:C634,"typo_fuzzy")</f>
         <v/>
       </c>
       <c r="C48" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"typo_fuzzy",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"typo_fuzzy",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="D48" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"typo_fuzzy",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"typo_fuzzy",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="E48" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"typo_fuzzy",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"typo_fuzzy"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"typo_fuzzy",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="F48" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"typo_fuzzy"),"")</f>
         <v/>
       </c>
       <c r="G48" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"typo_fuzzy"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"typo_fuzzy"),"")</f>
         <v/>
       </c>
     </row>
@@ -1731,27 +1731,27 @@
         </is>
       </c>
       <c r="B49" s="5">
-        <f>COUNTIF(Raw!C2:C610,"multilingual_edge")</f>
+        <f>COUNTIF(Raw!C2:C634,"multilingual_edge")</f>
         <v/>
       </c>
       <c r="C49" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multilingual_edge",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"multilingual_edge",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="D49" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multilingual_edge",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"multilingual_edge",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="E49" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multilingual_edge",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"multilingual_edge"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"multilingual_edge",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="F49" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"multilingual_edge"),"")</f>
         <v/>
       </c>
       <c r="G49" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"multilingual_edge"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"multilingual_edge"),"")</f>
         <v/>
       </c>
     </row>
@@ -1762,27 +1762,27 @@
         </is>
       </c>
       <c r="B50" s="5">
-        <f>COUNTIF(Raw!C2:C610,"property_ambiguity")</f>
+        <f>COUNTIF(Raw!C2:C634,"property_ambiguity")</f>
         <v/>
       </c>
       <c r="C50" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"property_ambiguity",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"property_ambiguity",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="D50" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"property_ambiguity",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"property_ambiguity",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="E50" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"property_ambiguity",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"property_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"property_ambiguity",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="F50" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"property_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="G50" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"property_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"property_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1793,27 +1793,27 @@
         </is>
       </c>
       <c r="B51" s="5">
-        <f>COUNTIF(Raw!C2:C610,"ghost_property")</f>
+        <f>COUNTIF(Raw!C2:C634,"ghost_property")</f>
         <v/>
       </c>
       <c r="C51" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ghost_property",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"ghost_property"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ghost_property",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="D51" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ghost_property",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"ghost_property"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ghost_property",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="E51" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"ghost_property",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"ghost_property"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"ghost_property",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="F51" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"ghost_property"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"ghost_property"),"")</f>
         <v/>
       </c>
       <c r="G51" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"ghost_property"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"ghost_property"),"")</f>
         <v/>
       </c>
     </row>
@@ -1824,27 +1824,27 @@
         </is>
       </c>
       <c r="B52" s="5">
-        <f>COUNTIF(Raw!C2:C610,"multi_value_ambiguity")</f>
+        <f>COUNTIF(Raw!C2:C634,"multi_value_ambiguity")</f>
         <v/>
       </c>
       <c r="C52" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multi_value_ambiguity",Raw!I2:I610,TRUE)/COUNTIF(Raw!C2:C610,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"multi_value_ambiguity",Raw!I2:I634,TRUE)/COUNTIF(Raw!C2:C634,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="D52" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multi_value_ambiguity",Raw!K2:K610,"success")/COUNTIF(Raw!C2:C610,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"multi_value_ambiguity",Raw!K2:K634,"success")/COUNTIF(Raw!C2:C634,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="E52" s="6">
-        <f>IFERROR(COUNTIFS(Raw!C2:C610,"multi_value_ambiguity",Raw!J2:J610,TRUE)/COUNTIF(Raw!C2:C610,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(COUNTIFS(Raw!C2:C634,"multi_value_ambiguity",Raw!J2:J634,TRUE)/COUNTIF(Raw!C2:C634,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="F52" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!M2:M610,Raw!C2:C610,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!M2:M634,Raw!C2:C634,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
       <c r="G52" s="6">
-        <f>IFERROR(AVERAGEIFS(Raw!N2:N610,Raw!C2:C610,"multi_value_ambiguity"),"")</f>
+        <f>IFERROR(AVERAGEIFS(Raw!N2:N634,Raw!C2:C634,"multi_value_ambiguity"),"")</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O610"/>
+  <dimension ref="A1:O634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35087,7 +35087,7 @@
         <v>1</v>
       </c>
       <c r="O545" s="5" t="n">
-        <v>40.7</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="546">
@@ -35148,7 +35148,7 @@
         <v>1</v>
       </c>
       <c r="O546" s="5" t="n">
-        <v>41.08</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="547">
@@ -35209,7 +35209,7 @@
         <v>0</v>
       </c>
       <c r="O547" s="5" t="n">
-        <v>37.13</v>
+        <v>35.21</v>
       </c>
     </row>
     <row r="548">
@@ -35268,7 +35268,7 @@
         <v>1</v>
       </c>
       <c r="O548" s="5" t="n">
-        <v>25.4</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="549">
@@ -35327,7 +35327,7 @@
         <v>1</v>
       </c>
       <c r="O549" s="5" t="n">
-        <v>12.42</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="550">
@@ -35386,7 +35386,7 @@
         <v>1</v>
       </c>
       <c r="O550" s="5" t="n">
-        <v>12.13</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="551">
@@ -35445,7 +35445,7 @@
         <v>1</v>
       </c>
       <c r="O551" s="5" t="n">
-        <v>14.77</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="552">
@@ -35504,7 +35504,7 @@
         <v>1</v>
       </c>
       <c r="O552" s="5" t="n">
-        <v>13.1</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="553">
@@ -35563,7 +35563,7 @@
         <v>1</v>
       </c>
       <c r="O553" s="5" t="n">
-        <v>13.21</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="554">
@@ -35622,7 +35622,7 @@
         <v>1</v>
       </c>
       <c r="O554" s="5" t="n">
-        <v>14.8</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="555">
@@ -35681,7 +35681,7 @@
         <v>1</v>
       </c>
       <c r="O555" s="5" t="n">
-        <v>13.35</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="556">
@@ -35740,7 +35740,7 @@
         <v>1</v>
       </c>
       <c r="O556" s="5" t="n">
-        <v>13.69</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="557">
@@ -35801,7 +35801,7 @@
         <v>0</v>
       </c>
       <c r="O557" s="5" t="n">
-        <v>76.8</v>
+        <v>74.43000000000001</v>
       </c>
     </row>
     <row r="558">
@@ -35862,7 +35862,7 @@
         <v>0</v>
       </c>
       <c r="O558" s="5" t="n">
-        <v>12.28</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="559">
@@ -35923,7 +35923,7 @@
         <v>0</v>
       </c>
       <c r="O559" s="5" t="n">
-        <v>68.23999999999999</v>
+        <v>68.06</v>
       </c>
     </row>
     <row r="560">
@@ -35984,7 +35984,7 @@
         <v>0</v>
       </c>
       <c r="O560" s="5" t="n">
-        <v>15.89</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="561">
@@ -36045,7 +36045,7 @@
         <v>0</v>
       </c>
       <c r="O561" s="5" t="n">
-        <v>21</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="562">
@@ -36106,7 +36106,7 @@
         <v>0</v>
       </c>
       <c r="O562" s="5" t="n">
-        <v>15.93</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="563">
@@ -36167,7 +36167,7 @@
         <v>0</v>
       </c>
       <c r="O563" s="5" t="n">
-        <v>55.99</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="564">
@@ -36228,7 +36228,7 @@
         <v>0</v>
       </c>
       <c r="O564" s="5" t="n">
-        <v>81.94</v>
+        <v>57.66</v>
       </c>
     </row>
     <row r="565">
@@ -36289,7 +36289,7 @@
         <v>0</v>
       </c>
       <c r="O565" s="5" t="n">
-        <v>65.08</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="566">
@@ -36354,7 +36354,7 @@
         <v>0</v>
       </c>
       <c r="O566" s="5" t="n">
-        <v>17.58</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="567">
@@ -36415,7 +36415,7 @@
         <v>0</v>
       </c>
       <c r="O567" s="5" t="n">
-        <v>12.67</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="568">
@@ -36476,7 +36476,7 @@
         <v>0</v>
       </c>
       <c r="O568" s="5" t="n">
-        <v>10.79</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="569">
@@ -36537,7 +36537,7 @@
         <v>1</v>
       </c>
       <c r="O569" s="5" t="n">
-        <v>17.11</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="570">
@@ -36598,7 +36598,7 @@
         <v>1</v>
       </c>
       <c r="O570" s="5" t="n">
-        <v>12.6</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="571">
@@ -36659,7 +36659,7 @@
         <v>1</v>
       </c>
       <c r="O571" s="5" t="n">
-        <v>13.03</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="572">
@@ -36720,7 +36720,7 @@
         <v>1</v>
       </c>
       <c r="O572" s="5" t="n">
-        <v>12.46</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="573">
@@ -36781,7 +36781,7 @@
         <v>1</v>
       </c>
       <c r="O573" s="5" t="n">
-        <v>12.24</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="574">
@@ -36842,7 +36842,7 @@
         <v>1</v>
       </c>
       <c r="O574" s="5" t="n">
-        <v>13.66</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="575">
@@ -36903,7 +36903,7 @@
         <v>1</v>
       </c>
       <c r="O575" s="5" t="n">
-        <v>12.81</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="576">
@@ -36964,7 +36964,7 @@
         <v>1</v>
       </c>
       <c r="O576" s="5" t="n">
-        <v>13.71</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="577">
@@ -37025,13 +37025,13 @@
         <v>1</v>
       </c>
       <c r="O577" s="5" t="n">
-        <v>14.4</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
@@ -37086,13 +37086,13 @@
         <v>1</v>
       </c>
       <c r="O578" s="5" t="n">
-        <v>15.67</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
@@ -37147,13 +37147,13 @@
         <v>1</v>
       </c>
       <c r="O579" s="5" t="n">
-        <v>12.41</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
@@ -37208,13 +37208,13 @@
         <v>1</v>
       </c>
       <c r="O580" s="5" t="n">
-        <v>13.05</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -37269,13 +37269,13 @@
         <v>1</v>
       </c>
       <c r="O581" s="5" t="n">
-        <v>18.37</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
@@ -37330,13 +37330,13 @@
         <v>1</v>
       </c>
       <c r="O582" s="5" t="n">
-        <v>13.97</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -37391,13 +37391,13 @@
         <v>1</v>
       </c>
       <c r="O583" s="5" t="n">
-        <v>14.19</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
@@ -37452,13 +37452,13 @@
         <v>1</v>
       </c>
       <c r="O584" s="5" t="n">
-        <v>17.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -37513,13 +37513,13 @@
         <v>1</v>
       </c>
       <c r="O585" s="5" t="n">
-        <v>13.79</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
@@ -37574,13 +37574,13 @@
         <v>1</v>
       </c>
       <c r="O586" s="5" t="n">
-        <v>13.97</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -37635,13 +37635,13 @@
         <v>1</v>
       </c>
       <c r="O587" s="5" t="n">
-        <v>15.89</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
@@ -37696,13 +37696,13 @@
         <v>1</v>
       </c>
       <c r="O588" s="5" t="n">
-        <v>11.9</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -37757,13 +37757,13 @@
         <v>1</v>
       </c>
       <c r="O589" s="5" t="n">
-        <v>12.59</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
@@ -37807,24 +37807,24 @@
       </c>
       <c r="K590" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L590" s="5" t="n"/>
       <c r="M590" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N590" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O590" s="5" t="n">
-        <v>16.74</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -37868,24 +37868,24 @@
       </c>
       <c r="K591" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L591" s="5" t="n"/>
       <c r="M591" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N591" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O591" s="5" t="n">
-        <v>12.99</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
@@ -37929,24 +37929,24 @@
       </c>
       <c r="K592" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L592" s="5" t="n"/>
       <c r="M592" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N592" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O592" s="5" t="n">
-        <v>12.8</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
@@ -38001,13 +38001,13 @@
         <v>1</v>
       </c>
       <c r="O593" s="5" t="n">
-        <v>17.85</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B594" s="5" t="n">
@@ -38062,13 +38062,13 @@
         <v>1</v>
       </c>
       <c r="O594" s="5" t="n">
-        <v>13.07</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B595" s="5" t="n">
@@ -38123,26 +38123,26 @@
         <v>1</v>
       </c>
       <c r="O595" s="5" t="n">
-        <v>13.32</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E596" s="5" t="inlineStr">
@@ -38157,12 +38157,12 @@
       </c>
       <c r="G596" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H596" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I596" s="5" t="b">
@@ -38178,52 +38178,52 @@
       </c>
       <c r="L596" s="5" t="n"/>
       <c r="M596" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N596" s="5" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="O596" s="5" t="n">
-        <v>16.73</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B597" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C597" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F597" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G597" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H597" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I597" s="5" t="b">
@@ -38239,52 +38239,52 @@
       </c>
       <c r="L597" s="5" t="n"/>
       <c r="M597" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N597" s="5" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="O597" s="5" t="n">
-        <v>14.66</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B598" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C598" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D598" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E598" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F598" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G598" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H598" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I598" s="5" t="b">
@@ -38300,27 +38300,27 @@
       </c>
       <c r="L598" s="5" t="n"/>
       <c r="M598" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N598" s="5" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="O598" s="5" t="n">
-        <v>11.73</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C599" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D599" s="5" t="inlineStr">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="E599" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F599" s="5" t="inlineStr">
@@ -38340,12 +38340,12 @@
       </c>
       <c r="G599" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H599" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I599" s="5" t="b">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="K599" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L599" s="5" t="n"/>
@@ -38364,24 +38364,24 @@
         <v>0</v>
       </c>
       <c r="N599" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O599" s="5" t="n">
-        <v>13.44</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
@@ -38391,7 +38391,7 @@
       </c>
       <c r="E600" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F600" s="5" t="inlineStr">
@@ -38401,12 +38401,12 @@
       </c>
       <c r="G600" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H600" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I600" s="5" t="b">
@@ -38417,7 +38417,7 @@
       </c>
       <c r="K600" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L600" s="5" t="n"/>
@@ -38425,24 +38425,24 @@
         <v>0</v>
       </c>
       <c r="N600" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O600" s="5" t="n">
-        <v>9.630000000000001</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C601" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D601" s="5" t="inlineStr">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="E601" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F601" s="5" t="inlineStr">
@@ -38462,12 +38462,12 @@
       </c>
       <c r="G601" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H601" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I601" s="5" t="b">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="K601" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L601" s="5" t="n"/>
@@ -38486,24 +38486,24 @@
         <v>0</v>
       </c>
       <c r="N601" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O601" s="5" t="n">
-        <v>9.76</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D602" s="5" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="E602" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F602" s="5" t="inlineStr">
@@ -38523,12 +38523,12 @@
       </c>
       <c r="G602" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H602" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I602" s="5" t="b">
@@ -38544,27 +38544,27 @@
       </c>
       <c r="L602" s="5" t="n"/>
       <c r="M602" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N602" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O602" s="5" t="n">
-        <v>13.87</v>
+        <v>13.88</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C603" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D603" s="5" t="inlineStr">
@@ -38574,7 +38574,7 @@
       </c>
       <c r="E603" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F603" s="5" t="inlineStr">
@@ -38584,12 +38584,12 @@
       </c>
       <c r="G603" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H603" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I603" s="5" t="b">
@@ -38605,27 +38605,27 @@
       </c>
       <c r="L603" s="5" t="n"/>
       <c r="M603" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N603" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O603" s="5" t="n">
-        <v>10.04</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
@@ -38635,7 +38635,7 @@
       </c>
       <c r="E604" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F604" s="5" t="inlineStr">
@@ -38645,12 +38645,12 @@
       </c>
       <c r="G604" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H604" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I604" s="5" t="b">
@@ -38666,19 +38666,19 @@
       </c>
       <c r="L604" s="5" t="n"/>
       <c r="M604" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N604" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O604" s="5" t="n">
-        <v>9.68</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B605" s="5" t="n">
@@ -38686,17 +38686,17 @@
       </c>
       <c r="C605" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D605" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E605" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F605" s="5" t="inlineStr">
@@ -38730,16 +38730,16 @@
         <v>0</v>
       </c>
       <c r="N605" s="5" t="n">
-        <v>0.0769</v>
+        <v>0.0213</v>
       </c>
       <c r="O605" s="5" t="n">
-        <v>13.66</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
@@ -38747,22 +38747,22 @@
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E606" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F606" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G606" s="5" t="inlineStr">
@@ -38791,16 +38791,16 @@
         <v>0</v>
       </c>
       <c r="N606" s="5" t="n">
-        <v>0.0769</v>
+        <v>0.0213</v>
       </c>
       <c r="O606" s="5" t="n">
-        <v>10.4</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
@@ -38808,12 +38808,12 @@
       </c>
       <c r="C607" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D607" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E607" s="5" t="inlineStr">
@@ -38823,7 +38823,7 @@
       </c>
       <c r="F607" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G607" s="5" t="inlineStr">
@@ -38852,16 +38852,16 @@
         <v>0</v>
       </c>
       <c r="N607" s="5" t="n">
-        <v>0.0769</v>
+        <v>0.0213</v>
       </c>
       <c r="O607" s="5" t="n">
-        <v>9.91</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_002</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
@@ -38869,12 +38869,12 @@
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E608" s="5" t="inlineStr">
@@ -38889,16 +38889,16 @@
       </c>
       <c r="G608" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H608" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I608" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J608" s="5" t="b">
         <v>1</v>
@@ -38913,16 +38913,16 @@
         <v>0</v>
       </c>
       <c r="N608" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0769</v>
       </c>
       <c r="O608" s="5" t="n">
-        <v>38.68</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_002</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
@@ -38930,27 +38930,27 @@
       </c>
       <c r="C609" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F609" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
@@ -38959,7 +38959,7 @@
         </is>
       </c>
       <c r="I609" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J609" s="5" t="b">
         <v>1</v>
@@ -38974,16 +38974,16 @@
         <v>0</v>
       </c>
       <c r="N609" s="5" t="n">
-        <v>0.1099</v>
+        <v>0.0769</v>
       </c>
       <c r="O609" s="5" t="n">
-        <v>12.81</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_002</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
@@ -38991,27 +38991,27 @@
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E610" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F610" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H610" s="5" t="inlineStr">
@@ -39020,7 +39020,7 @@
         </is>
       </c>
       <c r="I610" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J610" s="5" t="b">
         <v>1</v>
@@ -39035,14 +39035,1490 @@
         <v>0</v>
       </c>
       <c r="N610" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O610" s="5" t="n">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B611" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C611" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D611" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E611" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F611" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G611" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H611" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I611" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J611" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K611" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L611" s="5" t="n"/>
+      <c r="M611" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N611" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O611" s="5" t="n">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B612" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C612" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D612" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E612" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F612" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G612" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H612" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I612" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J612" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K612" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L612" s="5" t="n"/>
+      <c r="M612" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N612" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O612" s="5" t="n">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B613" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C613" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D613" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E613" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F613" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G613" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H613" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I613" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J613" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K613" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L613" s="5" t="n"/>
+      <c r="M613" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N613" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O613" s="5" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B614" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C614" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D614" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E614" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F614" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G614" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H614" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I614" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J614" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K614" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L614" s="5" t="n"/>
+      <c r="M614" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N614" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O614" s="5" t="n">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B615" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C615" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D615" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E615" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F615" s="5" t="inlineStr">
+        <is>
+          <t>few-shot</t>
+        </is>
+      </c>
+      <c r="G615" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H615" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I615" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J615" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K615" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L615" s="5" t="n"/>
+      <c r="M615" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N615" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O615" s="5" t="n">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3_001</t>
+        </is>
+      </c>
+      <c r="B616" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C616" s="5" t="inlineStr">
+        <is>
+          <t>group_aggregate_kg3</t>
+        </is>
+      </c>
+      <c r="D616" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E616" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F616" s="5" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="G616" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I616" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J616" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K616" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L616" s="5" t="n"/>
+      <c r="M616" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N616" s="5" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="O616" s="5" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_002</t>
+        </is>
+      </c>
+      <c r="B617" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D617" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E617" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F617" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G617" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H617" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I617" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J617" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K617" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L617" s="5" t="n"/>
+      <c r="M617" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N617" s="5" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="O617" s="5" t="n">
+        <v>38.95</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_002</t>
+        </is>
+      </c>
+      <c r="B618" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C618" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D618" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E618" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F618" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G618" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H618" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I618" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J618" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K618" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L618" s="5" t="n"/>
+      <c r="M618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N618" s="5" t="n">
         <v>0.1099</v>
       </c>
-      <c r="O610" s="5" t="n">
-        <v>12.27</v>
+      <c r="O618" s="5" t="n">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1_002</t>
+        </is>
+      </c>
+      <c r="B619" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="D619" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E619" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F619" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G619" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H619" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I619" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J619" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K619" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L619" s="5" t="n"/>
+      <c r="M619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N619" s="5" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="O619" s="5" t="n">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_002</t>
+        </is>
+      </c>
+      <c r="B620" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C620" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D620" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E620" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F620" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G620" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H620" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I620" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J620" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K620" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L620" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'department', 'property': 'memberOf', 'function': 'COUNT'}</t>
+        </is>
+      </c>
+      <c r="M620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O620" s="5" t="n">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_002</t>
+        </is>
+      </c>
+      <c r="B621" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C621" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D621" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E621" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F621" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G621" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H621" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I621" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J621" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K621" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L621" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'department', 'property': 'memberOf', 'function': 'COUNT'}</t>
+        </is>
+      </c>
+      <c r="M621" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N621" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O621" s="5" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3_002</t>
+        </is>
+      </c>
+      <c r="B622" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C622" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="D622" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E622" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F622" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G622" s="5" t="inlineStr">
+        <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H622" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I622" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J622" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K622" s="5" t="inlineStr">
+        <is>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L622" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'memberOf', 'function': 'COUNT'}</t>
+        </is>
+      </c>
+      <c r="M622" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N622" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O622" s="5" t="n">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_002</t>
+        </is>
+      </c>
+      <c r="B623" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C623" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D623" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E623" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F623" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G623" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H623" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I623" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J623" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K623" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L623" s="5" t="n"/>
+      <c r="M623" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N623" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O623" s="5" t="n">
+        <v>25.27</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_002</t>
+        </is>
+      </c>
+      <c r="B624" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C624" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D624" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E624" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G624" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H624" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I624" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J624" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K624" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L624" s="5" t="n"/>
+      <c r="M624" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N624" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O624" s="5" t="n">
+        <v>30.46</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_002</t>
+        </is>
+      </c>
+      <c r="B625" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C625" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D625" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E625" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F625" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G625" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H625" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I625" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J625" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K625" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L625" s="5" t="n"/>
+      <c r="M625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N625" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O625" s="5" t="n">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_003</t>
+        </is>
+      </c>
+      <c r="B626" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C626" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D626" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E626" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F626" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G626" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H626" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I626" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J626" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K626" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L626" s="5" t="n"/>
+      <c r="M626" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N626" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O626" s="5" t="n">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_003</t>
+        </is>
+      </c>
+      <c r="B627" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C627" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D627" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E627" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F627" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G627" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H627" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I627" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J627" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K627" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L627" s="5" t="n"/>
+      <c r="M627" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N627" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O627" s="5" t="n">
+        <v>12.58</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2_003</t>
+        </is>
+      </c>
+      <c r="B628" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C628" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="D628" s="5" t="inlineStr">
+        <is>
+          <t>airports</t>
+        </is>
+      </c>
+      <c r="E628" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F628" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G628" s="5" t="inlineStr">
+        <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H628" s="5" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="I628" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J628" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K628" s="5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L628" s="5" t="n"/>
+      <c r="M628" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N628" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O628" s="5" t="n">
+        <v>13.44</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_002</t>
+        </is>
+      </c>
+      <c r="B629" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C629" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D629" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E629" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F629" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G629" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H629" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I629" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J629" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K629" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L629" s="5" t="n"/>
+      <c r="M629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O629" s="5" t="n">
+        <v>67.06</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_002</t>
+        </is>
+      </c>
+      <c r="B630" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C630" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D630" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E630" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F630" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G630" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I630" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J630" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K630" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L630" s="5" t="n"/>
+      <c r="M630" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N630" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O630" s="5" t="n">
+        <v>53.87</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights_002</t>
+        </is>
+      </c>
+      <c r="B631" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C631" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="D631" s="5" t="inlineStr">
+        <is>
+          <t>flights</t>
+        </is>
+      </c>
+      <c r="E631" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F631" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G631" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_flights</t>
+        </is>
+      </c>
+      <c r="H631" s="5" t="inlineStr">
+        <is>
+          <t>open_kg</t>
+        </is>
+      </c>
+      <c r="I631" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J631" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K631" s="5" t="inlineStr">
+        <is>
+          <t>generation_failure</t>
+        </is>
+      </c>
+      <c r="L631" s="5" t="n"/>
+      <c r="M631" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N631" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O631" s="5" t="n">
+        <v>53.22</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments_002</t>
+        </is>
+      </c>
+      <c r="B632" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C632" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="D632" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E632" s="5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F632" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G632" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="H632" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I632" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J632" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K632" s="5" t="inlineStr">
+        <is>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L632" s="5" t="n"/>
+      <c r="M632" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N632" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O632" s="5" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments_002</t>
+        </is>
+      </c>
+      <c r="B633" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C633" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="D633" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E633" s="5" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F633" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G633" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="H633" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I633" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J633" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K633" s="5" t="inlineStr">
+        <is>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L633" s="5" t="n"/>
+      <c r="M633" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N633" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O633" s="5" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments_002</t>
+        </is>
+      </c>
+      <c r="B634" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C634" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="D634" s="5" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E634" s="5" t="inlineStr">
+        <is>
+          <t>ar</t>
+        </is>
+      </c>
+      <c r="F634" s="5" t="inlineStr">
+        <is>
+          <t>zero-shot</t>
+        </is>
+      </c>
+      <c r="G634" s="5" t="inlineStr">
+        <is>
+          <t>compare_two_departments</t>
+        </is>
+      </c>
+      <c r="H634" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
+      </c>
+      <c r="I634" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J634" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K634" s="5" t="inlineStr">
+        <is>
+          <t>mapping_failure</t>
+        </is>
+      </c>
+      <c r="L634" s="5" t="n"/>
+      <c r="M634" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N634" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O634" s="5" t="n">
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O610"/>
+  <autoFilter ref="A1:O634"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
@@ -30998,20 +30998,20 @@
     <row r="479">
       <c r="A479" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ask_query_005</t>
         </is>
       </c>
       <c r="B479" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C479" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E479" s="5" t="inlineStr">
@@ -31026,12 +31026,12 @@
       </c>
       <c r="G479" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H479" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I479" s="5" t="b">
@@ -31053,46 +31053,46 @@
         <v>1</v>
       </c>
       <c r="O479" s="5" t="n">
-        <v>9.029999999999999</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ask_query_005</t>
         </is>
       </c>
       <c r="B480" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C480" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E480" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F480" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I480" s="5" t="b">
@@ -31114,74 +31114,70 @@
         <v>1</v>
       </c>
       <c r="O480" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ask_query_005</t>
         </is>
       </c>
       <c r="B481" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C481" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F481" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G481" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H481" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I481" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J481" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K481" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>routing_miss</t>
         </is>
       </c>
       <c r="L481" s="5" t="n"/>
-      <c r="M481" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N481" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M481" s="5" t="n"/>
+      <c r="N481" s="5" t="n"/>
       <c r="O481" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg1_001</t>
         </is>
       </c>
       <c r="B482" s="5" t="n">
@@ -31189,17 +31185,17 @@
       </c>
       <c r="C482" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E482" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F482" s="5" t="inlineStr">
@@ -31209,16 +31205,16 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H482" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H482" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I482" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J482" s="5" t="b">
         <v>1</v>
@@ -31236,13 +31232,13 @@
         <v>1</v>
       </c>
       <c r="O482" s="5" t="n">
-        <v>9.19</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg1_001</t>
         </is>
       </c>
       <c r="B483" s="5" t="n">
@@ -31250,12 +31246,12 @@
       </c>
       <c r="C483" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E483" s="5" t="inlineStr">
@@ -31265,21 +31261,21 @@
       </c>
       <c r="F483" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
+          <t>ranking_kg1</t>
+        </is>
+      </c>
+      <c r="H483" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H483" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I483" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J483" s="5" t="b">
         <v>1</v>
@@ -31297,13 +31293,13 @@
         <v>1</v>
       </c>
       <c r="O483" s="5" t="n">
-        <v>8.18</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg1_001</t>
         </is>
       </c>
       <c r="B484" s="5" t="n">
@@ -31311,60 +31307,60 @@
       </c>
       <c r="C484" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E484" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F484" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G484" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="H484" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I484" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J484" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K484" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L484" s="5" t="n"/>
       <c r="M484" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N484" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O484" s="5" t="n">
-        <v>8.119999999999999</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B485" s="5" t="n">
@@ -31372,17 +31368,17 @@
       </c>
       <c r="C485" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F485" s="5" t="inlineStr">
@@ -31390,18 +31386,16 @@
           <t>zero-shot</t>
         </is>
       </c>
-      <c r="G485" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G485" s="5" t="n">
+        <v/>
       </c>
       <c r="H485" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I485" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J485" s="5" t="b">
         <v>1</v>
@@ -31419,13 +31413,13 @@
         <v>1</v>
       </c>
       <c r="O485" s="5" t="n">
-        <v>10.37</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B486" s="5" t="n">
@@ -31433,17 +31427,17 @@
       </c>
       <c r="C486" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E486" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F486" s="5" t="inlineStr">
@@ -31451,18 +31445,16 @@
           <t>few-shot</t>
         </is>
       </c>
-      <c r="G486" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G486" s="5" t="n">
+        <v/>
       </c>
       <c r="H486" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I486" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J486" s="5" t="b">
         <v>1</v>
@@ -31480,13 +31472,13 @@
         <v>1</v>
       </c>
       <c r="O486" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B487" s="5" t="n">
@@ -31494,17 +31486,17 @@
       </c>
       <c r="C487" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E487" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F487" s="5" t="inlineStr">
@@ -31512,18 +31504,16 @@
           <t>cot</t>
         </is>
       </c>
-      <c r="G487" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G487" s="5" t="n">
+        <v/>
       </c>
       <c r="H487" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I487" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J487" s="5" t="b">
         <v>1</v>
@@ -31541,13 +31531,13 @@
         <v>1</v>
       </c>
       <c r="O487" s="5" t="n">
-        <v>8.140000000000001</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B488" s="5" t="n">
@@ -31555,17 +31545,17 @@
       </c>
       <c r="C488" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E488" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F488" s="5" t="inlineStr">
@@ -31573,18 +31563,16 @@
           <t>zero-shot</t>
         </is>
       </c>
-      <c r="G488" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G488" s="5" t="n">
+        <v/>
       </c>
       <c r="H488" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I488" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J488" s="5" t="b">
         <v>1</v>
@@ -31602,13 +31590,13 @@
         <v>1</v>
       </c>
       <c r="O488" s="5" t="n">
-        <v>7.05</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B489" s="5" t="n">
@@ -31616,17 +31604,17 @@
       </c>
       <c r="C489" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E489" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F489" s="5" t="inlineStr">
@@ -31634,18 +31622,16 @@
           <t>few-shot</t>
         </is>
       </c>
-      <c r="G489" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G489" s="5" t="n">
+        <v/>
       </c>
       <c r="H489" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I489" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J489" s="5" t="b">
         <v>1</v>
@@ -31663,13 +31649,13 @@
         <v>1</v>
       </c>
       <c r="O489" s="5" t="n">
-        <v>7.84</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B490" s="5" t="n">
@@ -31677,17 +31663,17 @@
       </c>
       <c r="C490" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E490" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F490" s="5" t="inlineStr">
@@ -31695,18 +31681,16 @@
           <t>cot</t>
         </is>
       </c>
-      <c r="G490" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G490" s="5" t="n">
+        <v/>
       </c>
       <c r="H490" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I490" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J490" s="5" t="b">
         <v>1</v>
@@ -31724,13 +31708,13 @@
         <v>1</v>
       </c>
       <c r="O490" s="5" t="n">
-        <v>7.92</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B491" s="5" t="n">
@@ -31738,17 +31722,17 @@
       </c>
       <c r="C491" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E491" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F491" s="5" t="inlineStr">
@@ -31756,18 +31740,16 @@
           <t>zero-shot</t>
         </is>
       </c>
-      <c r="G491" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G491" s="5" t="n">
+        <v/>
       </c>
       <c r="H491" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I491" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J491" s="5" t="b">
         <v>1</v>
@@ -31785,13 +31767,13 @@
         <v>1</v>
       </c>
       <c r="O491" s="5" t="n">
-        <v>12.85</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B492" s="5" t="n">
@@ -31799,17 +31781,17 @@
       </c>
       <c r="C492" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E492" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F492" s="5" t="inlineStr">
@@ -31817,18 +31799,16 @@
           <t>few-shot</t>
         </is>
       </c>
-      <c r="G492" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G492" s="5" t="n">
+        <v/>
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I492" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J492" s="5" t="b">
         <v>1</v>
@@ -31846,13 +31826,13 @@
         <v>1</v>
       </c>
       <c r="O492" s="5" t="n">
-        <v>9.92</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_009</t>
         </is>
       </c>
       <c r="B493" s="5" t="n">
@@ -31860,17 +31840,17 @@
       </c>
       <c r="C493" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E493" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F493" s="5" t="inlineStr">
@@ -31878,18 +31858,16 @@
           <t>cot</t>
         </is>
       </c>
-      <c r="G493" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
+      <c r="G493" s="5" t="n">
+        <v/>
       </c>
       <c r="H493" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I493" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J493" s="5" t="b">
         <v>1</v>
@@ -31907,13 +31885,13 @@
         <v>1</v>
       </c>
       <c r="O493" s="5" t="n">
-        <v>10.22</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>count_kg2_001</t>
         </is>
       </c>
       <c r="B494" s="5" t="n">
@@ -31921,7 +31899,7 @@
       </c>
       <c r="C494" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D494" s="5" t="inlineStr">
@@ -31931,7 +31909,7 @@
       </c>
       <c r="E494" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F494" s="5" t="inlineStr">
@@ -31941,16 +31919,16 @@
       </c>
       <c r="G494" s="5" t="inlineStr">
         <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H494" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H494" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I494" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J494" s="5" t="b">
         <v>1</v>
@@ -31968,13 +31946,13 @@
         <v>1</v>
       </c>
       <c r="O494" s="5" t="n">
-        <v>12.16</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>count_kg2_001</t>
         </is>
       </c>
       <c r="B495" s="5" t="n">
@@ -31982,7 +31960,7 @@
       </c>
       <c r="C495" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D495" s="5" t="inlineStr">
@@ -31992,26 +31970,26 @@
       </c>
       <c r="E495" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F495" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G495" s="5" t="inlineStr">
         <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H495" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H495" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I495" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J495" s="5" t="b">
         <v>1</v>
@@ -32029,13 +32007,13 @@
         <v>1</v>
       </c>
       <c r="O495" s="5" t="n">
-        <v>10.6</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>count_kg2_001</t>
         </is>
       </c>
       <c r="B496" s="5" t="n">
@@ -32043,7 +32021,7 @@
       </c>
       <c r="C496" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D496" s="5" t="inlineStr">
@@ -32058,21 +32036,21 @@
       </c>
       <c r="F496" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G496" s="5" t="inlineStr">
         <is>
+          <t>count_kg2</t>
+        </is>
+      </c>
+      <c r="H496" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H496" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I496" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J496" s="5" t="b">
         <v>1</v>
@@ -32090,26 +32068,26 @@
         <v>1</v>
       </c>
       <c r="O496" s="5" t="n">
-        <v>10.95</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="5" t="inlineStr">
         <is>
-          <t>ask_query_005</t>
+          <t>compare_two_flights_001</t>
         </is>
       </c>
       <c r="B497" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C497" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E497" s="5" t="inlineStr">
@@ -32124,16 +32102,16 @@
       </c>
       <c r="G497" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="H497" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I497" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J497" s="5" t="b">
         <v>1</v>
@@ -32145,32 +32123,32 @@
       </c>
       <c r="L497" s="5" t="n"/>
       <c r="M497" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N497" s="5" t="n">
-        <v>1</v>
+        <v>0.2222</v>
       </c>
       <c r="O497" s="5" t="n">
-        <v>8.710000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="5" t="inlineStr">
         <is>
-          <t>ask_query_005</t>
+          <t>compare_two_flights_001</t>
         </is>
       </c>
       <c r="B498" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C498" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E498" s="5" t="inlineStr">
@@ -32185,16 +32163,16 @@
       </c>
       <c r="G498" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="H498" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I498" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J498" s="5" t="b">
         <v>1</v>
@@ -32206,32 +32184,32 @@
       </c>
       <c r="L498" s="5" t="n"/>
       <c r="M498" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N498" s="5" t="n">
-        <v>1</v>
+        <v>0.2222</v>
       </c>
       <c r="O498" s="5" t="n">
-        <v>5.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="5" t="inlineStr">
         <is>
-          <t>ask_query_005</t>
+          <t>compare_two_flights_001</t>
         </is>
       </c>
       <c r="B499" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C499" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E499" s="5" t="inlineStr">
@@ -32246,12 +32224,12 @@
       </c>
       <c r="G499" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="H499" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I499" s="5" t="b">
@@ -32262,33 +32240,37 @@
       </c>
       <c r="K499" s="5" t="inlineStr">
         <is>
-          <t>routing_miss</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L499" s="5" t="n"/>
-      <c r="M499" s="5" t="n"/>
-      <c r="N499" s="5" t="n"/>
+      <c r="M499" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N499" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O499" s="5" t="n">
-        <v>4.36</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_001</t>
+          <t>filter_numeric_kg3_002</t>
         </is>
       </c>
       <c r="B500" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C500" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E500" s="5" t="inlineStr">
@@ -32303,7 +32285,7 @@
       </c>
       <c r="G500" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="H500" s="5" t="inlineStr">
@@ -32324,32 +32306,32 @@
       </c>
       <c r="L500" s="5" t="n"/>
       <c r="M500" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N500" s="5" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="O500" s="5" t="n">
-        <v>10.87</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_001</t>
+          <t>filter_numeric_kg3_002</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C501" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E501" s="5" t="inlineStr">
@@ -32364,7 +32346,7 @@
       </c>
       <c r="G501" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="H501" s="5" t="inlineStr">
@@ -32385,32 +32367,32 @@
       </c>
       <c r="L501" s="5" t="n"/>
       <c r="M501" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N501" s="5" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="O501" s="5" t="n">
-        <v>7.81</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_001</t>
+          <t>filter_numeric_kg3_002</t>
         </is>
       </c>
       <c r="B502" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C502" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E502" s="5" t="inlineStr">
@@ -32425,23 +32407,23 @@
       </c>
       <c r="G502" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>filter_numeric_kg3</t>
         </is>
       </c>
       <c r="H502" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I502" s="5" t="b">
         <v>0</v>
       </c>
       <c r="J502" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K502" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L502" s="5" t="n"/>
@@ -32452,17 +32434,17 @@
         <v>0</v>
       </c>
       <c r="O502" s="5" t="n">
-        <v>32.62</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C503" s="5" t="inlineStr">
         <is>
@@ -32484,8 +32466,10 @@
           <t>zero-shot</t>
         </is>
       </c>
-      <c r="G503" s="5" t="n">
-        <v/>
+      <c r="G503" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H503" s="5" t="inlineStr">
         <is>
@@ -32493,7 +32477,7 @@
         </is>
       </c>
       <c r="I503" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J503" s="5" t="b">
         <v>1</v>
@@ -32511,17 +32495,17 @@
         <v>1</v>
       </c>
       <c r="O503" s="5" t="n">
-        <v>12.52</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B504" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C504" s="5" t="inlineStr">
         <is>
@@ -32543,8 +32527,10 @@
           <t>few-shot</t>
         </is>
       </c>
-      <c r="G504" s="5" t="n">
-        <v/>
+      <c r="G504" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H504" s="5" t="inlineStr">
         <is>
@@ -32552,7 +32538,7 @@
         </is>
       </c>
       <c r="I504" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J504" s="5" t="b">
         <v>1</v>
@@ -32570,17 +32556,17 @@
         <v>1</v>
       </c>
       <c r="O504" s="5" t="n">
-        <v>10.88</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C505" s="5" t="inlineStr">
         <is>
@@ -32602,8 +32588,10 @@
           <t>cot</t>
         </is>
       </c>
-      <c r="G505" s="5" t="n">
-        <v/>
+      <c r="G505" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H505" s="5" t="inlineStr">
         <is>
@@ -32611,7 +32599,7 @@
         </is>
       </c>
       <c r="I505" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J505" s="5" t="b">
         <v>1</v>
@@ -32635,11 +32623,11 @@
     <row r="506">
       <c r="A506" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B506" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C506" s="5" t="inlineStr">
         <is>
@@ -32661,8 +32649,10 @@
           <t>zero-shot</t>
         </is>
       </c>
-      <c r="G506" s="5" t="n">
-        <v/>
+      <c r="G506" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H506" s="5" t="inlineStr">
         <is>
@@ -32670,7 +32660,7 @@
         </is>
       </c>
       <c r="I506" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J506" s="5" t="b">
         <v>1</v>
@@ -32688,17 +32678,17 @@
         <v>1</v>
       </c>
       <c r="O506" s="5" t="n">
-        <v>12.3</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C507" s="5" t="inlineStr">
         <is>
@@ -32720,8 +32710,10 @@
           <t>few-shot</t>
         </is>
       </c>
-      <c r="G507" s="5" t="n">
-        <v/>
+      <c r="G507" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H507" s="5" t="inlineStr">
         <is>
@@ -32729,7 +32721,7 @@
         </is>
       </c>
       <c r="I507" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J507" s="5" t="b">
         <v>1</v>
@@ -32747,17 +32739,17 @@
         <v>1</v>
       </c>
       <c r="O507" s="5" t="n">
-        <v>12.02</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B508" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C508" s="5" t="inlineStr">
         <is>
@@ -32779,8 +32771,10 @@
           <t>cot</t>
         </is>
       </c>
-      <c r="G508" s="5" t="n">
-        <v/>
+      <c r="G508" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H508" s="5" t="inlineStr">
         <is>
@@ -32788,7 +32782,7 @@
         </is>
       </c>
       <c r="I508" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J508" s="5" t="b">
         <v>1</v>
@@ -32812,11 +32806,11 @@
     <row r="509">
       <c r="A509" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C509" s="5" t="inlineStr">
         <is>
@@ -32838,8 +32832,10 @@
           <t>zero-shot</t>
         </is>
       </c>
-      <c r="G509" s="5" t="n">
-        <v/>
+      <c r="G509" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H509" s="5" t="inlineStr">
         <is>
@@ -32847,7 +32843,7 @@
         </is>
       </c>
       <c r="I509" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J509" s="5" t="b">
         <v>1</v>
@@ -32865,17 +32861,17 @@
         <v>1</v>
       </c>
       <c r="O509" s="5" t="n">
-        <v>13.62</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B510" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C510" s="5" t="inlineStr">
         <is>
@@ -32897,8 +32893,10 @@
           <t>few-shot</t>
         </is>
       </c>
-      <c r="G510" s="5" t="n">
-        <v/>
+      <c r="G510" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H510" s="5" t="inlineStr">
         <is>
@@ -32906,7 +32904,7 @@
         </is>
       </c>
       <c r="I510" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J510" s="5" t="b">
         <v>1</v>
@@ -32924,17 +32922,17 @@
         <v>1</v>
       </c>
       <c r="O510" s="5" t="n">
-        <v>12.2</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_009</t>
+          <t>single_kg3_010</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C511" s="5" t="inlineStr">
         <is>
@@ -32956,8 +32954,10 @@
           <t>cot</t>
         </is>
       </c>
-      <c r="G511" s="5" t="n">
-        <v/>
+      <c r="G511" s="5" t="inlineStr">
+        <is>
+          <t>single_kg3</t>
+        </is>
       </c>
       <c r="H511" s="5" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         </is>
       </c>
       <c r="I511" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J511" s="5" t="b">
         <v>1</v>
@@ -32983,26 +32983,26 @@
         <v>1</v>
       </c>
       <c r="O511" s="5" t="n">
-        <v>12.68</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_001</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B512" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C512" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E512" s="5" t="inlineStr">
@@ -33017,16 +33017,16 @@
       </c>
       <c r="G512" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H512" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I512" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J512" s="5" t="b">
         <v>1</v>
@@ -33044,50 +33044,50 @@
         <v>1</v>
       </c>
       <c r="O512" s="5" t="n">
-        <v>10.49</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_001</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C513" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E513" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F513" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G513" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H513" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I513" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J513" s="5" t="b">
         <v>1</v>
@@ -33105,50 +33105,50 @@
         <v>1</v>
       </c>
       <c r="O513" s="5" t="n">
-        <v>11.38</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_001</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B514" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C514" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E514" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F514" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G514" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H514" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I514" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J514" s="5" t="b">
         <v>1</v>
@@ -33166,31 +33166,31 @@
         <v>1</v>
       </c>
       <c r="O514" s="5" t="n">
-        <v>11.19</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights_001</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C515" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E515" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F515" s="5" t="inlineStr">
@@ -33200,16 +33200,16 @@
       </c>
       <c r="G515" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H515" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I515" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J515" s="5" t="b">
         <v>1</v>
@@ -33221,32 +33221,32 @@
       </c>
       <c r="L515" s="5" t="n"/>
       <c r="M515" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N515" s="5" t="n">
-        <v>0.2222</v>
+        <v>1</v>
       </c>
       <c r="O515" s="5" t="n">
-        <v>0.02</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights_001</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B516" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C516" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E516" s="5" t="inlineStr">
@@ -33256,21 +33256,21 @@
       </c>
       <c r="F516" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G516" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H516" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I516" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J516" s="5" t="b">
         <v>1</v>
@@ -33282,80 +33282,80 @@
       </c>
       <c r="L516" s="5" t="n"/>
       <c r="M516" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N516" s="5" t="n">
-        <v>0.2222</v>
+        <v>1</v>
       </c>
       <c r="O516" s="5" t="n">
-        <v>0.02</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights_001</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C517" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E517" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F517" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G517" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H517" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I517" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J517" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K517" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L517" s="5" t="n"/>
       <c r="M517" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N517" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O517" s="5" t="n">
-        <v>59.2</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3_002</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B518" s="5" t="n">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="C518" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D518" s="5" t="inlineStr">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="E518" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F518" s="5" t="inlineStr">
@@ -33383,16 +33383,16 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I518" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J518" s="5" t="b">
         <v>1</v>
@@ -33404,19 +33404,19 @@
       </c>
       <c r="L518" s="5" t="n"/>
       <c r="M518" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N518" s="5" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="O518" s="5" t="n">
-        <v>0.09</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3_002</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="C519" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D519" s="5" t="inlineStr">
@@ -33434,26 +33434,26 @@
       </c>
       <c r="E519" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F519" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G519" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H519" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I519" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J519" s="5" t="b">
         <v>1</v>
@@ -33465,19 +33465,19 @@
       </c>
       <c r="L519" s="5" t="n"/>
       <c r="M519" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N519" s="5" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="O519" s="5" t="n">
-        <v>1.92</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3_002</t>
+          <t>single_kg3_011</t>
         </is>
       </c>
       <c r="B520" s="5" t="n">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="C520" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D520" s="5" t="inlineStr">
@@ -33500,21 +33500,21 @@
       </c>
       <c r="F520" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G520" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H520" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I520" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J520" s="5" t="b">
         <v>1</v>
@@ -33526,19 +33526,19 @@
       </c>
       <c r="L520" s="5" t="n"/>
       <c r="M520" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N520" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O520" s="5" t="n">
-        <v>6.53</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
@@ -33593,13 +33593,13 @@
         <v>1</v>
       </c>
       <c r="O521" s="5" t="n">
-        <v>12.81</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B522" s="5" t="n">
@@ -33654,13 +33654,13 @@
         <v>1</v>
       </c>
       <c r="O522" s="5" t="n">
-        <v>10.11</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
@@ -33715,13 +33715,13 @@
         <v>1</v>
       </c>
       <c r="O523" s="5" t="n">
-        <v>10.87</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B524" s="5" t="n">
@@ -33776,13 +33776,13 @@
         <v>1</v>
       </c>
       <c r="O524" s="5" t="n">
-        <v>10.46</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
@@ -33837,13 +33837,13 @@
         <v>1</v>
       </c>
       <c r="O525" s="5" t="n">
-        <v>11.59</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B526" s="5" t="n">
@@ -33898,13 +33898,13 @@
         <v>1</v>
       </c>
       <c r="O526" s="5" t="n">
-        <v>12.11</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
@@ -33959,13 +33959,13 @@
         <v>1</v>
       </c>
       <c r="O527" s="5" t="n">
-        <v>11.78</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B528" s="5" t="n">
@@ -34020,13 +34020,13 @@
         <v>1</v>
       </c>
       <c r="O528" s="5" t="n">
-        <v>11.45</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_010</t>
+          <t>single_kg3_012</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
@@ -34081,13 +34081,13 @@
         <v>1</v>
       </c>
       <c r="O529" s="5" t="n">
-        <v>11.68</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B530" s="5" t="n">
@@ -34142,13 +34142,13 @@
         <v>1</v>
       </c>
       <c r="O530" s="5" t="n">
-        <v>11.34</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
@@ -34203,13 +34203,13 @@
         <v>1</v>
       </c>
       <c r="O531" s="5" t="n">
-        <v>10.07</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
@@ -34264,13 +34264,13 @@
         <v>1</v>
       </c>
       <c r="O532" s="5" t="n">
-        <v>10.28</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
@@ -34314,24 +34314,24 @@
       </c>
       <c r="K533" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L533" s="5" t="n"/>
       <c r="M533" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N533" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O533" s="5" t="n">
-        <v>9.710000000000001</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B534" s="5" t="n">
@@ -34375,24 +34375,24 @@
       </c>
       <c r="K534" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L534" s="5" t="n"/>
       <c r="M534" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N534" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O534" s="5" t="n">
-        <v>12.29</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
@@ -34436,24 +34436,24 @@
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>no_results</t>
         </is>
       </c>
       <c r="L535" s="5" t="n"/>
       <c r="M535" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N535" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O535" s="5" t="n">
-        <v>11.78</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B536" s="5" t="n">
@@ -34514,7 +34514,7 @@
     <row r="537">
       <c r="A537" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
@@ -34569,13 +34569,13 @@
         <v>1</v>
       </c>
       <c r="O537" s="5" t="n">
-        <v>12.37</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_011</t>
+          <t>single_kg3_013</t>
         </is>
       </c>
       <c r="B538" s="5" t="n">
@@ -34630,26 +34630,26 @@
         <v>1</v>
       </c>
       <c r="O538" s="5" t="n">
-        <v>13.13</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>ranking_kg1_002</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C539" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E539" s="5" t="inlineStr">
@@ -34664,16 +34664,16 @@
       </c>
       <c r="G539" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="H539" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I539" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J539" s="5" t="b">
         <v>1</v>
@@ -34685,56 +34685,56 @@
       </c>
       <c r="L539" s="5" t="n"/>
       <c r="M539" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N539" s="5" t="n">
-        <v>1</v>
+        <v>0.093</v>
       </c>
       <c r="O539" s="5" t="n">
-        <v>13.22</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>ranking_kg1_002</t>
         </is>
       </c>
       <c r="B540" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C540" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E540" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F540" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G540" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="H540" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I540" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J540" s="5" t="b">
         <v>1</v>
@@ -34746,56 +34746,56 @@
       </c>
       <c r="L540" s="5" t="n"/>
       <c r="M540" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N540" s="5" t="n">
-        <v>1</v>
+        <v>0.1099</v>
       </c>
       <c r="O540" s="5" t="n">
-        <v>11.8</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>ranking_kg1_002</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C541" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E541" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F541" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G541" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ranking_kg1</t>
         </is>
       </c>
       <c r="H541" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I541" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J541" s="5" t="b">
         <v>1</v>
@@ -34807,37 +34807,37 @@
       </c>
       <c r="L541" s="5" t="n"/>
       <c r="M541" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N541" s="5" t="n">
-        <v>1</v>
+        <v>0.093</v>
       </c>
       <c r="O541" s="5" t="n">
-        <v>11.43</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>count_kg2_003</t>
         </is>
       </c>
       <c r="B542" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C542" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E542" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F542" s="5" t="inlineStr">
@@ -34847,16 +34847,16 @@
       </c>
       <c r="G542" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="H542" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I542" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J542" s="5" t="b">
         <v>1</v>
@@ -34874,26 +34874,26 @@
         <v>1</v>
       </c>
       <c r="O542" s="5" t="n">
-        <v>13.92</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>count_kg2_003</t>
         </is>
       </c>
       <c r="B543" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C543" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E543" s="5" t="inlineStr">
@@ -34903,21 +34903,21 @@
       </c>
       <c r="F543" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G543" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="H543" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I543" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J543" s="5" t="b">
         <v>1</v>
@@ -34935,50 +34935,50 @@
         <v>1</v>
       </c>
       <c r="O543" s="5" t="n">
-        <v>13.72</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>count_kg2_003</t>
         </is>
       </c>
       <c r="B544" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C544" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E544" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F544" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G544" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="H544" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I544" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J544" s="5" t="b">
         <v>1</v>
@@ -34996,31 +34996,31 @@
         <v>1</v>
       </c>
       <c r="O544" s="5" t="n">
-        <v>14.29</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>compare_two_flights_002</t>
         </is>
       </c>
       <c r="B545" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C545" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E545" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F545" s="5" t="inlineStr">
@@ -35030,16 +35030,16 @@
       </c>
       <c r="G545" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="H545" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I545" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J545" s="5" t="b">
         <v>1</v>
@@ -35051,56 +35051,56 @@
       </c>
       <c r="L545" s="5" t="n"/>
       <c r="M545" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N545" s="5" t="n">
-        <v>1</v>
+        <v>0.2222</v>
       </c>
       <c r="O545" s="5" t="n">
-        <v>17.69</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>compare_two_flights_002</t>
         </is>
       </c>
       <c r="B546" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C546" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E546" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F546" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G546" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="H546" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I546" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J546" s="5" t="b">
         <v>1</v>
@@ -35112,32 +35112,32 @@
       </c>
       <c r="L546" s="5" t="n"/>
       <c r="M546" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N546" s="5" t="n">
-        <v>1</v>
+        <v>0.2222</v>
       </c>
       <c r="O546" s="5" t="n">
-        <v>13.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_012</t>
+          <t>compare_two_flights_002</t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C547" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E547" s="5" t="inlineStr">
@@ -35147,58 +35147,58 @@
       </c>
       <c r="F547" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G547" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>compare_two_flights</t>
         </is>
       </c>
       <c r="H547" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I547" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J547" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K547" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>generation_failure</t>
         </is>
       </c>
       <c r="L547" s="5" t="n"/>
       <c r="M547" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N547" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O547" s="5" t="n">
-        <v>13.01</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>count_kg2_002</t>
         </is>
       </c>
       <c r="B548" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C548" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E548" s="5" t="inlineStr">
@@ -35213,16 +35213,16 @@
       </c>
       <c r="G548" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="H548" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I548" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J548" s="5" t="b">
         <v>1</v>
@@ -35234,56 +35234,56 @@
       </c>
       <c r="L548" s="5" t="n"/>
       <c r="M548" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N548" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O548" s="5" t="n">
-        <v>10.97</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>count_kg2_002</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C549" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E549" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F549" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G549" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="H549" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I549" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J549" s="5" t="b">
         <v>1</v>
@@ -35295,56 +35295,56 @@
       </c>
       <c r="L549" s="5" t="n"/>
       <c r="M549" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N549" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O549" s="5" t="n">
-        <v>9.77</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>count_kg2_002</t>
         </is>
       </c>
       <c r="B550" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C550" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E550" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F550" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G550" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>count_kg2</t>
         </is>
       </c>
       <c r="H550" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I550" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J550" s="5" t="b">
         <v>1</v>
@@ -35356,37 +35356,37 @@
       </c>
       <c r="L550" s="5" t="n"/>
       <c r="M550" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N550" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O550" s="5" t="n">
-        <v>10.45</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C551" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E551" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F551" s="5" t="inlineStr">
@@ -35396,12 +35396,12 @@
       </c>
       <c r="G551" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H551" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I551" s="5" t="b">
@@ -35412,37 +35412,37 @@
       </c>
       <c r="K551" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L551" s="5" t="n"/>
       <c r="M551" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N551" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O551" s="5" t="n">
-        <v>11.65</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B552" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C552" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E552" s="5" t="inlineStr">
@@ -35452,17 +35452,17 @@
       </c>
       <c r="F552" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G552" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H552" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I552" s="5" t="b">
@@ -35473,57 +35473,57 @@
       </c>
       <c r="K552" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L552" s="5" t="n"/>
       <c r="M552" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N552" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O552" s="5" t="n">
-        <v>11.18</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>filter_numeric_kg2_001</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C553" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E553" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F553" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I553" s="5" t="b">
@@ -35534,42 +35534,42 @@
       </c>
       <c r="K553" s="5" t="inlineStr">
         <is>
-          <t>no_results</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L553" s="5" t="n"/>
       <c r="M553" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N553" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O553" s="5" t="n">
-        <v>12.79</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B554" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C554" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E554" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F554" s="5" t="inlineStr">
@@ -35579,12 +35579,12 @@
       </c>
       <c r="G554" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H554" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I554" s="5" t="b">
@@ -35600,52 +35600,52 @@
       </c>
       <c r="L554" s="5" t="n"/>
       <c r="M554" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N554" s="5" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="O554" s="5" t="n">
-        <v>13.19</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C555" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E555" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F555" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G555" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H555" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I555" s="5" t="b">
@@ -35661,32 +35661,32 @@
       </c>
       <c r="L555" s="5" t="n"/>
       <c r="M555" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N555" s="5" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="O555" s="5" t="n">
-        <v>12.1</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_013</t>
+          <t>filter_numeric_kg2_002</t>
         </is>
       </c>
       <c r="B556" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C556" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E556" s="5" t="inlineStr">
@@ -35696,17 +35696,17 @@
       </c>
       <c r="F556" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G556" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H556" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I556" s="5" t="b">
@@ -35722,19 +35722,19 @@
       </c>
       <c r="L556" s="5" t="n"/>
       <c r="M556" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N556" s="5" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="O556" s="5" t="n">
-        <v>11.65</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
@@ -35742,12 +35742,12 @@
       </c>
       <c r="C557" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E557" s="5" t="inlineStr">
@@ -35783,19 +35783,19 @@
       </c>
       <c r="L557" s="5" t="n"/>
       <c r="M557" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N557" s="5" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="O557" s="5" t="n">
-        <v>9.56</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B558" s="5" t="n">
@@ -35803,12 +35803,12 @@
       </c>
       <c r="C558" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D558" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E558" s="5" t="inlineStr">
@@ -35844,19 +35844,19 @@
       </c>
       <c r="L558" s="5" t="n"/>
       <c r="M558" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N558" s="5" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="O558" s="5" t="n">
-        <v>14</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1_001</t>
+          <t>filter_numeric_kg2_003</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
@@ -35864,12 +35864,12 @@
       </c>
       <c r="C559" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg1</t>
+          <t>filter_numeric_kg2</t>
         </is>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E559" s="5" t="inlineStr">
@@ -35905,19 +35905,19 @@
       </c>
       <c r="L559" s="5" t="n"/>
       <c r="M559" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N559" s="5" t="n">
-        <v>0.0213</v>
+        <v>1</v>
       </c>
       <c r="O559" s="5" t="n">
-        <v>12.69</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>ranking_kg3_002</t>
         </is>
       </c>
       <c r="B560" s="5" t="n">
@@ -35925,7 +35925,7 @@
       </c>
       <c r="C560" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D560" s="5" t="inlineStr">
@@ -35945,40 +35945,44 @@
       </c>
       <c r="G560" s="5" t="inlineStr">
         <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H560" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H560" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I560" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J560" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K560" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L560" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L560" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'memberOf', 'function': 'COUNT', 'group_by': 'department'}</t>
+        </is>
+      </c>
       <c r="M560" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N560" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O560" s="5" t="n">
-        <v>10.48</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>ranking_kg3_002</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
@@ -35986,7 +35990,7 @@
       </c>
       <c r="C561" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D561" s="5" t="inlineStr">
@@ -35996,50 +36000,54 @@
       </c>
       <c r="E561" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F561" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G561" s="5" t="inlineStr">
         <is>
+          <t>ranking_kg3</t>
+        </is>
+      </c>
+      <c r="H561" s="5" t="inlineStr">
+        <is>
           <t>template</t>
         </is>
       </c>
-      <c r="H561" s="5" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
       <c r="I561" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J561" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K561" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L561" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L561" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'memberOf', 'function': 'COUNT', 'group_by': 'department'}</t>
+        </is>
+      </c>
       <c r="M561" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N561" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O561" s="5" t="n">
-        <v>8.43</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>ranking_kg3_002</t>
         </is>
       </c>
       <c r="B562" s="5" t="n">
@@ -36047,7 +36055,7 @@
       </c>
       <c r="C562" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D562" s="5" t="inlineStr">
@@ -36057,17 +36065,17 @@
       </c>
       <c r="E562" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F562" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G562" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H562" s="5" t="inlineStr">
@@ -36091,16 +36099,16 @@
         <v>0</v>
       </c>
       <c r="N562" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O562" s="5" t="n">
-        <v>8.19</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>compare_two_departments_002</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
@@ -36108,7 +36116,7 @@
       </c>
       <c r="C563" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>compare_two_departments</t>
         </is>
       </c>
       <c r="D563" s="5" t="inlineStr">
@@ -36118,7 +36126,7 @@
       </c>
       <c r="E563" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F563" s="5" t="inlineStr">
@@ -36128,7 +36136,7 @@
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>compare_two_departments</t>
         </is>
       </c>
       <c r="H563" s="5" t="inlineStr">
@@ -36149,19 +36157,19 @@
       </c>
       <c r="L563" s="5" t="n"/>
       <c r="M563" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N563" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O563" s="5" t="n">
-        <v>10.62</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>compare_two_departments_002</t>
         </is>
       </c>
       <c r="B564" s="5" t="n">
@@ -36169,7 +36177,7 @@
       </c>
       <c r="C564" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>compare_two_departments</t>
         </is>
       </c>
       <c r="D564" s="5" t="inlineStr">
@@ -36184,12 +36192,12 @@
       </c>
       <c r="F564" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>compare_two_departments</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
@@ -36210,19 +36218,19 @@
       </c>
       <c r="L564" s="5" t="n"/>
       <c r="M564" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N564" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O564" s="5" t="n">
-        <v>7.41</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>compare_two_departments_002</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
@@ -36230,7 +36238,7 @@
       </c>
       <c r="C565" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>compare_two_departments</t>
         </is>
       </c>
       <c r="D565" s="5" t="inlineStr">
@@ -36240,17 +36248,17 @@
       </c>
       <c r="E565" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F565" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G565" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>compare_two_departments</t>
         </is>
       </c>
       <c r="H565" s="5" t="inlineStr">
@@ -36271,19 +36279,19 @@
       </c>
       <c r="L565" s="5" t="n"/>
       <c r="M565" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N565" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O565" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>filter_string_kg3_002</t>
         </is>
       </c>
       <c r="B566" s="5" t="n">
@@ -36291,7 +36299,7 @@
       </c>
       <c r="C566" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D566" s="5" t="inlineStr">
@@ -36301,7 +36309,7 @@
       </c>
       <c r="E566" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F566" s="5" t="inlineStr">
@@ -36332,19 +36340,19 @@
       </c>
       <c r="L566" s="5" t="n"/>
       <c r="M566" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N566" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O566" s="5" t="n">
-        <v>10.2</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>filter_string_kg3_002</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
@@ -36352,7 +36360,7 @@
       </c>
       <c r="C567" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D567" s="5" t="inlineStr">
@@ -36362,12 +36370,12 @@
       </c>
       <c r="E567" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F567" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G567" s="5" t="inlineStr">
@@ -36393,19 +36401,19 @@
       </c>
       <c r="L567" s="5" t="n"/>
       <c r="M567" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N567" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O567" s="5" t="n">
-        <v>8.26</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3_001</t>
+          <t>filter_string_kg3_002</t>
         </is>
       </c>
       <c r="B568" s="5" t="n">
@@ -36413,7 +36421,7 @@
       </c>
       <c r="C568" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg3</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D568" s="5" t="inlineStr">
@@ -36428,7 +36436,7 @@
       </c>
       <c r="F568" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G568" s="5" t="inlineStr">
@@ -36454,32 +36462,32 @@
       </c>
       <c r="L568" s="5" t="n"/>
       <c r="M568" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N568" s="5" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="O568" s="5" t="n">
-        <v>8.41</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B569" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C569" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E569" s="5" t="inlineStr">
@@ -36494,7 +36502,7 @@
       </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H569" s="5" t="inlineStr">
@@ -36503,7 +36511,7 @@
         </is>
       </c>
       <c r="I569" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J569" s="5" t="b">
         <v>1</v>
@@ -36518,29 +36526,29 @@
         <v>0</v>
       </c>
       <c r="N569" s="5" t="n">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="O569" s="5" t="n">
-        <v>10.18</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B570" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C570" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E570" s="5" t="inlineStr">
@@ -36555,16 +36563,16 @@
       </c>
       <c r="G570" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H570" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I570" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J570" s="5" t="b">
         <v>1</v>
@@ -36576,32 +36584,32 @@
       </c>
       <c r="L570" s="5" t="n"/>
       <c r="M570" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N570" s="5" t="n">
-        <v>0.1099</v>
+        <v>1</v>
       </c>
       <c r="O570" s="5" t="n">
-        <v>12.32</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1_002</t>
+          <t>property_ambiguity_004</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C571" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>property_ambiguity</t>
         </is>
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E571" s="5" t="inlineStr">
@@ -36616,16 +36624,16 @@
       </c>
       <c r="G571" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg1</t>
+          <t>VARIES</t>
         </is>
       </c>
       <c r="H571" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I571" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J571" s="5" t="b">
         <v>1</v>
@@ -36637,32 +36645,32 @@
       </c>
       <c r="L571" s="5" t="n"/>
       <c r="M571" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N571" s="5" t="n">
-        <v>0.093</v>
+        <v>1</v>
       </c>
       <c r="O571" s="5" t="n">
-        <v>10.61</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_003</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B572" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C572" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E572" s="5" t="inlineStr">
@@ -36677,16 +36685,16 @@
       </c>
       <c r="G572" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H572" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I572" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J572" s="5" t="b">
         <v>1</v>
@@ -36704,50 +36712,50 @@
         <v>1</v>
       </c>
       <c r="O572" s="5" t="n">
-        <v>13.41</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_003</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F573" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G573" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H573" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I573" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J573" s="5" t="b">
         <v>1</v>
@@ -36765,50 +36773,50 @@
         <v>1</v>
       </c>
       <c r="O573" s="5" t="n">
-        <v>12.99</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_003</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B574" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C574" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E574" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F574" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G574" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H574" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I574" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J574" s="5" t="b">
         <v>1</v>
@@ -36826,31 +36834,31 @@
         <v>1</v>
       </c>
       <c r="O574" s="5" t="n">
-        <v>14.64</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights_002</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C575" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E575" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F575" s="5" t="inlineStr">
@@ -36860,16 +36868,16 @@
       </c>
       <c r="G575" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H575" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I575" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J575" s="5" t="b">
         <v>1</v>
@@ -36881,32 +36889,32 @@
       </c>
       <c r="L575" s="5" t="n"/>
       <c r="M575" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N575" s="5" t="n">
-        <v>0.2222</v>
+        <v>1</v>
       </c>
       <c r="O575" s="5" t="n">
-        <v>0.02</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights_002</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B576" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C576" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E576" s="5" t="inlineStr">
@@ -36916,21 +36924,21 @@
       </c>
       <c r="F576" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G576" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H576" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I576" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J576" s="5" t="b">
         <v>1</v>
@@ -36942,98 +36950,98 @@
       </c>
       <c r="L576" s="5" t="n"/>
       <c r="M576" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N576" s="5" t="n">
-        <v>0.2222</v>
+        <v>1</v>
       </c>
       <c r="O576" s="5" t="n">
-        <v>0.01</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights_002</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B577" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C577" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E577" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F577" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G577" s="5" t="inlineStr">
         <is>
-          <t>compare_two_flights</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H577" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I577" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J577" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K577" s="5" t="inlineStr">
         <is>
-          <t>generation_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L577" s="5" t="n"/>
       <c r="M577" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N577" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O577" s="5" t="n">
-        <v>55.53</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_002</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C578" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E578" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F578" s="5" t="inlineStr">
@@ -37043,16 +37051,16 @@
       </c>
       <c r="G578" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H578" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I578" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J578" s="5" t="b">
         <v>1</v>
@@ -37064,56 +37072,56 @@
       </c>
       <c r="L578" s="5" t="n"/>
       <c r="M578" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N578" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O578" s="5" t="n">
-        <v>15.08</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_002</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C579" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E579" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F579" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G579" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H579" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I579" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J579" s="5" t="b">
         <v>1</v>
@@ -37125,32 +37133,32 @@
       </c>
       <c r="L579" s="5" t="n"/>
       <c r="M579" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N579" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O579" s="5" t="n">
-        <v>14.64</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="5" t="inlineStr">
         <is>
-          <t>count_kg2_002</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E580" s="5" t="inlineStr">
@@ -37160,21 +37168,21 @@
       </c>
       <c r="F580" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G580" s="5" t="inlineStr">
         <is>
-          <t>count_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H580" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I580" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J580" s="5" t="b">
         <v>1</v>
@@ -37186,19 +37194,19 @@
       </c>
       <c r="L580" s="5" t="n"/>
       <c r="M580" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N580" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O580" s="5" t="n">
-        <v>13.38</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -37206,12 +37214,12 @@
       </c>
       <c r="C581" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E581" s="5" t="inlineStr">
@@ -37253,13 +37261,13 @@
         <v>1</v>
       </c>
       <c r="O581" s="5" t="n">
-        <v>17.19</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
@@ -37267,22 +37275,22 @@
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E582" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F582" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G582" s="5" t="inlineStr">
@@ -37314,13 +37322,13 @@
         <v>1</v>
       </c>
       <c r="O582" s="5" t="n">
-        <v>13.43</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_001</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
@@ -37328,22 +37336,22 @@
       </c>
       <c r="C583" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D583" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E583" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F583" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G583" s="5" t="inlineStr">
@@ -37375,13 +37383,13 @@
         <v>1</v>
       </c>
       <c r="O583" s="5" t="n">
-        <v>14.81</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
@@ -37389,17 +37397,17 @@
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E584" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F584" s="5" t="inlineStr">
@@ -37430,19 +37438,19 @@
       </c>
       <c r="L584" s="5" t="n"/>
       <c r="M584" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N584" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1</v>
       </c>
       <c r="O584" s="5" t="n">
-        <v>11.52</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
@@ -37450,12 +37458,12 @@
       </c>
       <c r="C585" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D585" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E585" s="5" t="inlineStr">
@@ -37465,7 +37473,7 @@
       </c>
       <c r="F585" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G585" s="5" t="inlineStr">
@@ -37491,19 +37499,19 @@
       </c>
       <c r="L585" s="5" t="n"/>
       <c r="M585" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N585" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1</v>
       </c>
       <c r="O585" s="5" t="n">
-        <v>10.61</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_002</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
@@ -37511,22 +37519,22 @@
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E586" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F586" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G586" s="5" t="inlineStr">
@@ -37552,19 +37560,19 @@
       </c>
       <c r="L586" s="5" t="n"/>
       <c r="M586" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N586" s="5" t="n">
-        <v>0.9772999999999999</v>
+        <v>1</v>
       </c>
       <c r="O586" s="5" t="n">
-        <v>13.07</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -37572,17 +37580,17 @@
       </c>
       <c r="C587" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E587" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F587" s="5" t="inlineStr">
@@ -37619,13 +37627,13 @@
         <v>1</v>
       </c>
       <c r="O587" s="5" t="n">
-        <v>14.46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
@@ -37633,22 +37641,22 @@
       </c>
       <c r="C588" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D588" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E588" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F588" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G588" s="5" t="inlineStr">
@@ -37680,13 +37688,13 @@
         <v>1</v>
       </c>
       <c r="O588" s="5" t="n">
-        <v>13.74</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2_003</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B589" s="5" t="n">
@@ -37694,12 +37702,12 @@
       </c>
       <c r="C589" s="5" t="inlineStr">
         <is>
-          <t>filter_numeric_kg2</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E589" s="5" t="inlineStr">
@@ -37709,7 +37717,7 @@
       </c>
       <c r="F589" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G589" s="5" t="inlineStr">
@@ -37741,26 +37749,26 @@
         <v>1</v>
       </c>
       <c r="O589" s="5" t="n">
-        <v>14.59</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C590" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D590" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E590" s="5" t="inlineStr">
@@ -37775,7 +37783,7 @@
       </c>
       <c r="G590" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H590" s="5" t="inlineStr">
@@ -37784,59 +37792,63 @@
         </is>
       </c>
       <c r="I590" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J590" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K590" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L590" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L590" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M590" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N590" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O590" s="5" t="n">
-        <v>14.96</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C591" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D591" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E591" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F591" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G591" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H591" s="5" t="inlineStr">
@@ -37845,59 +37857,63 @@
         </is>
       </c>
       <c r="I591" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J591" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K591" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L591" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L591" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M591" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N591" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O591" s="5" t="n">
-        <v>13.46</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C592" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D592" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E592" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F592" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G592" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H592" s="5" t="inlineStr">
@@ -37906,49 +37922,53 @@
         </is>
       </c>
       <c r="I592" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J592" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K592" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L592" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L592" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M592" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N592" s="5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O592" s="5" t="n">
-        <v>13.83</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C593" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D593" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E593" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F593" s="5" t="inlineStr">
@@ -37958,7 +37978,7 @@
       </c>
       <c r="G593" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H593" s="5" t="inlineStr">
@@ -37979,7 +37999,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>params={'property': 'memberOf', 'function': 'COUNT', 'group_by': 'department'}</t>
+          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
         </is>
       </c>
       <c r="M593" s="5" t="n">
@@ -37989,26 +38009,26 @@
         <v>0</v>
       </c>
       <c r="O593" s="5" t="n">
-        <v>10.76</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B594" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C594" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D594" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E594" s="5" t="inlineStr">
@@ -38018,12 +38038,12 @@
       </c>
       <c r="F594" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G594" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H594" s="5" t="inlineStr">
@@ -38044,7 +38064,7 @@
       </c>
       <c r="L594" s="5" t="inlineStr">
         <is>
-          <t>params={'property': 'memberOf', 'function': 'COUNT', 'group_by': 'department'}</t>
+          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
         </is>
       </c>
       <c r="M594" s="5" t="n">
@@ -38054,41 +38074,41 @@
         <v>0</v>
       </c>
       <c r="O594" s="5" t="n">
-        <v>11.22</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B595" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C595" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D595" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E595" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F595" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G595" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H595" s="5" t="inlineStr">
@@ -38097,17 +38117,21 @@
         </is>
       </c>
       <c r="I595" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J595" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K595" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L595" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L595" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M595" s="5" t="n">
         <v>0</v>
       </c>
@@ -38115,31 +38139,31 @@
         <v>0</v>
       </c>
       <c r="O595" s="5" t="n">
-        <v>15.38</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D596" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E596" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F596" s="5" t="inlineStr">
@@ -38149,7 +38173,7 @@
       </c>
       <c r="G596" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H596" s="5" t="inlineStr">
@@ -38158,59 +38182,63 @@
         </is>
       </c>
       <c r="I596" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J596" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K596" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L596" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L596" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'value': 'Germany', 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M596" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N596" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O596" s="5" t="n">
-        <v>4.05</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B597" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C597" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D597" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E597" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F597" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G597" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H597" s="5" t="inlineStr">
@@ -38219,44 +38247,48 @@
         </is>
       </c>
       <c r="I597" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J597" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K597" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L597" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L597" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'value': 'Germany', 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M597" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N597" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O597" s="5" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments_002</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B598" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C598" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D598" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E598" s="5" t="inlineStr">
@@ -38266,12 +38298,12 @@
       </c>
       <c r="F598" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G598" s="5" t="inlineStr">
         <is>
-          <t>compare_two_departments</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H598" s="5" t="inlineStr">
@@ -38280,31 +38312,35 @@
         </is>
       </c>
       <c r="I598" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J598" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K598" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L598" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L598" s="5" t="inlineStr">
+        <is>
+          <t>params={'property': 'airport', 'value': 'Germany', 'mode': 'count'}</t>
+        </is>
+      </c>
       <c r="M598" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N598" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O598" s="5" t="n">
-        <v>2.77</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_002</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
@@ -38312,12 +38348,12 @@
       </c>
       <c r="C599" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D599" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E599" s="5" t="inlineStr">
@@ -38359,13 +38395,13 @@
         <v>1</v>
       </c>
       <c r="O599" s="5" t="n">
-        <v>32.83</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_002</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
@@ -38373,22 +38409,22 @@
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E600" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F600" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G600" s="5" t="inlineStr">
@@ -38420,13 +38456,13 @@
         <v>1</v>
       </c>
       <c r="O600" s="5" t="n">
-        <v>17.17</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_002</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
@@ -38434,22 +38470,22 @@
       </c>
       <c r="C601" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D601" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E601" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F601" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G601" s="5" t="inlineStr">
@@ -38481,31 +38517,31 @@
         <v>1</v>
       </c>
       <c r="O601" s="5" t="n">
-        <v>17.16</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D602" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E602" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F602" s="5" t="inlineStr">
@@ -38515,7 +38551,7 @@
       </c>
       <c r="G602" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H602" s="5" t="inlineStr">
@@ -38536,32 +38572,32 @@
       </c>
       <c r="L602" s="5" t="n"/>
       <c r="M602" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N602" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O602" s="5" t="n">
-        <v>14.4</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C603" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D603" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E603" s="5" t="inlineStr">
@@ -38571,17 +38607,17 @@
       </c>
       <c r="F603" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G603" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H603" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I603" s="5" t="b">
@@ -38603,46 +38639,46 @@
         <v>1</v>
       </c>
       <c r="O603" s="5" t="n">
-        <v>22.76</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>property_ambiguity</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E604" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F604" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G604" s="5" t="inlineStr">
         <is>
-          <t>VARIES</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H604" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I604" s="5" t="b">
@@ -38664,31 +38700,31 @@
         <v>1</v>
       </c>
       <c r="O604" s="5" t="n">
-        <v>11.19</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B605" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C605" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D605" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E605" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F605" s="5" t="inlineStr">
@@ -38698,12 +38734,12 @@
       </c>
       <c r="G605" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H605" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I605" s="5" t="b">
@@ -38725,31 +38761,31 @@
         <v>1</v>
       </c>
       <c r="O605" s="5" t="n">
-        <v>18.77</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E606" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F606" s="5" t="inlineStr">
@@ -38759,12 +38795,12 @@
       </c>
       <c r="G606" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H606" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I606" s="5" t="b">
@@ -38786,31 +38822,31 @@
         <v>1</v>
       </c>
       <c r="O606" s="5" t="n">
-        <v>14.7</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C607" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D607" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E607" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F607" s="5" t="inlineStr">
@@ -38820,12 +38856,12 @@
       </c>
       <c r="G607" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H607" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I607" s="5" t="b">
@@ -38847,31 +38883,31 @@
         <v>1</v>
       </c>
       <c r="O607" s="5" t="n">
-        <v>15.36</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E608" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F608" s="5" t="inlineStr">
@@ -38881,12 +38917,12 @@
       </c>
       <c r="G608" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H608" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I608" s="5" t="b">
@@ -38908,31 +38944,31 @@
         <v>1</v>
       </c>
       <c r="O608" s="5" t="n">
-        <v>19.72</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C609" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F609" s="5" t="inlineStr">
@@ -38942,12 +38978,12 @@
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I609" s="5" t="b">
@@ -38969,31 +39005,31 @@
         <v>1</v>
       </c>
       <c r="O609" s="5" t="n">
-        <v>16.09</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E610" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F610" s="5" t="inlineStr">
@@ -39003,12 +39039,12 @@
       </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H610" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I610" s="5" t="b">
@@ -39030,31 +39066,31 @@
         <v>1</v>
       </c>
       <c r="O610" s="5" t="n">
-        <v>16.4</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B611" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C611" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D611" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E611" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F611" s="5" t="inlineStr">
@@ -39064,12 +39100,12 @@
       </c>
       <c r="G611" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H611" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I611" s="5" t="b">
@@ -39091,31 +39127,31 @@
         <v>1</v>
       </c>
       <c r="O611" s="5" t="n">
-        <v>17.86</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B612" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D612" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E612" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F612" s="5" t="inlineStr">
@@ -39125,12 +39161,12 @@
       </c>
       <c r="G612" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H612" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I612" s="5" t="b">
@@ -39152,31 +39188,31 @@
         <v>1</v>
       </c>
       <c r="O612" s="5" t="n">
-        <v>14.33</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C613" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D613" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E613" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F613" s="5" t="inlineStr">
@@ -39186,12 +39222,12 @@
       </c>
       <c r="G613" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H613" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I613" s="5" t="b">
@@ -39213,13 +39249,13 @@
         <v>1</v>
       </c>
       <c r="O613" s="5" t="n">
-        <v>14.76</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B614" s="5" t="n">
@@ -39227,17 +39263,17 @@
       </c>
       <c r="C614" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D614" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E614" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F614" s="5" t="inlineStr">
@@ -39274,13 +39310,13 @@
         <v>1</v>
       </c>
       <c r="O614" s="5" t="n">
-        <v>16.25</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
@@ -39288,17 +39324,17 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D615" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E615" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F615" s="5" t="inlineStr">
@@ -39335,13 +39371,13 @@
         <v>1</v>
       </c>
       <c r="O615" s="5" t="n">
-        <v>12.07</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B616" s="5" t="n">
@@ -39349,17 +39385,17 @@
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E616" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F616" s="5" t="inlineStr">
@@ -39396,13 +39432,13 @@
         <v>1</v>
       </c>
       <c r="O616" s="5" t="n">
-        <v>12.61</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>ranking_kg3_001</t>
         </is>
       </c>
       <c r="B617" s="5" t="n">
@@ -39410,7 +39446,7 @@
       </c>
       <c r="C617" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D617" s="5" t="inlineStr">
@@ -39420,7 +39456,7 @@
       </c>
       <c r="E617" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F617" s="5" t="inlineStr">
@@ -39430,7 +39466,7 @@
       </c>
       <c r="G617" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H617" s="5" t="inlineStr">
@@ -39451,19 +39487,19 @@
       </c>
       <c r="L617" s="5" t="n"/>
       <c r="M617" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N617" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O617" s="5" t="n">
-        <v>11.9</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>ranking_kg3_001</t>
         </is>
       </c>
       <c r="B618" s="5" t="n">
@@ -39471,7 +39507,7 @@
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D618" s="5" t="inlineStr">
@@ -39486,12 +39522,12 @@
       </c>
       <c r="F618" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G618" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H618" s="5" t="inlineStr">
@@ -39512,19 +39548,19 @@
       </c>
       <c r="L618" s="5" t="n"/>
       <c r="M618" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N618" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O618" s="5" t="n">
-        <v>12.3</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>ranking_kg3_001</t>
         </is>
       </c>
       <c r="B619" s="5" t="n">
@@ -39532,7 +39568,7 @@
       </c>
       <c r="C619" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D619" s="5" t="inlineStr">
@@ -39542,17 +39578,17 @@
       </c>
       <c r="E619" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F619" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G619" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H619" s="5" t="inlineStr">
@@ -39573,19 +39609,19 @@
       </c>
       <c r="L619" s="5" t="n"/>
       <c r="M619" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N619" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O619" s="5" t="n">
-        <v>12.77</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B620" s="5" t="n">
@@ -39593,17 +39629,17 @@
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D620" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E620" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F620" s="5" t="inlineStr">
@@ -39634,19 +39670,19 @@
       </c>
       <c r="L620" s="5" t="n"/>
       <c r="M620" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N620" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O620" s="5" t="n">
-        <v>12</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B621" s="5" t="n">
@@ -39654,22 +39690,22 @@
       </c>
       <c r="C621" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D621" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E621" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F621" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G621" s="5" t="inlineStr">
@@ -39695,19 +39731,19 @@
       </c>
       <c r="L621" s="5" t="n"/>
       <c r="M621" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N621" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O621" s="5" t="n">
-        <v>12.41</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>group_aggregate_kg1_001</t>
         </is>
       </c>
       <c r="B622" s="5" t="n">
@@ -39715,12 +39751,12 @@
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>group_aggregate_kg1</t>
         </is>
       </c>
       <c r="D622" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E622" s="5" t="inlineStr">
@@ -39730,7 +39766,7 @@
       </c>
       <c r="F622" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G622" s="5" t="inlineStr">
@@ -39756,32 +39792,32 @@
       </c>
       <c r="L622" s="5" t="n"/>
       <c r="M622" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N622" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O622" s="5" t="n">
-        <v>12.61</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B623" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C623" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D623" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E623" s="5" t="inlineStr">
@@ -39796,7 +39832,7 @@
       </c>
       <c r="G623" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H623" s="5" t="inlineStr">
@@ -39805,48 +39841,44 @@
         </is>
       </c>
       <c r="I623" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J623" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K623" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L623" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L623" s="5" t="n"/>
       <c r="M623" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N623" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O623" s="5" t="n">
-        <v>14.84</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B624" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D624" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E624" s="5" t="inlineStr">
@@ -39861,7 +39893,7 @@
       </c>
       <c r="G624" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H624" s="5" t="inlineStr">
@@ -39870,48 +39902,44 @@
         </is>
       </c>
       <c r="I624" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J624" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K624" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L624" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L624" s="5" t="n"/>
       <c r="M624" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N624" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O624" s="5" t="n">
-        <v>11.37</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B625" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C625" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D625" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E625" s="5" t="inlineStr">
@@ -39926,7 +39954,7 @@
       </c>
       <c r="G625" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H625" s="5" t="inlineStr">
@@ -39935,48 +39963,44 @@
         </is>
       </c>
       <c r="I625" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J625" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K625" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L625" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L625" s="5" t="n"/>
       <c r="M625" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N625" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O625" s="5" t="n">
-        <v>11.53</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B626" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D626" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E626" s="5" t="inlineStr">
@@ -39991,7 +40015,7 @@
       </c>
       <c r="G626" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H626" s="5" t="inlineStr">
@@ -40000,48 +40024,44 @@
         </is>
       </c>
       <c r="I626" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J626" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K626" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L626" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L626" s="5" t="n"/>
       <c r="M626" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N626" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O626" s="5" t="n">
-        <v>14.13</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B627" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C627" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D627" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E627" s="5" t="inlineStr">
@@ -40056,7 +40076,7 @@
       </c>
       <c r="G627" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H627" s="5" t="inlineStr">
@@ -40065,48 +40085,44 @@
         </is>
       </c>
       <c r="I627" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J627" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K627" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L627" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L627" s="5" t="n"/>
       <c r="M627" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N627" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O627" s="5" t="n">
-        <v>10.15</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B628" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D628" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E628" s="5" t="inlineStr">
@@ -40121,7 +40137,7 @@
       </c>
       <c r="G628" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H628" s="5" t="inlineStr">
@@ -40130,48 +40146,44 @@
         </is>
       </c>
       <c r="I628" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J628" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K628" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L628" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'operator': '&gt;', 'threshold': 1000, 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L628" s="5" t="n"/>
       <c r="M628" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N628" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O628" s="5" t="n">
-        <v>10.38</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B629" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C629" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D629" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E629" s="5" t="inlineStr">
@@ -40186,7 +40198,7 @@
       </c>
       <c r="G629" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H629" s="5" t="inlineStr">
@@ -40195,48 +40207,44 @@
         </is>
       </c>
       <c r="I629" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J629" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K629" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L629" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'value': 'Germany', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L629" s="5" t="n"/>
       <c r="M629" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N629" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O629" s="5" t="n">
-        <v>12.81</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B630" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D630" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E630" s="5" t="inlineStr">
@@ -40251,7 +40259,7 @@
       </c>
       <c r="G630" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H630" s="5" t="inlineStr">
@@ -40260,48 +40268,44 @@
         </is>
       </c>
       <c r="I630" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J630" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K630" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L630" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'value': 'Germany', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L630" s="5" t="n"/>
       <c r="M630" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N630" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O630" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>group_aggregate_kg3_001</t>
         </is>
       </c>
       <c r="B631" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C631" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>group_aggregate_kg3</t>
         </is>
       </c>
       <c r="D631" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E631" s="5" t="inlineStr">
@@ -40316,7 +40320,7 @@
       </c>
       <c r="G631" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H631" s="5" t="inlineStr">
@@ -40325,29 +40329,25 @@
         </is>
       </c>
       <c r="I631" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J631" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K631" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L631" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'airport', 'value': 'Germany', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L631" s="5" t="n"/>
       <c r="M631" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N631" s="5" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="O631" s="5" t="n">
-        <v>8.81</v>
+        <v>11.55</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/results/NL2SPARQL_Evaluation_Results.xlsx
@@ -38340,7 +38340,7 @@
     <row r="599">
       <c r="A599" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
@@ -38348,7 +38348,7 @@
       </c>
       <c r="C599" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D599" s="5" t="inlineStr">
@@ -38395,13 +38395,13 @@
         <v>1</v>
       </c>
       <c r="O599" s="5" t="n">
-        <v>44.77</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D600" s="5" t="inlineStr">
@@ -38456,13 +38456,13 @@
         <v>1</v>
       </c>
       <c r="O600" s="5" t="n">
-        <v>14.14</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
@@ -38470,7 +38470,7 @@
       </c>
       <c r="C601" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D601" s="5" t="inlineStr">
@@ -38517,13 +38517,13 @@
         <v>1</v>
       </c>
       <c r="O601" s="5" t="n">
-        <v>14.91</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
@@ -38531,7 +38531,7 @@
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D602" s="5" t="inlineStr">
@@ -38578,13 +38578,13 @@
         <v>1</v>
       </c>
       <c r="O602" s="5" t="n">
-        <v>16.86</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
@@ -38592,7 +38592,7 @@
       </c>
       <c r="C603" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D603" s="5" t="inlineStr">
@@ -38639,13 +38639,13 @@
         <v>1</v>
       </c>
       <c r="O603" s="5" t="n">
-        <v>14.14</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
@@ -38653,7 +38653,7 @@
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D604" s="5" t="inlineStr">
@@ -38700,13 +38700,13 @@
         <v>1</v>
       </c>
       <c r="O604" s="5" t="n">
-        <v>14.45</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B605" s="5" t="n">
@@ -38714,7 +38714,7 @@
       </c>
       <c r="C605" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D605" s="5" t="inlineStr">
@@ -38761,13 +38761,13 @@
         <v>1</v>
       </c>
       <c r="O605" s="5" t="n">
-        <v>17.62</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
@@ -38775,7 +38775,7 @@
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D606" s="5" t="inlineStr">
@@ -38822,13 +38822,13 @@
         <v>1</v>
       </c>
       <c r="O606" s="5" t="n">
-        <v>14.27</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
@@ -38836,7 +38836,7 @@
       </c>
       <c r="C607" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D607" s="5" t="inlineStr">
@@ -38883,13 +38883,13 @@
         <v>1</v>
       </c>
       <c r="O607" s="5" t="n">
-        <v>14.42</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>ranking_kg3_001</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
@@ -38897,12 +38897,12 @@
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D608" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E608" s="5" t="inlineStr">
@@ -38917,7 +38917,7 @@
       </c>
       <c r="G608" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H608" s="5" t="inlineStr">
@@ -38938,19 +38938,19 @@
       </c>
       <c r="L608" s="5" t="n"/>
       <c r="M608" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N608" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O608" s="5" t="n">
-        <v>18.3</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>ranking_kg3_001</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
@@ -38958,27 +38958,27 @@
       </c>
       <c r="C609" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D609" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E609" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F609" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
@@ -38999,19 +38999,19 @@
       </c>
       <c r="L609" s="5" t="n"/>
       <c r="M609" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N609" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O609" s="5" t="n">
-        <v>15.59</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>ranking_kg3_001</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
@@ -39019,27 +39019,27 @@
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="D610" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E610" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F610" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G610" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ranking_kg3</t>
         </is>
       </c>
       <c r="H610" s="5" t="inlineStr">
@@ -39060,19 +39060,19 @@
       </c>
       <c r="L610" s="5" t="n"/>
       <c r="M610" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N610" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="O610" s="5" t="n">
-        <v>15.44</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B611" s="5" t="n">
@@ -39080,7 +39080,7 @@
       </c>
       <c r="C611" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D611" s="5" t="inlineStr">
@@ -39090,7 +39090,7 @@
       </c>
       <c r="E611" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F611" s="5" t="inlineStr">
@@ -39127,13 +39127,13 @@
         <v>1</v>
       </c>
       <c r="O611" s="5" t="n">
-        <v>21.77</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B612" s="5" t="n">
@@ -39141,7 +39141,7 @@
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D612" s="5" t="inlineStr">
@@ -39151,7 +39151,7 @@
       </c>
       <c r="E612" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F612" s="5" t="inlineStr">
@@ -39188,13 +39188,13 @@
         <v>1</v>
       </c>
       <c r="O612" s="5" t="n">
-        <v>16.43</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
@@ -39202,7 +39202,7 @@
       </c>
       <c r="C613" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D613" s="5" t="inlineStr">
@@ -39212,7 +39212,7 @@
       </c>
       <c r="E613" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F613" s="5" t="inlineStr">
@@ -39249,13 +39249,13 @@
         <v>1</v>
       </c>
       <c r="O613" s="5" t="n">
-        <v>15.57</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B614" s="5" t="n">
@@ -39263,7 +39263,7 @@
       </c>
       <c r="C614" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D614" s="5" t="inlineStr">
@@ -39273,7 +39273,7 @@
       </c>
       <c r="E614" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F614" s="5" t="inlineStr">
@@ -39310,13 +39310,13 @@
         <v>1</v>
       </c>
       <c r="O614" s="5" t="n">
-        <v>18.98</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
@@ -39324,7 +39324,7 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D615" s="5" t="inlineStr">
@@ -39334,7 +39334,7 @@
       </c>
       <c r="E615" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F615" s="5" t="inlineStr">
@@ -39371,13 +39371,13 @@
         <v>1</v>
       </c>
       <c r="O615" s="5" t="n">
-        <v>15.38</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B616" s="5" t="n">
@@ -39385,7 +39385,7 @@
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D616" s="5" t="inlineStr">
@@ -39395,7 +39395,7 @@
       </c>
       <c r="E616" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F616" s="5" t="inlineStr">
@@ -39432,13 +39432,13 @@
         <v>1</v>
       </c>
       <c r="O616" s="5" t="n">
-        <v>15.38</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_001</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B617" s="5" t="n">
@@ -39446,17 +39446,17 @@
       </c>
       <c r="C617" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D617" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E617" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F617" s="5" t="inlineStr">
@@ -39466,7 +39466,7 @@
       </c>
       <c r="G617" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H617" s="5" t="inlineStr">
@@ -39487,19 +39487,19 @@
       </c>
       <c r="L617" s="5" t="n"/>
       <c r="M617" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N617" s="5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O617" s="5" t="n">
-        <v>18.84</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_001</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B618" s="5" t="n">
@@ -39507,27 +39507,27 @@
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D618" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E618" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F618" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G618" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H618" s="5" t="inlineStr">
@@ -39548,19 +39548,19 @@
       </c>
       <c r="L618" s="5" t="n"/>
       <c r="M618" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N618" s="5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O618" s="5" t="n">
-        <v>19.56</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3_001</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B619" s="5" t="n">
@@ -39568,12 +39568,12 @@
       </c>
       <c r="C619" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D619" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E619" s="5" t="inlineStr">
@@ -39583,12 +39583,12 @@
       </c>
       <c r="F619" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G619" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H619" s="5" t="inlineStr">
@@ -39609,13 +39609,13 @@
       </c>
       <c r="L619" s="5" t="n"/>
       <c r="M619" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N619" s="5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O619" s="5" t="n">
-        <v>21.18</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="620">
@@ -39676,7 +39676,7 @@
         <v>0.5</v>
       </c>
       <c r="O620" s="5" t="n">
-        <v>15.44</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="621">
@@ -39737,7 +39737,7 @@
         <v>0.5</v>
       </c>
       <c r="O621" s="5" t="n">
-        <v>17.31</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="622">
@@ -39798,7 +39798,7 @@
         <v>0.5</v>
       </c>
       <c r="O622" s="5" t="n">
-        <v>14.81</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="623">
@@ -39856,10 +39856,10 @@
         <v>0</v>
       </c>
       <c r="N623" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O623" s="5" t="n">
-        <v>12.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="624">
@@ -39917,10 +39917,10 @@
         <v>0</v>
       </c>
       <c r="N624" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O624" s="5" t="n">
-        <v>10.79</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="625">
@@ -39978,10 +39978,10 @@
         <v>0</v>
       </c>
       <c r="N625" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O625" s="5" t="n">
-        <v>11.42</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="626">
@@ -40039,10 +40039,10 @@
         <v>0</v>
       </c>
       <c r="N626" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O626" s="5" t="n">
-        <v>14.79</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="627">
@@ -40100,10 +40100,10 @@
         <v>0</v>
       </c>
       <c r="N627" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O627" s="5" t="n">
-        <v>11.07</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="628">
@@ -40161,10 +40161,10 @@
         <v>0</v>
       </c>
       <c r="N628" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O628" s="5" t="n">
-        <v>11.25</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="629">
@@ -40222,10 +40222,10 @@
         <v>0</v>
       </c>
       <c r="N629" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O629" s="5" t="n">
-        <v>13.86</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="630">
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="N630" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O630" s="5" t="n">
-        <v>10.53</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="631">
@@ -40344,10 +40344,10 @@
         <v>0</v>
       </c>
       <c r="N631" s="5" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
       <c r="O631" s="5" t="n">
-        <v>11.55</v>
+        <v>10.78</v>
       </c>
     </row>
   </sheetData>
